--- a/output/yearly_surface_area_iteration_17_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_17_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497626050964</v>
+        <v>10.84497614253865</v>
       </c>
       <c r="C21" t="n">
-        <v>37.7890716920536</v>
+        <v>37.78907128098638</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.141011816513046</v>
+        <v>6.254714623756429</v>
       </c>
       <c r="C2" t="n">
-        <v>10.3270041009722</v>
+        <v>14.26872113352314</v>
       </c>
       <c r="D2" t="n">
-        <v>28.40294283156447</v>
+        <v>29.67528785626834</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.95554361586841</v>
+        <v>17.83835578616454</v>
       </c>
       <c r="C3" t="n">
-        <v>38.91647899634356</v>
+        <v>38.23907308041327</v>
       </c>
       <c r="D3" t="n">
-        <v>72.60515146757287</v>
+        <v>70.78891821471626</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.17183121043897</v>
+        <v>37.9818551819006</v>
       </c>
       <c r="C4" t="n">
-        <v>82.66413844528567</v>
+        <v>58.52983463178634</v>
       </c>
       <c r="D4" t="n">
-        <v>101.1190317897172</v>
+        <v>85.47193687943155</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>36.49647090537518</v>
+        <v>49.3573658310084</v>
       </c>
       <c r="C5" t="n">
-        <v>136.6838241237622</v>
+        <v>110.127548723886</v>
       </c>
       <c r="D5" t="n">
-        <v>74.12195167063419</v>
+        <v>59.12575548826417</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>36.18623863083319</v>
+        <v>47.53720558733482</v>
       </c>
       <c r="C6" t="n">
-        <v>148.206596928507</v>
+        <v>150.58144462508</v>
       </c>
       <c r="D6" t="n">
-        <v>47.21519234034186</v>
+        <v>42.74725853831463</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>24.79305652304895</v>
+        <v>33.41672835715293</v>
       </c>
       <c r="C7" t="n">
-        <v>118.4557144990116</v>
+        <v>148.2193596486622</v>
       </c>
       <c r="D7" t="n">
-        <v>38.32743037379547</v>
+        <v>38.08788393395925</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.10142311317368</v>
+        <v>16.6062624173348</v>
       </c>
       <c r="C8" t="n">
-        <v>75.18714792974197</v>
+        <v>99.47067739428682</v>
       </c>
       <c r="D8" t="n">
-        <v>35.88287859022092</v>
+        <v>35.63253292563798</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.878124415953151</v>
+        <v>7.987499321752047</v>
       </c>
       <c r="C9" t="n">
-        <v>42.15624642035802</v>
+        <v>52.36249555370786</v>
       </c>
       <c r="D9" t="n">
-        <v>34.05780960802609</v>
+        <v>33.39218466454675</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.409429850399925</v>
+        <v>5.551783267515713</v>
       </c>
       <c r="C10" t="n">
-        <v>30.7483380970101</v>
+        <v>31.8871654339364</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>34.73423377625215</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>28.96450251839364</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>36.07235589714055</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.77167905773377</v>
+        <v>27.33774657245668</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>34.71459882216721</v>
       </c>
     </row>
     <row r="13">
@@ -940,7 +940,7 @@
         <v>25.23582473766426</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>32.26022956155019</v>
       </c>
     </row>
     <row r="14">
@@ -951,10 +951,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>23.35381438862312</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -965,7 +965,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>20.42526098685489</v>
       </c>
       <c r="D15" t="n">
         <v>29.38370878810703</v>
@@ -982,7 +982,7 @@
         <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1010,7 +1010,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1021,10 +1021,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.673267985410594</v>
+        <v>7.651890743445948</v>
       </c>
       <c r="C21" t="n">
-        <v>93.03837432310345</v>
+        <v>92.77917526428212</v>
       </c>
       <c r="D21" t="n">
-        <v>8.632426483586919</v>
+        <v>7.651890743445948</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.030475236560656</v>
+        <v>7.58105577219387</v>
       </c>
       <c r="C2" t="n">
-        <v>16.97638130183585</v>
+        <v>9.346238144429634</v>
       </c>
       <c r="D2" t="n">
-        <v>24.75476836258332</v>
+        <v>23.44118993430109</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.75919407501905</v>
+        <v>19.12444527872787</v>
       </c>
       <c r="C3" t="n">
-        <v>39.25027321578748</v>
+        <v>46.48084505756524</v>
       </c>
       <c r="D3" t="n">
-        <v>76.72358308688824</v>
+        <v>76.07562960208534</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.48264432205771</v>
+        <v>35.54417563225577</v>
       </c>
       <c r="C4" t="n">
-        <v>88.6753796383889</v>
+        <v>76.15515116612933</v>
       </c>
       <c r="D4" t="n">
-        <v>110.5379192642611</v>
+        <v>97.18811398191299</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.26361677301944</v>
+        <v>52.98983233672161</v>
       </c>
       <c r="C5" t="n">
-        <v>142.5743103492431</v>
+        <v>107.8449853115121</v>
       </c>
       <c r="D5" t="n">
-        <v>90.34533248331273</v>
+        <v>73.48381566287377</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>42.0629803884546</v>
+        <v>55.74854338565514</v>
       </c>
       <c r="C6" t="n">
-        <v>180.28716666018</v>
+        <v>160.6443585936099</v>
       </c>
       <c r="D6" t="n">
-        <v>56.79508643838223</v>
+        <v>49.54978838104078</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>33.23706852727577</v>
+        <v>43.5375654402333</v>
       </c>
       <c r="C7" t="n">
-        <v>161.2147540097772</v>
+        <v>180.7976754663884</v>
       </c>
       <c r="D7" t="n">
-        <v>42.57937968088841</v>
+        <v>41.44153409166636</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>19.10971906316416</v>
+        <v>25.11801501315464</v>
       </c>
       <c r="C8" t="n">
-        <v>112.9893432817654</v>
+        <v>142.4466831476909</v>
       </c>
       <c r="D8" t="n">
-        <v>37.55184968744049</v>
+        <v>37.30150402285756</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.651561680450389</v>
+        <v>11.87031149204818</v>
       </c>
       <c r="C9" t="n">
-        <v>64.89843198923538</v>
+        <v>84.42343033129593</v>
       </c>
       <c r="D9" t="n">
-        <v>35.49999698556465</v>
+        <v>34.94530953266521</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.121196935978863</v>
+        <v>6.548257187326225</v>
       </c>
       <c r="C10" t="n">
-        <v>39.85895679242051</v>
+        <v>44.98367980858886</v>
       </c>
       <c r="D10" t="n">
-        <v>35.3036474447153</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
-        <v>32.16303653882975</v>
+        <v>32.87382187670443</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>36.60544490054656</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>30.59224021203486</v>
+        <v>29.72437524148068</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>34.93156506480576</v>
       </c>
     </row>
     <row r="13">
@@ -1265,7 +1265,7 @@
         <v>25.19753657719863</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>22.21695054710532</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1293,7 +1293,7 @@
         <v>20.25247339090745</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1321,7 +1321,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.847140481352865</v>
+        <v>7.822855652645925</v>
       </c>
       <c r="C21" t="n">
-        <v>101.0319336974181</v>
+        <v>100.7192665278163</v>
       </c>
       <c r="D21" t="n">
-        <v>9.80892560169108</v>
+        <v>8.800712609226666</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.058945919983814</v>
+        <v>8.096473316923445</v>
       </c>
       <c r="C2" t="n">
-        <v>11.14774518172253</v>
+        <v>15.6353139378347</v>
       </c>
       <c r="D2" t="n">
-        <v>26.12136116689489</v>
+        <v>25.51071409485337</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.94710879715769</v>
+        <v>21.34319509032566</v>
       </c>
       <c r="C3" t="n">
-        <v>50.97724954301563</v>
+        <v>41.50829293555515</v>
       </c>
       <c r="D3" t="n">
-        <v>77.45498512655212</v>
+        <v>76.13944320286139</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.62754207165874</v>
+        <v>34.93156506480576</v>
       </c>
       <c r="C4" t="n">
-        <v>91.62356799424208</v>
+        <v>92.28722944231292</v>
       </c>
       <c r="D4" t="n">
-        <v>119.9823321791154</v>
+        <v>108.7128502820663</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.50905369908114</v>
+        <v>52.69530802544756</v>
       </c>
       <c r="C5" t="n">
-        <v>151.1400590687965</v>
+        <v>120.1168316145973</v>
       </c>
       <c r="D5" t="n">
-        <v>103.1571400237336</v>
+        <v>85.78020565856507</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.72588107299945</v>
+        <v>61.78629176677302</v>
       </c>
       <c r="C6" t="n">
-        <v>198.0381469006666</v>
+        <v>165.6355639220006</v>
       </c>
       <c r="D6" t="n">
-        <v>67.74353683614267</v>
+        <v>58.40515267334701</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>39.94436884268997</v>
+        <v>52.64033015400972</v>
       </c>
       <c r="C7" t="n">
-        <v>201.5184425122215</v>
+        <v>201.1591228524672</v>
       </c>
       <c r="D7" t="n">
-        <v>47.84940135728529</v>
+        <v>44.67541102945535</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>25.86905200690345</v>
+        <v>34.13045893814036</v>
       </c>
       <c r="C8" t="n">
-        <v>155.5481062608646</v>
+        <v>181.750952487212</v>
       </c>
       <c r="D8" t="n">
-        <v>39.55461500410399</v>
+        <v>39.13737222979909</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>13.42343636016663</v>
+        <v>16.9734360587231</v>
       </c>
       <c r="C9" t="n">
-        <v>95.07342942696533</v>
+        <v>121.5874896755589</v>
       </c>
       <c r="D9" t="n">
-        <v>36.94218436310322</v>
+        <v>36.38749691020377</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.402377690020952</v>
+        <v>8.398851609831464</v>
       </c>
       <c r="C10" t="n">
-        <v>54.6637121724624</v>
+        <v>67.19081287865171</v>
       </c>
       <c r="D10" t="n">
-        <v>35.73070769606267</v>
+        <v>35.44600086183109</v>
       </c>
     </row>
     <row r="11">
@@ -1531,10 +1531,10 @@
         <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>38.02701557629594</v>
+        <v>40.15937158992001</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>36.96083756948391</v>
       </c>
     </row>
     <row r="12">
@@ -1545,10 +1545,10 @@
         <v>4.122358610132356</v>
       </c>
       <c r="C12" t="n">
-        <v>32.97886888105885</v>
+        <v>32.76190263842031</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -1573,10 +1573,10 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>27.3485457972034</v>
+        <v>27.04125876577415</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>30.42141611149592</v>
       </c>
     </row>
     <row r="15">
@@ -1590,7 +1590,7 @@
         <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>29.74204670015712</v>
+        <v>29.38370878810703</v>
       </c>
     </row>
     <row r="16">
@@ -1604,7 +1604,7 @@
         <v>21.49242074137117</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -1632,7 +1632,7 @@
         <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>8.004180850274691</v>
+        <v>7.977750720274644</v>
       </c>
       <c r="C21" t="n">
-        <v>108.0564414787083</v>
+        <v>107.6996347237077</v>
       </c>
       <c r="D21" t="n">
-        <v>11.0057486691277</v>
+        <v>9.972188400343304</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.739877916103601</v>
+        <v>7.467173038501239</v>
       </c>
       <c r="C2" t="n">
-        <v>7.758752106662542</v>
+        <v>10.88169155387165</v>
       </c>
       <c r="D2" t="n">
-        <v>21.63968289700819</v>
+        <v>21.13899156784232</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.69109363052752</v>
+        <v>24.72040719293469</v>
       </c>
       <c r="C3" t="n">
-        <v>69.61572970814132</v>
+        <v>63.30800070835556</v>
       </c>
       <c r="D3" t="n">
-        <v>84.81318416988195</v>
+        <v>82.28027509292518</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>18.49318150489717</v>
+        <v>25.30847406777853</v>
       </c>
       <c r="C4" t="n">
-        <v>124.7045386365426</v>
+        <v>108.6873248417559</v>
       </c>
       <c r="D4" t="n">
-        <v>115.4005156433956</v>
+        <v>101.7954559579433</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25.74633354387261</v>
+        <v>34.80295611554943</v>
       </c>
       <c r="C5" t="n">
-        <v>118.3251420543468</v>
+        <v>98.96016858807852</v>
       </c>
       <c r="D5" t="n">
-        <v>68.20692175254716</v>
+        <v>57.94765824316799</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>24.79502001845745</v>
+        <v>32.68434456978482</v>
       </c>
       <c r="C6" t="n">
-        <v>132.7097094169711</v>
+        <v>132.4681994817264</v>
       </c>
       <c r="D6" t="n">
-        <v>31.51704654943536</v>
+        <v>29.42396044398116</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.12757044828985</v>
+        <v>22.57725195456389</v>
       </c>
       <c r="C7" t="n">
-        <v>109.3529497852352</v>
+        <v>127.7980256526243</v>
       </c>
       <c r="D7" t="n">
-        <v>27.78738702100172</v>
+        <v>27.48795397120644</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.262789589568655</v>
+        <v>11.76624623539802</v>
       </c>
       <c r="C8" t="n">
-        <v>70.01333752836128</v>
+        <v>89.62374792069132</v>
       </c>
       <c r="D8" t="n">
-        <v>27.20422888467911</v>
+        <v>26.78698611037422</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.324999547834698</v>
+        <v>5.990624491314035</v>
       </c>
       <c r="C9" t="n">
-        <v>41.71249645803847</v>
+        <v>51.25312064790897</v>
       </c>
       <c r="D9" t="n">
-        <v>27.17968519207294</v>
+        <v>27.06874770149305</v>
       </c>
     </row>
     <row r="10">
@@ -1828,10 +1828,10 @@
         <v>3.843542262126263</v>
       </c>
       <c r="C10" t="n">
-        <v>29.75186417719959</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D10" t="n">
-        <v>28.61303684027329</v>
+        <v>28.89774367450487</v>
       </c>
     </row>
     <row r="11">
@@ -1842,10 +1842,10 @@
         <v>3.020837685967435</v>
       </c>
       <c r="C11" t="n">
-        <v>26.29905750136355</v>
+        <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
-        <v>28.43141351498762</v>
+        <v>28.07602084605028</v>
       </c>
     </row>
     <row r="12">
@@ -1870,10 +1870,10 @@
         <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>22.63419332141022</v>
+        <v>22.37403017978481</v>
       </c>
       <c r="D13" t="n">
-        <v>25.49598787928967</v>
+        <v>25.23582473766426</v>
       </c>
     </row>
     <row r="14">
@@ -1887,7 +1887,7 @@
         <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>24.89024954576939</v>
+        <v>24.58296251434014</v>
       </c>
     </row>
     <row r="15">
@@ -1901,7 +1901,7 @@
         <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>21.85861263505523</v>
+        <v>22.21695054710532</v>
       </c>
     </row>
     <row r="16">
@@ -1929,7 +1929,7 @@
         <v>15.58328130950962</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>17.47216389248049</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>15.51652246562084</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>13.37631247036279</v>
       </c>
     </row>
     <row r="19">
@@ -1971,7 +1971,7 @@
         <v>72.62969516017901</v>
       </c>
       <c r="D20" t="n">
-        <v>7.397468951499714</v>
+        <v>6.724971774090649</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.907936699979052</v>
+        <v>4.532729150507524</v>
       </c>
       <c r="C2" t="n">
-        <v>4.449280595646544</v>
+        <v>5.386849653202249</v>
       </c>
       <c r="D2" t="n">
-        <v>15.13756785178157</v>
+        <v>15.20727193878309</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.48983535115693</v>
+        <v>25.75615102091507</v>
       </c>
       <c r="C3" t="n">
-        <v>50.93797963484576</v>
+        <v>53.97158004096841</v>
       </c>
       <c r="D3" t="n">
-        <v>83.91979375901735</v>
+        <v>80.66530011943918</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.90006702281185</v>
+        <v>34.44658169890783</v>
       </c>
       <c r="C4" t="n">
-        <v>152.2975396121035</v>
+        <v>135.8208678917292</v>
       </c>
       <c r="D4" t="n">
-        <v>128.1249476381385</v>
+        <v>116.7916521403133</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>28.20070280448963</v>
+        <v>38.23907308041327</v>
       </c>
       <c r="C5" t="n">
-        <v>168.222469122691</v>
+        <v>144.9550485320416</v>
       </c>
       <c r="D5" t="n">
-        <v>87.27737090754145</v>
+        <v>73.16474765899356</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.86043726174349</v>
+        <v>38.31957639216151</v>
       </c>
       <c r="C6" t="n">
-        <v>161.4091400552181</v>
+        <v>149.0116300459894</v>
       </c>
       <c r="D6" t="n">
-        <v>39.00385454202154</v>
+        <v>35.58246379272141</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.04961146902685</v>
+        <v>20.84054026575129</v>
       </c>
       <c r="C7" t="n">
-        <v>140.3143271340669</v>
+        <v>156.663371652889</v>
       </c>
       <c r="D7" t="n">
-        <v>30.24273802932299</v>
+        <v>29.8235317596096</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.927612711792993</v>
+        <v>9.680032363873551</v>
       </c>
       <c r="C8" t="n">
-        <v>93.87962421860124</v>
+        <v>115.5762484824558</v>
       </c>
       <c r="D8" t="n">
-        <v>27.95526587842792</v>
+        <v>27.53802310412303</v>
       </c>
     </row>
     <row r="9">
@@ -2122,10 +2122,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.437499623195581</v>
+        <v>4.659374604355361</v>
       </c>
       <c r="C9" t="n">
-        <v>45.5953086283346</v>
+        <v>55.24687030878498</v>
       </c>
       <c r="D9" t="n">
         <v>28.39999758845172</v>
@@ -2139,7 +2139,7 @@
         <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>32.17187226816798</v>
+        <v>33.02599277086271</v>
       </c>
       <c r="D10" t="n">
         <v>29.60951076008381</v>
@@ -2156,7 +2156,7 @@
         <v>28.96450251839364</v>
       </c>
       <c r="D11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.31989518733098</v>
       </c>
     </row>
     <row r="12">
@@ -2167,10 +2167,10 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>20.61179305066178</v>
+        <v>20.39482680802324</v>
       </c>
       <c r="D12" t="n">
-        <v>28.42257778564941</v>
+        <v>28.20561154301086</v>
       </c>
     </row>
     <row r="13">
@@ -2184,7 +2184,7 @@
         <v>16.3902779224005</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>25.75615102091507</v>
       </c>
     </row>
     <row r="14">
@@ -2198,7 +2198,7 @@
         <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>18.12993485432585</v>
+        <v>18.4372218857551</v>
       </c>
     </row>
     <row r="15">
@@ -2226,7 +2226,7 @@
         <v>13.22610507161303</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>13.22217808079604</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>11.33329549782518</v>
       </c>
     </row>
     <row r="18">
@@ -2268,7 +2268,7 @@
         <v>63.19019098384595</v>
       </c>
       <c r="D19" t="n">
-        <v>6.018113427032947</v>
+        <v>5.416302084329653</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.50542014123786</v>
+        <v>4.396266219617217</v>
       </c>
       <c r="C2" t="n">
-        <v>11.08884031946772</v>
+        <v>6.180101798233672</v>
       </c>
       <c r="D2" t="n">
-        <v>16.52085036706533</v>
+        <v>19.08615711826224</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.70519795128547</v>
+        <v>20.59706683509808</v>
       </c>
       <c r="C3" t="n">
-        <v>33.83593462686632</v>
+        <v>37.19351177539041</v>
       </c>
       <c r="D3" t="n">
-        <v>77.16046081527806</v>
+        <v>74.61282552275759</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.8565102709265</v>
+        <v>41.30016242225481</v>
       </c>
       <c r="C4" t="n">
-        <v>139.7773111398439</v>
+        <v>135.1061555630376</v>
       </c>
       <c r="D4" t="n">
-        <v>138.9222088894449</v>
+        <v>128.4057274815531</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.2749557771139</v>
+        <v>44.17864669110647</v>
       </c>
       <c r="C5" t="n">
-        <v>220.9668645333509</v>
+        <v>194.3860454408685</v>
       </c>
       <c r="D5" t="n">
-        <v>109.0476262492145</v>
+        <v>94.19869222248147</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.92585450502953</v>
+        <v>44.11581483803468</v>
       </c>
       <c r="C6" t="n">
-        <v>210.9186767803848</v>
+        <v>187.371458094025</v>
       </c>
       <c r="D6" t="n">
-        <v>53.45419900083034</v>
+        <v>47.25544399621598</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.1162314441954</v>
+        <v>30.3625112492411</v>
       </c>
       <c r="C7" t="n">
-        <v>181.3366549560199</v>
+        <v>183.3129130846687</v>
       </c>
       <c r="D7" t="n">
-        <v>33.71616140694821</v>
+        <v>32.63820242768521</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.18210635137117</v>
+        <v>14.10280577150543</v>
       </c>
       <c r="C8" t="n">
-        <v>134.6025189907589</v>
+        <v>156.8832831386403</v>
       </c>
       <c r="D8" t="n">
-        <v>29.70768553050848</v>
+        <v>29.29044275620359</v>
       </c>
     </row>
     <row r="9">
@@ -2433,10 +2433,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>6.212499472473814</v>
       </c>
       <c r="C9" t="n">
-        <v>75.10468112258522</v>
+        <v>91.96717969072843</v>
       </c>
       <c r="D9" t="n">
         <v>28.95468504135117</v>
@@ -2447,10 +2447,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.562361508084175</v>
+        <v>2.704714925199962</v>
       </c>
       <c r="C10" t="n">
-        <v>40.85543071223102</v>
+        <v>45.55309347705201</v>
       </c>
       <c r="D10" t="n">
         <v>30.17892442854695</v>
@@ -2464,10 +2464,10 @@
         <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>32.69612554223576</v>
+        <v>33.40691088011046</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>29.49759152179966</v>
       </c>
     </row>
     <row r="12">
@@ -2478,10 +2478,10 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>24.95111790343269</v>
+        <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
-        <v>29.07347651356504</v>
+        <v>28.8565102709265</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.73174619702914</v>
+        <v>18.47158305540374</v>
       </c>
       <c r="D13" t="n">
-        <v>26.27647730416588</v>
+        <v>26.01631416254048</v>
       </c>
     </row>
     <row r="14">
@@ -2509,7 +2509,7 @@
         <v>15.97892563432109</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>19.0517959486136</v>
       </c>
     </row>
     <row r="15">
@@ -2537,7 +2537,7 @@
         <v>14.05273663858884</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>14.16661937228147</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>10.38885420633975</v>
       </c>
     </row>
     <row r="18">
@@ -2562,7 +2562,7 @@
         <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>6.955682484588652</v>
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>33.7014351913845</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>4.212679398923063</v>
+        <v>3.610868056219768</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.516800203061322</v>
+        <v>2.679189484889545</v>
       </c>
       <c r="C2" t="n">
-        <v>5.338744015694155</v>
+        <v>3.036545649235384</v>
       </c>
       <c r="D2" t="n">
-        <v>11.51393707540659</v>
+        <v>13.34587829153114</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.97870465014283</v>
+        <v>20.18964153783566</v>
       </c>
       <c r="C3" t="n">
-        <v>39.8295043612931</v>
+        <v>34.16482010778901</v>
       </c>
       <c r="D3" t="n">
-        <v>75.99708978574559</v>
+        <v>75.10369937488099</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.63878326476196</v>
+        <v>45.32041927114551</v>
       </c>
       <c r="C4" t="n">
-        <v>134.3659177940355</v>
+        <v>133.4597646630156</v>
       </c>
       <c r="D4" t="n">
-        <v>147.7795366771596</v>
+        <v>137.2630552692678</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.01755795215198</v>
+        <v>46.24031687002478</v>
       </c>
       <c r="C5" t="n">
-        <v>266.1763463139165</v>
+        <v>239.8409641474958</v>
       </c>
       <c r="D5" t="n">
-        <v>114.1036269260856</v>
+        <v>99.10743074371554</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.12961605915636</v>
+        <v>35.94472869558847</v>
       </c>
       <c r="C6" t="n">
-        <v>243.2407564473025</v>
+        <v>219.1300145787051</v>
       </c>
       <c r="D6" t="n">
-        <v>51.64287448649497</v>
+        <v>46.08814597586652</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.366053024963818</v>
+        <v>9.342311153612647</v>
       </c>
       <c r="C7" t="n">
-        <v>184.4507586738907</v>
+        <v>196.8472869354152</v>
       </c>
       <c r="D7" t="n">
-        <v>33.95570784678443</v>
+        <v>32.99752208743954</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.838633523605028</v>
+        <v>4.255876297909922</v>
       </c>
       <c r="C8" t="n">
-        <v>93.54582999915733</v>
+        <v>112.3217548428776</v>
       </c>
       <c r="D8" t="n">
-        <v>31.2097595180061</v>
+        <v>30.95941385342316</v>
       </c>
     </row>
     <row r="9">
@@ -2744,10 +2744,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.774999849278233</v>
+        <v>1.885937339858122</v>
       </c>
       <c r="C9" t="n">
-        <v>31.17343485294896</v>
+        <v>34.72343455150543</v>
       </c>
       <c r="D9" t="n">
         <v>31.50624732468863</v>
@@ -2761,10 +2761,10 @@
         <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>26.1930287493049</v>
       </c>
       <c r="D10" t="n">
-        <v>23.20360698987336</v>
+        <v>23.06125357275758</v>
       </c>
     </row>
     <row r="11">
@@ -2775,10 +2775,10 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>19.90198946049134</v>
+        <v>19.36890045708532</v>
       </c>
       <c r="D11" t="n">
-        <v>23.27821981539612</v>
+        <v>23.10052348092744</v>
       </c>
     </row>
     <row r="12">
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>15.18763698469816</v>
+        <v>14.97067074205961</v>
       </c>
       <c r="D12" t="n">
         <v>21.26269177857742</v>
@@ -2806,7 +2806,7 @@
         <v>13.00815708127024</v>
       </c>
       <c r="D13" t="n">
-        <v>15.34962535589888</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -2834,7 +2834,7 @@
         <v>11.82515109765283</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>12.18348900970292</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>11.98615772114931</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>8.679631453246051</v>
       </c>
     </row>
     <row r="17">
@@ -2859,7 +2859,7 @@
         <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>29.27768003604838</v>
+        <v>29.7499006817911</v>
       </c>
       <c r="D17" t="n">
         <v>5.66664774891259</v>
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>28.89283493598363</v>
+        <v>28.35778243716912</v>
       </c>
       <c r="D18" t="n">
-        <v>3.21031499288707</v>
+        <v>2.675262494072558</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.572178985126643</v>
+        <v>4.034001316750144</v>
       </c>
       <c r="C2" t="n">
-        <v>8.586365421342604</v>
+        <v>2.805834938737384</v>
       </c>
       <c r="D2" t="n">
-        <v>9.98437415219006</v>
+        <v>12.81966152205485</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.331511928865933</v>
+        <v>15.01583113645496</v>
       </c>
       <c r="C3" t="n">
-        <v>30.51271864799087</v>
+        <v>23.2085157283946</v>
       </c>
       <c r="D3" t="n">
-        <v>68.64870821945821</v>
+        <v>69.10031216341176</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.42257778564941</v>
+        <v>42.02763747110171</v>
       </c>
       <c r="C4" t="n">
-        <v>118.9485518465436</v>
+        <v>110.5379192642611</v>
       </c>
       <c r="D4" t="n">
-        <v>150.9319285554961</v>
+        <v>141.9980244468501</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>39.61351986635881</v>
+        <v>55.14967728606459</v>
       </c>
       <c r="C5" t="n">
-        <v>257.3406169756952</v>
+        <v>244.4060909722435</v>
       </c>
       <c r="D5" t="n">
-        <v>136.217493964245</v>
+        <v>119.8223073033232</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>34.25415914887547</v>
+        <v>45.92713935237005</v>
       </c>
       <c r="C6" t="n">
-        <v>323.7843198514151</v>
+        <v>289.5704123584138</v>
       </c>
       <c r="D6" t="n">
-        <v>67.86429180376503</v>
+        <v>61.58503348740243</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.73210604992764</v>
+        <v>19.22360179685679</v>
       </c>
       <c r="C7" t="n">
-        <v>252.2424011475415</v>
+        <v>249.9667099690974</v>
       </c>
       <c r="D7" t="n">
-        <v>38.62686342359076</v>
+        <v>36.83026512481909</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.923464736797754</v>
+        <v>5.757950285407543</v>
       </c>
       <c r="C8" t="n">
-        <v>151.3756785178157</v>
+        <v>169.984706251814</v>
       </c>
       <c r="D8" t="n">
-        <v>32.87873061522568</v>
+        <v>32.54493639578176</v>
       </c>
     </row>
     <row r="9">
@@ -3055,10 +3055,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>60.34999487545991</v>
+        <v>70.44530651822986</v>
       </c>
       <c r="D9" t="n">
         <v>32.28280975874785</v>
@@ -3072,10 +3072,10 @@
         <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>30.17892442854695</v>
+        <v>31.60245859970483</v>
       </c>
       <c r="D10" t="n">
-        <v>24.48478774391545</v>
+        <v>24.34243432679967</v>
       </c>
     </row>
     <row r="11">
@@ -3089,7 +3089,7 @@
         <v>22.92282714645877</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3100,7 +3100,7 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.35729941108361</v>
+        <v>17.14033316844506</v>
       </c>
       <c r="D12" t="n">
         <v>21.26269177857742</v>
@@ -3114,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>15.08946221427348</v>
+        <v>14.82929907264807</v>
       </c>
       <c r="D13" t="n">
-        <v>15.34962535589888</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -3131,7 +3131,7 @@
         <v>13.82791641431633</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>13.82791641431633</v>
       </c>
     </row>
     <row r="15">
@@ -3145,7 +3145,7 @@
         <v>12.90016483380309</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>11.46681318560274</v>
       </c>
     </row>
     <row r="16">
@@ -3159,7 +3159,7 @@
         <v>23.55899965881071</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>7.852999886270235</v>
       </c>
     </row>
     <row r="17">
@@ -3173,7 +3173,7 @@
         <v>33.0554452019901</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>4.249985811684442</v>
       </c>
     </row>
     <row r="18">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.59730351480956</v>
+        <v>2.870630287217673</v>
       </c>
       <c r="C2" t="n">
-        <v>4.645630136495907</v>
+        <v>1.98214861487431</v>
       </c>
       <c r="D2" t="n">
-        <v>7.717518703084177</v>
+        <v>9.309913479372502</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.115527433931634</v>
+        <v>14.53477476137403</v>
       </c>
       <c r="C3" t="n">
-        <v>32.00006641992479</v>
+        <v>18.07888397370501</v>
       </c>
       <c r="D3" t="n">
-        <v>62.92511910369931</v>
+        <v>64.88861451219293</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.15532142591602</v>
+        <v>37.59897357724434</v>
       </c>
       <c r="C4" t="n">
-        <v>104.6798307130204</v>
+        <v>92.14683952060562</v>
       </c>
       <c r="D4" t="n">
-        <v>151.2254711190659</v>
+        <v>143.7337543879585</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>41.87153958612647</v>
+        <v>59.81297888123694</v>
       </c>
       <c r="C5" t="n">
-        <v>252.260072606218</v>
+        <v>235.6439927118407</v>
       </c>
       <c r="D5" t="n">
-        <v>150.9437095279471</v>
+        <v>134.6466976374501</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>39.16486116551801</v>
+        <v>52.81017250684443</v>
       </c>
       <c r="C6" t="n">
-        <v>364.9617638106391</v>
+        <v>333.9277371316932</v>
       </c>
       <c r="D6" t="n">
-        <v>80.30205346886787</v>
+        <v>72.41272891754049</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>13.1750541909922</v>
+        <v>17.00779722837174</v>
       </c>
       <c r="C7" t="n">
-        <v>316.4408470236489</v>
+        <v>307.7572885795859</v>
       </c>
       <c r="D7" t="n">
-        <v>43.47767883027424</v>
+        <v>40.90255460203486</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.005530633326986</v>
+        <v>4.589670517353839</v>
       </c>
       <c r="C8" t="n">
-        <v>196.6882438073272</v>
+        <v>212.4600206760522</v>
       </c>
       <c r="D8" t="n">
-        <v>33.62976760897448</v>
+        <v>33.79666471869644</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.553124868118454</v>
+        <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>64.45468202691582</v>
+        <v>77.32343093418301</v>
       </c>
       <c r="D9" t="n">
-        <v>31.94999728700819</v>
+        <v>31.72812230584841</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>30.7483380970101</v>
+        <v>31.74481201682062</v>
       </c>
       <c r="D10" t="n">
-        <v>25.0542014123786</v>
+        <v>25.19655482949439</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.56743447752142</v>
+        <v>22.38973814305275</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>23.98900515327081</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.48943444052943</v>
+        <v>16.27246819789088</v>
       </c>
       <c r="D12" t="n">
-        <v>19.52696183746906</v>
+        <v>19.7439280801076</v>
       </c>
     </row>
     <row r="13">
@@ -3428,7 +3428,7 @@
         <v>11.44717823151781</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>15.60978849752428</v>
       </c>
     </row>
     <row r="14">
@@ -3442,7 +3442,7 @@
         <v>10.75504610002381</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>10.75504610002381</v>
       </c>
     </row>
     <row r="15">
@@ -3456,7 +3456,7 @@
         <v>19.70858516275472</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>6.450082416901544</v>
       </c>
     </row>
     <row r="16">
@@ -3470,7 +3470,7 @@
         <v>28.10547327717769</v>
       </c>
       <c r="D16" t="n">
-        <v>3.719842051391165</v>
+        <v>3.306526267903257</v>
       </c>
     </row>
     <row r="17">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.724930716361646</v>
+        <v>3.569634652641403</v>
       </c>
       <c r="C2" t="n">
-        <v>12.80493530649115</v>
+        <v>10.68534201302228</v>
       </c>
       <c r="D2" t="n">
-        <v>14.22748772994478</v>
+        <v>10.69712298547324</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>7.372925258893545</v>
+        <v>12.18839774822415</v>
       </c>
       <c r="C3" t="n">
-        <v>25.92795686915826</v>
+        <v>13.39594742444773</v>
       </c>
       <c r="D3" t="n">
-        <v>56.26886966890594</v>
+        <v>58.78214379177777</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>21.44136986075034</v>
+        <v>32.72361447795468</v>
       </c>
       <c r="C4" t="n">
-        <v>94.03572210357649</v>
+        <v>72.02002983584177</v>
       </c>
       <c r="D4" t="n">
-        <v>148.290045483368</v>
+        <v>142.7127367755419</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.22711218151306</v>
+        <v>58.92940594741481</v>
       </c>
       <c r="C5" t="n">
-        <v>225.5074476654924</v>
+        <v>208.2777754559609</v>
       </c>
       <c r="D5" t="n">
-        <v>163.8046044535803</v>
+        <v>146.9430876331414</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.16235789076178</v>
+        <v>61.86679507852126</v>
       </c>
       <c r="C6" t="n">
-        <v>379.8146248281891</v>
+        <v>350.3906643842079</v>
       </c>
       <c r="D6" t="n">
-        <v>97.7310204623615</v>
+        <v>90.00270253453061</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>23.35577788403162</v>
+        <v>31.68001666834032</v>
       </c>
       <c r="C7" t="n">
-        <v>399.3239152069816</v>
+        <v>374.2913122440964</v>
       </c>
       <c r="D7" t="n">
-        <v>51.92169083450106</v>
+        <v>48.32849423695774</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.842781498600267</v>
+        <v>8.428304040958867</v>
       </c>
       <c r="C8" t="n">
-        <v>275.5471281509522</v>
+        <v>286.4788888377404</v>
       </c>
       <c r="D8" t="n">
-        <v>36.13322425480386</v>
+        <v>35.88287859022092</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>2.32968730217768</v>
       </c>
       <c r="C9" t="n">
-        <v>124.9156143929556</v>
+        <v>139.559363149501</v>
       </c>
       <c r="D9" t="n">
-        <v>33.17030968338697</v>
+        <v>32.61562223048752</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>45.26838664282043</v>
+        <v>51.38958357879929</v>
       </c>
       <c r="D10" t="n">
-        <v>25.90832191507333</v>
+        <v>26.47773558353648</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>26.47675383583222</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>24.34439782220815</v>
+        <v>24.16670148773948</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>19.09302935219197</v>
+        <v>18.87606310955342</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>20.17786056538469</v>
       </c>
     </row>
     <row r="13">
@@ -3739,7 +3739,7 @@
         <v>13.00815708127024</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3753,7 +3753,7 @@
         <v>11.36962016288231</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>10.75504610002381</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>6.091744504851459</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>2.89321048441535</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.285328729037327</v>
+        <v>7.320892630568465</v>
       </c>
       <c r="C2" t="n">
-        <v>7.866744354129692</v>
+        <v>12.00775617064274</v>
       </c>
       <c r="D2" t="n">
-        <v>2.554507526450201</v>
+        <v>5.285729639664827</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.273326772408113</v>
+        <v>2.610467145592269</v>
       </c>
       <c r="C2" t="n">
-        <v>7.682175785731292</v>
+        <v>6.325400458462199</v>
       </c>
       <c r="D2" t="n">
-        <v>10.58520374718911</v>
+        <v>7.959028638328891</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.64076245570368</v>
+        <v>15.85031668506475</v>
       </c>
       <c r="C3" t="n">
-        <v>36.6437330610122</v>
+        <v>23.2085157283946</v>
       </c>
       <c r="D3" t="n">
-        <v>62.38024912784233</v>
+        <v>63.63688618927824</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.28593492830985</v>
+        <v>45.02687670757571</v>
       </c>
       <c r="C4" t="n">
-        <v>132.3876961699781</v>
+        <v>107.5003918673215</v>
       </c>
       <c r="D4" t="n">
-        <v>152.2209632911722</v>
+        <v>144.3718903957189</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>25.42726553999239</v>
+        <v>35.39200473809752</v>
       </c>
       <c r="C5" t="n">
-        <v>329.0818304635309</v>
+        <v>301.6419821298325</v>
       </c>
       <c r="D5" t="n">
-        <v>146.1331457771377</v>
+        <v>133.2231634662922</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>14.49059611468292</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="C6" t="n">
-        <v>326.2799225156105</v>
+        <v>308.3276839957533</v>
       </c>
       <c r="D6" t="n">
-        <v>77.0014176871901</v>
+        <v>71.20517924131691</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.491495746929157</v>
+        <v>5.569454726192155</v>
       </c>
       <c r="C7" t="n">
-        <v>193.7331832175443</v>
+        <v>201.4585559022625</v>
       </c>
       <c r="D7" t="n">
-        <v>31.50035683846316</v>
+        <v>30.9014907388726</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.418625432636641</v>
+        <v>1.585522542358599</v>
       </c>
       <c r="C8" t="n">
-        <v>92.04375601165971</v>
+        <v>102.808619588726</v>
       </c>
       <c r="D8" t="n">
-        <v>24.45042657426681</v>
+        <v>24.03318379996192</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>34.50155957034565</v>
+        <v>39.160934174701</v>
       </c>
       <c r="D9" t="n">
-        <v>19.74687332322034</v>
+        <v>20.1906232855399</v>
       </c>
     </row>
     <row r="10">
@@ -4316,10 +4316,10 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>20.78359889890498</v>
+        <v>20.92595231602077</v>
       </c>
       <c r="D10" t="n">
-        <v>19.07535789351553</v>
+        <v>18.93300447639974</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.28188476430585</v>
+        <v>15.10418842983717</v>
       </c>
       <c r="D11" t="n">
-        <v>15.99267010218054</v>
+        <v>16.17036643664921</v>
       </c>
     </row>
     <row r="12">
@@ -4347,7 +4347,7 @@
         <v>10.63134588928871</v>
       </c>
       <c r="D12" t="n">
-        <v>13.0179745583127</v>
+        <v>12.80100831567416</v>
       </c>
     </row>
     <row r="13">
@@ -4361,7 +4361,7 @@
         <v>9.365873098514571</v>
       </c>
       <c r="D13" t="n">
-        <v>9.105709956889166</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.916592502868027</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>21.85861263505523</v>
+        <v>22.21695054710532</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5083653843506</v>
+        <v>2.150027472300515</v>
       </c>
     </row>
     <row r="16">
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.406885517914684</v>
+        <v>7.176575718044184</v>
       </c>
       <c r="C2" t="n">
-        <v>5.607742886657781</v>
+        <v>9.483682823024189</v>
       </c>
       <c r="D2" t="n">
-        <v>20.30548776693678</v>
+        <v>15.67065685518759</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.1106186954104</v>
+        <v>15.54597489674824</v>
       </c>
       <c r="C3" t="n">
-        <v>20.13564541410208</v>
+        <v>30.25746424488669</v>
       </c>
       <c r="D3" t="n">
-        <v>5.384886157793755</v>
+        <v>7.574183538264141</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.493238258159399</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>4.736932672990861</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>9.35114688295087</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>8.050331174823848</v>
       </c>
       <c r="C6" t="n">
         <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>32.8453511932813</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>32.21899615797182</v>
       </c>
     </row>
     <row r="8">
@@ -4655,7 +4655,7 @@
         <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>25.60201663134832</v>
+        <v>25.81898287398687</v>
       </c>
       <c r="D12" t="n">
         <v>43.17628228507047</v>
@@ -4666,10 +4666,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>24.19517217116264</v>
+        <v>23.93500902953724</v>
       </c>
       <c r="D13" t="n">
         <v>44.22773407631881</v>
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39947978514713</v>
+        <v>13.397776363799</v>
       </c>
       <c r="C21" t="n">
-        <v>70.15021769871142</v>
+        <v>70.14129978694773</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576409386487897</v>
+        <v>1.576208983976353</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.208752408106076</v>
+        <v>6.252751128347935</v>
       </c>
       <c r="C2" t="n">
-        <v>6.107452468119408</v>
+        <v>3.956443248114646</v>
       </c>
       <c r="D2" t="n">
-        <v>29.95115896116169</v>
+        <v>18.04157756094363</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.87133429748144</v>
+        <v>21.12721059539136</v>
       </c>
       <c r="C3" t="n">
-        <v>21.22047662729481</v>
+        <v>34.46425315758428</v>
       </c>
       <c r="D3" t="n">
-        <v>21.13702807243383</v>
+        <v>18.90355204527233</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>10.72068493037517</v>
+        <v>17.99543541884404</v>
       </c>
       <c r="C4" t="n">
-        <v>31.20485077948487</v>
+        <v>46.64774216728719</v>
       </c>
       <c r="D4" t="n">
-        <v>17.89333365760237</v>
+        <v>19.04197847157113</v>
       </c>
     </row>
     <row r="5">
@@ -4868,10 +4868,10 @@
         <v>3.067961575771283</v>
       </c>
       <c r="C5" t="n">
-        <v>5.399612373357458</v>
+        <v>5.473243451175969</v>
       </c>
       <c r="D5" t="n">
-        <v>29.10881943091793</v>
+        <v>29.40334374219198</v>
       </c>
     </row>
     <row r="6">
@@ -4882,10 +4882,10 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>16.34217228489241</v>
       </c>
       <c r="D6" t="n">
-        <v>34.77743067523902</v>
+        <v>34.57617239586842</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>9.513135254151592</v>
       </c>
       <c r="C8" t="n">
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>36.63391558396972</v>
       </c>
     </row>
     <row r="9">
@@ -4921,7 +4921,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.318749208710722</v>
+        <v>9.429686699290611</v>
       </c>
       <c r="C9" t="n">
         <v>25.73749781453438</v>
@@ -4935,10 +4935,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.968265278294615</v>
+        <v>8.825911861178826</v>
       </c>
       <c r="C10" t="n">
-        <v>27.04714925199963</v>
+        <v>27.3318560862312</v>
       </c>
       <c r="D10" t="n">
         <v>50.1084028247572</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>29.07347651356504</v>
+        <v>28.8565102709265</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -4977,7 +4977,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>5.203262832508096</v>
       </c>
       <c r="C13" t="n">
         <v>26.79680358741669</v>
@@ -4991,10 +4991,10 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.302018440009523</v>
+        <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
-        <v>25.81211064005714</v>
+        <v>25.50482360862789</v>
       </c>
       <c r="D14" t="n">
         <v>44.86390658867074</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5022,10 +5022,10 @@
         <v>5.373105185342793</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -5039,7 +5039,7 @@
         <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>36.36098972218912</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>34.24335992412875</v>
       </c>
       <c r="D18" t="n">
         <v>31.56809743005619</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.4431984343725</v>
+        <v>15.43768895154831</v>
       </c>
       <c r="C21" t="n">
-        <v>86.1567912654466</v>
+        <v>86.12605415074323</v>
       </c>
       <c r="D21" t="n">
-        <v>3.251199670394211</v>
+        <v>3.250039779273329</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.526838664282042</v>
+        <v>6.021058670145687</v>
       </c>
       <c r="C2" t="n">
-        <v>10.82573193472958</v>
+        <v>10.29755166984479</v>
       </c>
       <c r="D2" t="n">
-        <v>31.2706278756694</v>
+        <v>18.49612674800991</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.57542732787565</v>
+        <v>21.61317570899353</v>
       </c>
       <c r="C3" t="n">
-        <v>22.7618205229623</v>
+        <v>23.07107104980004</v>
       </c>
       <c r="D3" t="n">
-        <v>40.19275101186442</v>
+        <v>28.9468310597172</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.15157436154828</v>
+        <v>30.57947749187965</v>
       </c>
       <c r="C4" t="n">
-        <v>44.1207235765559</v>
+        <v>69.59511300635214</v>
       </c>
       <c r="D4" t="n">
-        <v>24.45337181737955</v>
+        <v>24.23640557474101</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>9.768389657255765</v>
+        <v>15.41343895667493</v>
       </c>
       <c r="C5" t="n">
-        <v>35.14656781203582</v>
+        <v>50.58455046131692</v>
       </c>
       <c r="D5" t="n">
-        <v>28.8879261974624</v>
+        <v>29.52606220522283</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>5.916993413495527</v>
       </c>
       <c r="C6" t="n">
-        <v>12.11574841810989</v>
+        <v>12.23650338573225</v>
       </c>
       <c r="D6" t="n">
-        <v>36.6290068454485</v>
+        <v>36.54850353370026</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>9.581857593448868</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>24.37385025333556</v>
       </c>
       <c r="D7" t="n">
-        <v>37.78845088416398</v>
+        <v>37.4890178343687</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>10.34762080276138</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>29.54078842078653</v>
       </c>
       <c r="D8" t="n">
-        <v>38.05254101660637</v>
+        <v>37.88564390688441</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>10.09531164276995</v>
       </c>
       <c r="C9" t="n">
         <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>41.15780900513902</v>
       </c>
     </row>
     <row r="10">
@@ -5246,10 +5246,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.537678946757763</v>
+        <v>9.395325529641976</v>
       </c>
       <c r="C10" t="n">
-        <v>29.46715734296802</v>
+        <v>29.89421759431538</v>
       </c>
       <c r="D10" t="n">
         <v>49.25428232206248</v>
@@ -5263,7 +5263,7 @@
         <v>8.351727720027615</v>
       </c>
       <c r="C11" t="n">
-        <v>31.27455486648638</v>
+        <v>31.45225120095506</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5277,7 +5277,7 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D12" t="n">
         <v>46.2138096820101</v>
@@ -5288,10 +5288,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
         <v>45.00822350119503</v>
@@ -5302,7 +5302,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.302018440009523</v>
+        <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
         <v>27.9631198600619</v>
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
         <v>27.5920192278566</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>43.71722527011046</v>
       </c>
     </row>
     <row r="16">
@@ -5347,10 +5347,10 @@
         <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73611278685612</v>
+        <v>16.72502612706146</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0902879998223</v>
+        <v>102.0226593750749</v>
       </c>
       <c r="D21" t="n">
-        <v>5.020833836056835</v>
+        <v>4.181256531765364</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.567090320156161</v>
+        <v>5.893431468593603</v>
       </c>
       <c r="C2" t="n">
-        <v>9.832203258031806</v>
+        <v>5.913066422678538</v>
       </c>
       <c r="D2" t="n">
-        <v>24.5171854181556</v>
+        <v>27.67939477353457</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.67360209830033</v>
+        <v>21.01921834792421</v>
       </c>
       <c r="C3" t="n">
-        <v>33.86047831947249</v>
+        <v>32.61856747360027</v>
       </c>
       <c r="D3" t="n">
-        <v>55.01714134599126</v>
+        <v>36.56519324467245</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.71237328485147</v>
+        <v>36.60348140513808</v>
       </c>
       <c r="C4" t="n">
-        <v>51.2933723037831</v>
+        <v>63.06060028688537</v>
       </c>
       <c r="D4" t="n">
-        <v>38.30092318578082</v>
+        <v>32.80019079888594</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22.11386703815941</v>
+        <v>30.13965452037709</v>
       </c>
       <c r="C5" t="n">
-        <v>60.15659057772332</v>
+        <v>91.40071126537806</v>
       </c>
       <c r="D5" t="n">
-        <v>30.85142160595602</v>
+        <v>31.29320807286709</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9.700649065662736</v>
+        <v>13.20254312671111</v>
       </c>
       <c r="C6" t="n">
-        <v>34.57617239586842</v>
+        <v>47.37619896383834</v>
       </c>
       <c r="D6" t="n">
-        <v>37.95731148929444</v>
+        <v>38.07806645691679</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.563785224144926</v>
+        <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>21.19985992550562</v>
+        <v>21.31963314542373</v>
       </c>
       <c r="D7" t="n">
-        <v>39.76470901281281</v>
+        <v>39.88448223273092</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.84831213192725</v>
+        <v>10.76486357706628</v>
       </c>
       <c r="C8" t="n">
-        <v>31.87734795689393</v>
+        <v>31.29320807286708</v>
       </c>
       <c r="D8" t="n">
-        <v>40.05530633326986</v>
+        <v>39.30426933952106</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.6499990956694</v>
+        <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>33.9468721174462</v>
+        <v>34.05780960802609</v>
       </c>
       <c r="D9" t="n">
-        <v>42.26718391093791</v>
+        <v>42.15624642035802</v>
       </c>
     </row>
     <row r="10">
@@ -5557,10 +5557,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>10.10709261522091</v>
+        <v>9.964739198105127</v>
       </c>
       <c r="C10" t="n">
-        <v>33.31069960509428</v>
+        <v>33.16834618797849</v>
       </c>
       <c r="D10" t="n">
         <v>48.68486865359933</v>
@@ -5574,7 +5574,7 @@
         <v>8.884816723433632</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>33.93999988351647</v>
       </c>
       <c r="D11" t="n">
         <v>50.82115165804038</v>
@@ -5585,7 +5585,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>7.159886007071988</v>
       </c>
       <c r="C12" t="n">
         <v>34.28066633689012</v>
@@ -5602,7 +5602,7 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>32.5203927031756</v>
       </c>
       <c r="D13" t="n">
         <v>45.78871292607123</v>
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.302018440009523</v>
+        <v>4.609305471438775</v>
       </c>
       <c r="C14" t="n">
         <v>30.72870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>45.7857676829585</v>
       </c>
     </row>
     <row r="15">
@@ -5630,7 +5630,7 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.02537087605695</v>
+        <v>29.38370878810703</v>
       </c>
       <c r="D15" t="n">
         <v>43.71722527011046</v>
@@ -5644,7 +5644,7 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
         <v>41.33157834879071</v>
@@ -5658,10 +5658,10 @@
         <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>35.31346492175777</v>
       </c>
       <c r="D18" t="n">
         <v>32.1031499288707</v>
@@ -5686,10 +5686,10 @@
         <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>36.71049190490098</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>25.27607639353838</v>
       </c>
     </row>
     <row r="20">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.0592513131011</v>
+        <v>18.04007890562052</v>
       </c>
       <c r="C21" t="n">
-        <v>117.8151157092786</v>
+        <v>117.6900385747625</v>
       </c>
       <c r="D21" t="n">
-        <v>6.879714785943274</v>
+        <v>6.01335963520684</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.455171081872026</v>
+        <v>6.705336820005715</v>
       </c>
       <c r="C2" t="n">
-        <v>9.481719327615695</v>
+        <v>5.830599615521806</v>
       </c>
       <c r="D2" t="n">
-        <v>30.11903781858789</v>
+        <v>29.71455776443821</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.93099992326224</v>
+        <v>18.19669369821463</v>
       </c>
       <c r="C3" t="n">
-        <v>34.14027641518283</v>
+        <v>25.4861704022472</v>
       </c>
       <c r="D3" t="n">
-        <v>57.78076113344603</v>
+        <v>46.85881792370026</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>20.9436237746972</v>
+        <v>27.9631198600619</v>
       </c>
       <c r="C4" t="n">
-        <v>58.6064109527176</v>
+        <v>61.22276858453534</v>
       </c>
       <c r="D4" t="n">
-        <v>49.11094715724244</v>
+        <v>36.80768492762142</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>18.92318699935727</v>
+        <v>26.06540154775282</v>
       </c>
       <c r="C5" t="n">
-        <v>58.48761948050374</v>
+        <v>77.63169971331654</v>
       </c>
       <c r="D5" t="n">
-        <v>29.96784867213389</v>
+        <v>29.01064466049325</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>10.78744377426395</v>
+        <v>14.49059611468292</v>
       </c>
       <c r="C6" t="n">
-        <v>44.35732477327939</v>
+        <v>64.96617258082844</v>
       </c>
       <c r="D6" t="n">
-        <v>30.51075515258238</v>
+        <v>30.26924521733767</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.090361846519712</v>
+        <v>6.048547605864599</v>
       </c>
       <c r="C7" t="n">
-        <v>22.99645822427728</v>
+        <v>28.62579956042849</v>
       </c>
       <c r="D7" t="n">
-        <v>30.84160412891355</v>
+        <v>31.26081039862693</v>
       </c>
     </row>
     <row r="8">
@@ -5843,10 +5843,10 @@
         <v>4.840016181936775</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>18.44213062427633</v>
       </c>
       <c r="D8" t="n">
-        <v>30.20837685967435</v>
+        <v>29.37389131106456</v>
       </c>
     </row>
     <row r="9">
@@ -5857,10 +5857,10 @@
         <v>4.881249585515139</v>
       </c>
       <c r="C9" t="n">
-        <v>22.07656062539802</v>
+        <v>21.85468564423824</v>
       </c>
       <c r="D9" t="n">
-        <v>30.06405994715006</v>
+        <v>30.17499743772996</v>
       </c>
     </row>
     <row r="10">
@@ -5871,10 +5871,10 @@
         <v>4.412955930589413</v>
       </c>
       <c r="C10" t="n">
-        <v>21.21065915025234</v>
+        <v>21.06830573313655</v>
       </c>
       <c r="D10" t="n">
-        <v>33.45305302221006</v>
+        <v>33.16834618797849</v>
       </c>
     </row>
     <row r="11">
@@ -5888,7 +5888,7 @@
         <v>20.43507846389736</v>
       </c>
       <c r="D11" t="n">
-        <v>34.29539255245382</v>
+        <v>34.65078522139116</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>2.820561154301086</v>
       </c>
       <c r="C12" t="n">
-        <v>19.96089432274615</v>
+        <v>19.7439280801076</v>
       </c>
       <c r="D12" t="n">
-        <v>32.11100391050467</v>
+        <v>31.89403766786613</v>
       </c>
     </row>
     <row r="13">
@@ -5927,7 +5927,7 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="D14" t="n">
         <v>29.49955501720816</v>
@@ -5941,7 +5941,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
         <v>28.30869505195678</v>
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -5969,10 +5969,10 @@
         <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>23.13881164139307</v>
       </c>
     </row>
     <row r="18">
@@ -5997,7 +5997,7 @@
         <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
         <v>15.64709491028566</v>
@@ -6011,7 +6011,7 @@
         <v>1.34499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.08745766113597</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.056781632094455</v>
+        <v>7.04513808457749</v>
       </c>
       <c r="C21" t="n">
-        <v>66.15732780088551</v>
+        <v>66.04816954291397</v>
       </c>
       <c r="D21" t="n">
-        <v>5.292586224070841</v>
+        <v>4.403211302860931</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.037928307567131</v>
+        <v>5.368196446821559</v>
       </c>
       <c r="C2" t="n">
-        <v>8.052294670232339</v>
+        <v>5.693154936927254</v>
       </c>
       <c r="D2" t="n">
-        <v>24.45729880819654</v>
+        <v>25.64423178263093</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.96183501272139</v>
+        <v>21.38737373701677</v>
       </c>
       <c r="C3" t="n">
-        <v>36.02032326881547</v>
+        <v>23.75338570425158</v>
       </c>
       <c r="D3" t="n">
-        <v>69.11994711749668</v>
+        <v>60.49529353568845</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.78520254141498</v>
+        <v>32.86400439966198</v>
       </c>
       <c r="C4" t="n">
-        <v>75.61911691961056</v>
+        <v>62.9457358054885</v>
       </c>
       <c r="D4" t="n">
-        <v>67.52755234120836</v>
+        <v>52.82489872240812</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.4090132442392</v>
+        <v>35.41654843070369</v>
       </c>
       <c r="C5" t="n">
-        <v>89.01997308257954</v>
+        <v>99.10743074371554</v>
       </c>
       <c r="D5" t="n">
-        <v>42.04334543436966</v>
+        <v>35.85833489761475</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19.32079481957723</v>
+        <v>26.04282135055514</v>
       </c>
       <c r="C6" t="n">
-        <v>73.01650375565229</v>
+        <v>98.89831848271095</v>
       </c>
       <c r="D6" t="n">
-        <v>33.65038431076368</v>
+        <v>33.12711278440013</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>12.39652826152447</v>
       </c>
       <c r="C7" t="n">
-        <v>46.95110220789945</v>
+        <v>65.63572451512475</v>
       </c>
       <c r="D7" t="n">
-        <v>32.87774886752143</v>
+        <v>33.47661496711198</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.507604620824606</v>
+        <v>6.00829594999048</v>
       </c>
       <c r="C8" t="n">
-        <v>25.78560345204247</v>
+        <v>29.95803119509142</v>
       </c>
       <c r="D8" t="n">
-        <v>32.21114217633784</v>
+        <v>31.2097595180061</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>23.07499804061703</v>
+        <v>23.18593553119691</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>31.39530983410874</v>
       </c>
     </row>
     <row r="10">
@@ -6182,10 +6182,10 @@
         <v>4.840016181936776</v>
       </c>
       <c r="C10" t="n">
-        <v>24.76949457814703</v>
+        <v>24.48478774391545</v>
       </c>
       <c r="D10" t="n">
-        <v>33.59540643932586</v>
+        <v>33.31069960509428</v>
       </c>
     </row>
     <row r="11">
@@ -6196,10 +6196,10 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>23.10052348092744</v>
       </c>
       <c r="D11" t="n">
-        <v>35.18387422479719</v>
+        <v>35.36157055926586</v>
       </c>
     </row>
     <row r="12">
@@ -6221,10 +6221,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.341468274628643</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
         <v>30.95941385342317</v>
@@ -6238,7 +6238,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
         <v>30.11412908006666</v>
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6280,10 +6280,10 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -6297,7 +6297,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6308,7 +6308,7 @@
         <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
         <v>15.64709491028566</v>
@@ -6322,7 +6322,7 @@
         <v>0.672497177409065</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.276546914976825</v>
+        <v>7.261553477705645</v>
       </c>
       <c r="C21" t="n">
-        <v>75.49417424288457</v>
+        <v>75.33861733119608</v>
       </c>
       <c r="D21" t="n">
-        <v>6.366978550604721</v>
+        <v>5.446165108279234</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.032037821341651</v>
+        <v>4.773257338047992</v>
       </c>
       <c r="C2" t="n">
-        <v>11.29108034654256</v>
+        <v>13.18879865885165</v>
       </c>
       <c r="D2" t="n">
-        <v>21.41486267273568</v>
+        <v>25.58434517267188</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.37769512869454</v>
+        <v>19.78221624057323</v>
       </c>
       <c r="C3" t="n">
-        <v>33.20270735762713</v>
+        <v>22.78145547704723</v>
       </c>
       <c r="D3" t="n">
-        <v>72.64933011426398</v>
+        <v>66.5281331782851</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.09525488950772</v>
+        <v>37.85422798034851</v>
       </c>
       <c r="C4" t="n">
-        <v>84.08080038251383</v>
+        <v>60.38042905429158</v>
       </c>
       <c r="D4" t="n">
-        <v>87.00346329805657</v>
+        <v>69.76102836836986</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>32.49584901056943</v>
+        <v>42.7551125199486</v>
       </c>
       <c r="C5" t="n">
-        <v>116.6316272645211</v>
+        <v>108.826733015759</v>
       </c>
       <c r="D5" t="n">
-        <v>56.76956099807182</v>
+        <v>46.75573441475435</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>27.97490083251287</v>
+        <v>37.83655652167208</v>
       </c>
       <c r="C6" t="n">
-        <v>110.6920536538279</v>
+        <v>130.7776299350134</v>
       </c>
       <c r="D6" t="n">
-        <v>38.9233512302733</v>
+        <v>36.74976181307086</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.70836417857646</v>
+        <v>22.0382724649324</v>
       </c>
       <c r="C7" t="n">
-        <v>78.93055192603505</v>
+        <v>107.1371452167502</v>
       </c>
       <c r="D7" t="n">
-        <v>35.57264631567892</v>
+        <v>35.87207936547421</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.094509821514951</v>
+        <v>10.01382658331747</v>
       </c>
       <c r="C8" t="n">
-        <v>45.56291095409447</v>
+        <v>59.74916528046088</v>
       </c>
       <c r="D8" t="n">
-        <v>33.79666471869644</v>
+        <v>33.46287049925253</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.546874528994477</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>28.17812260729194</v>
+        <v>31.06249736236907</v>
       </c>
       <c r="D9" t="n">
-        <v>33.05937219280708</v>
+        <v>32.28280975874785</v>
       </c>
     </row>
     <row r="10">
@@ -6493,10 +6493,10 @@
         <v>5.124723016168351</v>
       </c>
       <c r="C10" t="n">
-        <v>26.90479583488384</v>
+        <v>26.76244241776806</v>
       </c>
       <c r="D10" t="n">
-        <v>34.30717352490479</v>
+        <v>34.02246669067321</v>
       </c>
     </row>
     <row r="11">
@@ -6507,10 +6507,10 @@
         <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>35.53926689373453</v>
       </c>
     </row>
     <row r="12">
@@ -6532,10 +6532,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>23.15451960466103</v>
       </c>
       <c r="D13" t="n">
         <v>31.47974013667398</v>
@@ -6549,7 +6549,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>21.51009220004762</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
         <v>30.42141611149592</v>
@@ -6563,7 +6563,7 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>18.99190933865455</v>
       </c>
       <c r="D15" t="n">
         <v>29.02537087605695</v>
@@ -6580,7 +6580,7 @@
         <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>26.45221014322606</v>
       </c>
     </row>
     <row r="17">
@@ -6591,7 +6591,7 @@
         <v>0.9444412914854317</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>17.47216389248049</v>
       </c>
       <c r="D17" t="n">
         <v>24.0832529328785</v>
@@ -6608,7 +6608,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>20.33199495495144</v>
       </c>
     </row>
     <row r="19">
@@ -6619,10 +6619,10 @@
         <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>18.05434028109884</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>15.64709491028566</v>
       </c>
     </row>
     <row r="20">
@@ -6633,7 +6633,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.48260407215515</v>
+        <v>7.464353916806528</v>
       </c>
       <c r="C21" t="n">
-        <v>84.17929581174543</v>
+        <v>83.97398156407343</v>
       </c>
       <c r="D21" t="n">
-        <v>7.48260407215515</v>
+        <v>6.531309677205711</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_17_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_17_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497614253865</v>
+        <v>10.84497632556114</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907128098638</v>
+        <v>37.78907191872407</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.254714623756429</v>
+        <v>4.741841411512095</v>
       </c>
       <c r="C2" t="n">
-        <v>14.26872113352314</v>
+        <v>7.721445693901163</v>
       </c>
       <c r="D2" t="n">
-        <v>29.67528785626834</v>
+        <v>50.19872361354791</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.83835578616454</v>
+        <v>15.07964473723101</v>
       </c>
       <c r="C3" t="n">
-        <v>38.23907308041327</v>
+        <v>30.98395754602934</v>
       </c>
       <c r="D3" t="n">
-        <v>70.78891821471626</v>
+        <v>110.5938788834032</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.9818551819006</v>
+        <v>33.98712377332033</v>
       </c>
       <c r="C4" t="n">
-        <v>58.52983463178634</v>
+        <v>72.93894568701677</v>
       </c>
       <c r="D4" t="n">
-        <v>85.47193687943155</v>
+        <v>133.906459868448</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.3573658310084</v>
+        <v>45.33220024359647</v>
       </c>
       <c r="C5" t="n">
-        <v>110.127548723886</v>
+        <v>89.21632262342891</v>
       </c>
       <c r="D5" t="n">
-        <v>59.12575548826417</v>
+        <v>87.67006998924018</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>47.53720558733482</v>
+        <v>41.09694064747573</v>
       </c>
       <c r="C6" t="n">
-        <v>150.58144462508</v>
+        <v>111.5775900830585</v>
       </c>
       <c r="D6" t="n">
-        <v>42.74725853831463</v>
+        <v>52.1258943569844</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>33.41672835715293</v>
+        <v>26.76931465169778</v>
       </c>
       <c r="C7" t="n">
-        <v>148.2193596486622</v>
+        <v>106.4185058972415</v>
       </c>
       <c r="D7" t="n">
-        <v>38.08788393395925</v>
+        <v>39.34550274309942</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>16.6062624173348</v>
+        <v>13.4352173326176</v>
       </c>
       <c r="C8" t="n">
-        <v>99.47067739428682</v>
+        <v>74.35266238113219</v>
       </c>
       <c r="D8" t="n">
-        <v>35.63253292563798</v>
+        <v>35.88287859022092</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>7.987499321752047</v>
+        <v>6.878124415953151</v>
       </c>
       <c r="C9" t="n">
-        <v>52.36249555370786</v>
+        <v>42.71093387325747</v>
       </c>
       <c r="D9" t="n">
-        <v>33.39218466454675</v>
+        <v>34.16874709860598</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.551783267515713</v>
+        <v>5.267076433284139</v>
       </c>
       <c r="C10" t="n">
-        <v>31.8871654339364</v>
+        <v>30.60598467989432</v>
       </c>
       <c r="D10" t="n">
-        <v>34.73423377625215</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>4.442408361716816</v>
       </c>
       <c r="C11" t="n">
-        <v>28.96450251839364</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
-        <v>36.07235589714055</v>
+        <v>35.7169632282032</v>
       </c>
     </row>
     <row r="12">
@@ -923,10 +923,10 @@
         <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>27.33774657245668</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>34.71459882216721</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -951,7 +951,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>23.35381438862312</v>
+        <v>23.04652735719387</v>
       </c>
       <c r="D14" t="n">
         <v>30.42141611149592</v>
@@ -965,10 +965,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>20.42526098685489</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>29.02537087605695</v>
       </c>
     </row>
     <row r="16">
@@ -982,7 +982,7 @@
         <v>19.01252604044373</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -1007,10 +1007,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1021,10 +1021,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1035,7 +1035,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.651890743445948</v>
+        <v>7.661798412501951</v>
       </c>
       <c r="C21" t="n">
-        <v>92.77917526428212</v>
+        <v>92.89930575158614</v>
       </c>
       <c r="D21" t="n">
-        <v>7.651890743445948</v>
+        <v>7.661798412501951</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.58105577219387</v>
+        <v>5.16791991515521</v>
       </c>
       <c r="C2" t="n">
-        <v>9.346238144429634</v>
+        <v>12.0951317163207</v>
       </c>
       <c r="D2" t="n">
-        <v>23.44118993430109</v>
+        <v>50.32929605821273</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.12444527872787</v>
+        <v>15.29562923216531</v>
       </c>
       <c r="C3" t="n">
-        <v>46.48084505756524</v>
+        <v>30.29182541453534</v>
       </c>
       <c r="D3" t="n">
-        <v>76.07562960208534</v>
+        <v>121.3096550752571</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>35.54417563225577</v>
+        <v>31.01340997715674</v>
       </c>
       <c r="C4" t="n">
-        <v>76.15515116612933</v>
+        <v>74.22798042269284</v>
       </c>
       <c r="D4" t="n">
-        <v>97.18811398191299</v>
+        <v>152.1443869702409</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.98983233672161</v>
+        <v>47.66385104118265</v>
       </c>
       <c r="C5" t="n">
-        <v>107.8449853115121</v>
+        <v>110.3729856499477</v>
       </c>
       <c r="D5" t="n">
-        <v>73.48381566287377</v>
+        <v>111.0847527355266</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>55.74854338565514</v>
+        <v>50.39507315439728</v>
       </c>
       <c r="C6" t="n">
-        <v>160.6443585936099</v>
+        <v>124.4178683069026</v>
       </c>
       <c r="D6" t="n">
-        <v>49.54978838104078</v>
+        <v>64.12088780747193</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>43.5375654402333</v>
+        <v>36.4110588551057</v>
       </c>
       <c r="C7" t="n">
-        <v>180.7976754663884</v>
+        <v>132.0499749597172</v>
       </c>
       <c r="D7" t="n">
-        <v>41.44153409166636</v>
+        <v>44.55563780953724</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>25.11801501315464</v>
+        <v>20.19455027635689</v>
       </c>
       <c r="C8" t="n">
-        <v>142.4466831476909</v>
+        <v>103.9768993567797</v>
       </c>
       <c r="D8" t="n">
-        <v>37.30150402285756</v>
+        <v>37.71874679716245</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>11.87031149204818</v>
+        <v>9.873436661610169</v>
       </c>
       <c r="C9" t="n">
-        <v>84.42343033129593</v>
+        <v>65.23124446097505</v>
       </c>
       <c r="D9" t="n">
-        <v>34.94530953266521</v>
+        <v>35.61093447614454</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>6.548257187326225</v>
+        <v>5.836490101747287</v>
       </c>
       <c r="C10" t="n">
-        <v>44.98367980858886</v>
+        <v>39.43189654107314</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>35.3036474447153</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.797801030654161</v>
+        <v>4.620104696185489</v>
       </c>
       <c r="C11" t="n">
-        <v>32.87382187670443</v>
+        <v>32.16303653882975</v>
       </c>
       <c r="D11" t="n">
-        <v>36.60544490054656</v>
+        <v>36.25005223160922</v>
       </c>
     </row>
     <row r="12">
@@ -1234,10 +1234,10 @@
         <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
-        <v>29.72437524148068</v>
+        <v>30.15830772675777</v>
       </c>
       <c r="D12" t="n">
-        <v>34.93156506480576</v>
+        <v>35.36549755008285</v>
       </c>
     </row>
     <row r="13">
@@ -1248,10 +1248,10 @@
         <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>27.57729301229291</v>
+        <v>27.3171298706675</v>
       </c>
       <c r="D13" t="n">
-        <v>32.780555844801</v>
+        <v>33.04071898642641</v>
       </c>
     </row>
     <row r="14">
@@ -1293,7 +1293,7 @@
         <v>20.25247339090745</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -1318,10 +1318,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1346,7 +1346,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.822855652645925</v>
+        <v>7.834099524760994</v>
       </c>
       <c r="C21" t="n">
-        <v>100.7192665278163</v>
+        <v>100.8640313812978</v>
       </c>
       <c r="D21" t="n">
-        <v>8.800712609226666</v>
+        <v>8.813361965356119</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>8.096473316923445</v>
+        <v>6.959609475405639</v>
       </c>
       <c r="C2" t="n">
-        <v>15.6353139378347</v>
+        <v>7.229590094073512</v>
       </c>
       <c r="D2" t="n">
-        <v>25.51071409485337</v>
+        <v>50.3076976087193</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.34319509032566</v>
+        <v>15.78159434576748</v>
       </c>
       <c r="C3" t="n">
-        <v>41.50829293555515</v>
+        <v>37.57148464152544</v>
       </c>
       <c r="D3" t="n">
-        <v>76.13944320286139</v>
+        <v>129.1832716633165</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.93156506480576</v>
+        <v>29.36701907713484</v>
       </c>
       <c r="C4" t="n">
-        <v>92.28722944231292</v>
+        <v>74.58533658703867</v>
       </c>
       <c r="D4" t="n">
-        <v>108.7128502820663</v>
+        <v>171.0204500797944</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>52.69530802544756</v>
+        <v>46.82936549257286</v>
       </c>
       <c r="C5" t="n">
-        <v>120.1168316145973</v>
+        <v>120.0677442293849</v>
       </c>
       <c r="D5" t="n">
-        <v>85.78020565856507</v>
+        <v>131.0142311317369</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>61.78629176677302</v>
+        <v>55.74854338565514</v>
       </c>
       <c r="C6" t="n">
-        <v>165.6355639220006</v>
+        <v>144.3826896204657</v>
       </c>
       <c r="D6" t="n">
-        <v>58.40515267334701</v>
+        <v>79.13475544851842</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>52.64033015400972</v>
+        <v>45.6934833987593</v>
       </c>
       <c r="C7" t="n">
-        <v>201.1591228524672</v>
+        <v>152.7707420055504</v>
       </c>
       <c r="D7" t="n">
-        <v>44.67541102945535</v>
+        <v>50.12509253572939</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>34.13045893814036</v>
+        <v>27.87181732356695</v>
       </c>
       <c r="C8" t="n">
-        <v>181.750952487212</v>
+        <v>132.6832022289564</v>
       </c>
       <c r="D8" t="n">
-        <v>39.13737222979909</v>
+        <v>40.05530633326986</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>16.9734360587231</v>
+        <v>14.08906130364597</v>
       </c>
       <c r="C9" t="n">
-        <v>121.5874896755589</v>
+        <v>90.96874227550941</v>
       </c>
       <c r="D9" t="n">
-        <v>36.38749691020377</v>
+        <v>37.05312185368311</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.398851609831464</v>
+        <v>7.260024272905163</v>
       </c>
       <c r="C10" t="n">
-        <v>67.19081287865171</v>
+        <v>54.94841900669398</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>35.73070769606267</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>5.330890034060179</v>
+        <v>4.975497365122834</v>
       </c>
       <c r="C11" t="n">
-        <v>40.15937158992001</v>
+        <v>37.49392657288993</v>
       </c>
       <c r="D11" t="n">
-        <v>36.96083756948391</v>
+        <v>36.78314123501524</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>4.122358610132356</v>
+        <v>3.905392367493811</v>
       </c>
       <c r="C12" t="n">
         <v>32.76190263842031</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>35.58246379272139</v>
       </c>
     </row>
     <row r="13">
@@ -1562,7 +1562,7 @@
         <v>29.91876128692155</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>33.56104526967722</v>
       </c>
     </row>
     <row r="14">
@@ -1573,7 +1573,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>27.04125876577415</v>
+        <v>26.73397173434489</v>
       </c>
       <c r="D14" t="n">
         <v>30.42141611149592</v>
@@ -1604,7 +1604,7 @@
         <v>21.49242074137117</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -1629,10 +1629,10 @@
         <v>0.5350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -1657,7 +1657,7 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>18.82992096745382</v>
+        <v>19.50241814486288</v>
       </c>
       <c r="D20" t="n">
         <v>10.75995483854504</v>
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.977750720274644</v>
+        <v>7.989951275870022</v>
       </c>
       <c r="C21" t="n">
-        <v>107.6996347237077</v>
+        <v>107.8643422242453</v>
       </c>
       <c r="D21" t="n">
-        <v>9.972188400343304</v>
+        <v>9.987439094837528</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.467173038501239</v>
+        <v>6.299875018151782</v>
       </c>
       <c r="C2" t="n">
-        <v>10.88169155387165</v>
+        <v>5.031456984264903</v>
       </c>
       <c r="D2" t="n">
-        <v>21.13899156784232</v>
+        <v>41.48571273835746</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>24.72040719293469</v>
+        <v>19.43860454408685</v>
       </c>
       <c r="C3" t="n">
-        <v>63.30800070835556</v>
+        <v>51.94427103169874</v>
       </c>
       <c r="D3" t="n">
-        <v>82.28027509292518</v>
+        <v>138.0190010015378</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>25.30847406777853</v>
+        <v>22.48791291347744</v>
       </c>
       <c r="C4" t="n">
-        <v>108.6873248417559</v>
+        <v>100.0342005765245</v>
       </c>
       <c r="D4" t="n">
-        <v>101.7954559579433</v>
+        <v>158.7299505703286</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.80295611554943</v>
+        <v>31.39138284329177</v>
       </c>
       <c r="C5" t="n">
-        <v>98.96016858807852</v>
+        <v>86.27107951068848</v>
       </c>
       <c r="D5" t="n">
-        <v>57.94765824316799</v>
+        <v>82.49135084933826</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>32.68434456978482</v>
+        <v>28.37741739125406</v>
       </c>
       <c r="C6" t="n">
-        <v>132.4681994817264</v>
+        <v>100.588888029424</v>
       </c>
       <c r="D6" t="n">
-        <v>29.42396044398116</v>
+        <v>33.00635781677777</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.57725195456389</v>
+        <v>18.44507586738907</v>
       </c>
       <c r="C7" t="n">
-        <v>127.7980256526243</v>
+        <v>93.30333831620835</v>
       </c>
       <c r="D7" t="n">
-        <v>27.48795397120644</v>
+        <v>28.14670668075605</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.76624623539802</v>
+        <v>9.763480918734528</v>
       </c>
       <c r="C8" t="n">
-        <v>89.62374792069132</v>
+        <v>67.00918955336604</v>
       </c>
       <c r="D8" t="n">
-        <v>26.78698611037422</v>
+        <v>27.28767743954009</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.990624491314035</v>
+        <v>5.214062057254808</v>
       </c>
       <c r="C9" t="n">
-        <v>51.25312064790897</v>
+        <v>41.93437143919824</v>
       </c>
       <c r="D9" t="n">
-        <v>27.06874770149305</v>
+        <v>27.17968519207294</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.843542262126263</v>
+        <v>3.558835427894688</v>
       </c>
       <c r="C10" t="n">
-        <v>31.46010518258904</v>
+        <v>29.32480392585223</v>
       </c>
       <c r="D10" t="n">
-        <v>28.89774367450487</v>
+        <v>28.75539025738908</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.020837685967435</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
         <v>26.12136116689488</v>
       </c>
       <c r="D11" t="n">
-        <v>28.07602084605028</v>
+        <v>28.43141351498762</v>
       </c>
     </row>
     <row r="12">
@@ -1859,7 +1859,7 @@
         <v>24.30021917551705</v>
       </c>
       <c r="D12" t="n">
-        <v>27.12078032981814</v>
+        <v>27.33774657245668</v>
       </c>
     </row>
     <row r="13">
@@ -1870,7 +1870,7 @@
         <v>1.300815708127024</v>
       </c>
       <c r="C13" t="n">
-        <v>22.37403017978481</v>
+        <v>22.11386703815941</v>
       </c>
       <c r="D13" t="n">
         <v>25.23582473766426</v>
@@ -1901,7 +1901,7 @@
         <v>17.91689560250429</v>
       </c>
       <c r="D15" t="n">
-        <v>22.21695054710532</v>
+        <v>21.85861263505523</v>
       </c>
     </row>
     <row r="16">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>15.58328130950962</v>
+        <v>16.05550195525234</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>17.9443845382232</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>15.51652246562084</v>
+        <v>16.05157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>13.37631247036279</v>
+        <v>13.9113649691773</v>
       </c>
     </row>
     <row r="19">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.24890625298896</v>
+        <v>16.85071759569225</v>
       </c>
       <c r="D19" t="n">
         <v>9.027170140549421</v>
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.532729150507524</v>
+        <v>3.948589266480671</v>
       </c>
       <c r="C2" t="n">
-        <v>5.386849653202249</v>
+        <v>2.735149104031614</v>
       </c>
       <c r="D2" t="n">
-        <v>15.20727193878309</v>
+        <v>28.43043176728338</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>25.75615102091507</v>
+        <v>20.92104357749953</v>
       </c>
       <c r="C3" t="n">
-        <v>53.97158004096841</v>
+        <v>36.49156216685395</v>
       </c>
       <c r="D3" t="n">
-        <v>80.66530011943918</v>
+        <v>139.1725545540278</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.44658169890783</v>
+        <v>28.76717122984004</v>
       </c>
       <c r="C4" t="n">
-        <v>135.8208678917292</v>
+        <v>117.5957035100914</v>
       </c>
       <c r="D4" t="n">
-        <v>116.7916521403133</v>
+        <v>185.7613918590602</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.23907308041327</v>
+        <v>34.36116964863837</v>
       </c>
       <c r="C5" t="n">
-        <v>144.9550485320416</v>
+        <v>130.3760951239765</v>
       </c>
       <c r="D5" t="n">
-        <v>73.16474765899356</v>
+        <v>107.2068493037517</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.31957639216151</v>
+        <v>33.40887437551896</v>
       </c>
       <c r="C6" t="n">
-        <v>149.0116300459894</v>
+        <v>119.1046497315188</v>
       </c>
       <c r="D6" t="n">
-        <v>35.58246379272141</v>
+        <v>42.38499363544755</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>20.84054026575129</v>
+        <v>17.0676838383308</v>
       </c>
       <c r="C7" t="n">
-        <v>156.663371652889</v>
+        <v>115.8207036608132</v>
       </c>
       <c r="D7" t="n">
-        <v>29.8235317596096</v>
+        <v>30.72183090899544</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.680032363873551</v>
+        <v>8.17795837637593</v>
       </c>
       <c r="C8" t="n">
-        <v>115.5762484824558</v>
+        <v>86.20235717139117</v>
       </c>
       <c r="D8" t="n">
-        <v>27.53802310412303</v>
+        <v>28.03871443328891</v>
       </c>
     </row>
     <row r="9">
@@ -2122,10 +2122,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.659374604355361</v>
+        <v>4.215624642035802</v>
       </c>
       <c r="C9" t="n">
-        <v>55.24687030878498</v>
+        <v>45.81718360949438</v>
       </c>
       <c r="D9" t="n">
         <v>28.39999758845172</v>
@@ -2136,10 +2136,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.135301256736813</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>33.02599277086271</v>
+        <v>31.46010518258904</v>
       </c>
       <c r="D10" t="n">
         <v>29.60951076008381</v>
@@ -2156,7 +2156,7 @@
         <v>28.96450251839364</v>
       </c>
       <c r="D11" t="n">
-        <v>29.31989518733098</v>
+        <v>29.67528785626833</v>
       </c>
     </row>
     <row r="12">
@@ -2167,7 +2167,7 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>20.39482680802324</v>
+        <v>20.17786056538469</v>
       </c>
       <c r="D12" t="n">
         <v>28.20561154301086</v>
@@ -2198,7 +2198,7 @@
         <v>15.05706454003333</v>
       </c>
       <c r="D14" t="n">
-        <v>18.4372218857551</v>
+        <v>18.12993485432585</v>
       </c>
     </row>
     <row r="15">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.22610507161303</v>
+        <v>13.63942085510094</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>15.29268398905256</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.22217808079604</v>
+        <v>13.69439872653876</v>
       </c>
       <c r="D17" t="n">
-        <v>11.33329549782518</v>
+        <v>11.8055161435679</v>
       </c>
     </row>
     <row r="18">
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>13.9113649691773</v>
+        <v>14.44641746799181</v>
       </c>
       <c r="D18" t="n">
         <v>7.490734983403163</v>
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.396266219617217</v>
+        <v>3.659955441432109</v>
       </c>
       <c r="C2" t="n">
-        <v>6.180101798233672</v>
+        <v>5.14337622254904</v>
       </c>
       <c r="D2" t="n">
-        <v>19.08615711826224</v>
+        <v>29.11176467403067</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.59706683509808</v>
+        <v>17.16585860875548</v>
       </c>
       <c r="C3" t="n">
-        <v>37.19351177539041</v>
+        <v>23.33614292994668</v>
       </c>
       <c r="D3" t="n">
-        <v>74.61282552275759</v>
+        <v>130.2239242298182</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>41.30016242225481</v>
+        <v>33.97436105316512</v>
       </c>
       <c r="C4" t="n">
-        <v>135.1061555630376</v>
+        <v>104.4628644703819</v>
       </c>
       <c r="D4" t="n">
-        <v>128.4057274815531</v>
+        <v>208.8491526198325</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>44.17864669110647</v>
+        <v>38.38633523605029</v>
       </c>
       <c r="C5" t="n">
-        <v>194.3860454408685</v>
+        <v>170.8731879241574</v>
       </c>
       <c r="D5" t="n">
-        <v>94.19869222248147</v>
+        <v>142.3288734231814</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>44.11581483803468</v>
+        <v>38.96360288614742</v>
       </c>
       <c r="C6" t="n">
-        <v>187.371458094025</v>
+        <v>160.0405837554981</v>
       </c>
       <c r="D6" t="n">
-        <v>47.25544399621598</v>
+        <v>61.02151030516475</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>30.3625112492411</v>
+        <v>25.69135567243478</v>
       </c>
       <c r="C7" t="n">
-        <v>183.3129130846687</v>
+        <v>141.0329664535755</v>
       </c>
       <c r="D7" t="n">
-        <v>32.63820242768521</v>
+        <v>34.7941203862112</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.10280577150543</v>
+        <v>11.68279768053704</v>
       </c>
       <c r="C8" t="n">
-        <v>156.8832831386403</v>
+        <v>116.4107340310655</v>
       </c>
       <c r="D8" t="n">
-        <v>29.29044275620359</v>
+        <v>29.87458264023044</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.212499472473814</v>
+        <v>5.435937038414587</v>
       </c>
       <c r="C9" t="n">
-        <v>91.96717969072843</v>
+        <v>71.55468142402876</v>
       </c>
       <c r="D9" t="n">
-        <v>28.95468504135117</v>
+        <v>29.06562253193106</v>
       </c>
     </row>
     <row r="10">
@@ -2447,10 +2447,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.704714925199962</v>
+        <v>2.420008090968388</v>
       </c>
       <c r="C10" t="n">
-        <v>45.55309347705201</v>
+        <v>40.57072387799944</v>
       </c>
       <c r="D10" t="n">
         <v>30.17892442854695</v>
@@ -2464,10 +2464,10 @@
         <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>33.40691088011046</v>
+        <v>32.51842920776709</v>
       </c>
       <c r="D11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.852984190737</v>
       </c>
     </row>
     <row r="12">
@@ -2478,7 +2478,7 @@
         <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>24.30021917551705</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
         <v>28.8565102709265</v>
@@ -2509,7 +2509,7 @@
         <v>15.97892563432109</v>
       </c>
       <c r="D14" t="n">
-        <v>19.0517959486136</v>
+        <v>18.74450891718435</v>
       </c>
     </row>
     <row r="15">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.05273663858884</v>
+        <v>14.46605242207675</v>
       </c>
       <c r="D16" t="n">
-        <v>14.46605242207675</v>
+        <v>14.87936820556466</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.16661937228147</v>
+        <v>14.63884001802419</v>
       </c>
       <c r="D17" t="n">
-        <v>10.38885420633975</v>
+        <v>10.86107485208246</v>
       </c>
     </row>
     <row r="18">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.679189484889545</v>
+        <v>2.223658550119025</v>
       </c>
       <c r="C2" t="n">
-        <v>3.036545649235384</v>
+        <v>2.489712177969911</v>
       </c>
       <c r="D2" t="n">
-        <v>13.34587829153114</v>
+        <v>20.30254252382404</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.18964153783566</v>
+        <v>16.8222469122691</v>
       </c>
       <c r="C3" t="n">
-        <v>34.16482010778901</v>
+        <v>23.45886139297754</v>
       </c>
       <c r="D3" t="n">
-        <v>75.10369937488099</v>
+        <v>128.898564829085</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45.32041927114551</v>
+        <v>37.56068541677872</v>
       </c>
       <c r="C4" t="n">
-        <v>133.4597646630156</v>
+        <v>98.86003032224532</v>
       </c>
       <c r="D4" t="n">
-        <v>137.2630552692678</v>
+        <v>224.4324339293421</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.24031687002478</v>
+        <v>40.17802479630072</v>
       </c>
       <c r="C5" t="n">
-        <v>239.8409641474958</v>
+        <v>202.7309009269664</v>
       </c>
       <c r="D5" t="n">
-        <v>99.10743074371554</v>
+        <v>150.8455347575224</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>35.94472869558847</v>
+        <v>31.43654323768712</v>
       </c>
       <c r="C6" t="n">
-        <v>219.1300145787051</v>
+        <v>188.1764912115074</v>
       </c>
       <c r="D6" t="n">
-        <v>46.08814597586652</v>
+        <v>58.92842419971056</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.342311153612647</v>
+        <v>7.72537268471815</v>
       </c>
       <c r="C7" t="n">
-        <v>196.8472869354152</v>
+        <v>148.5187926984575</v>
       </c>
       <c r="D7" t="n">
-        <v>32.99752208743954</v>
+        <v>34.7941203862112</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.255876297909922</v>
+        <v>3.75518496874405</v>
       </c>
       <c r="C8" t="n">
-        <v>112.3217548428776</v>
+        <v>86.95339416514</v>
       </c>
       <c r="D8" t="n">
-        <v>30.95941385342316</v>
+        <v>31.37665662772806</v>
       </c>
     </row>
     <row r="9">
@@ -2744,10 +2744,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.885937339858122</v>
+        <v>1.664062358698343</v>
       </c>
       <c r="C9" t="n">
-        <v>34.72343455150543</v>
+        <v>30.95155987178918</v>
       </c>
       <c r="D9" t="n">
         <v>31.50624732468863</v>
@@ -2761,10 +2761,10 @@
         <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>26.1930287493049</v>
+        <v>25.48126166372597</v>
       </c>
       <c r="D10" t="n">
-        <v>23.06125357275758</v>
+        <v>23.34596040698915</v>
       </c>
     </row>
     <row r="11">
@@ -2775,7 +2775,7 @@
         <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>19.36890045708532</v>
+        <v>19.54659679155399</v>
       </c>
       <c r="D11" t="n">
         <v>23.10052348092744</v>
@@ -2806,7 +2806,7 @@
         <v>13.00815708127024</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>15.34962535589888</v>
       </c>
     </row>
     <row r="14">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>11.82515109765283</v>
+        <v>12.18348900970292</v>
       </c>
       <c r="D15" t="n">
-        <v>12.18348900970292</v>
+        <v>12.541826921753</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>11.98615772114931</v>
+        <v>12.39947350463721</v>
       </c>
       <c r="D16" t="n">
-        <v>8.679631453246051</v>
+        <v>9.092947236733956</v>
       </c>
     </row>
     <row r="17">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.034001316750144</v>
+        <v>2.747911824186823</v>
       </c>
       <c r="C2" t="n">
-        <v>2.805834938737384</v>
+        <v>7.549639845657972</v>
       </c>
       <c r="D2" t="n">
-        <v>12.81966152205485</v>
+        <v>15.78355784117597</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.01583113645496</v>
+        <v>12.4976482750619</v>
       </c>
       <c r="C3" t="n">
-        <v>23.2085157283946</v>
+        <v>16.71425466480195</v>
       </c>
       <c r="D3" t="n">
-        <v>69.10031216341176</v>
+        <v>116.9359690528376</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>42.02763747110171</v>
+        <v>34.90603962449534</v>
       </c>
       <c r="C4" t="n">
-        <v>110.5379192642611</v>
+        <v>79.71595008943251</v>
       </c>
       <c r="D4" t="n">
-        <v>141.9980244468501</v>
+        <v>234.6043218930433</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>55.14967728606459</v>
+        <v>46.90299657039137</v>
       </c>
       <c r="C5" t="n">
-        <v>244.4060909722435</v>
+        <v>194.9996377560228</v>
       </c>
       <c r="D5" t="n">
-        <v>119.8223073033232</v>
+        <v>186.679325962531</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.92713935237005</v>
+        <v>40.05039759474864</v>
       </c>
       <c r="C6" t="n">
-        <v>289.5704123584138</v>
+        <v>246.5413922289803</v>
       </c>
       <c r="D6" t="n">
-        <v>61.58503348740243</v>
+        <v>84.04545746516095</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>19.22360179685679</v>
+        <v>16.46881773874025</v>
       </c>
       <c r="C7" t="n">
-        <v>249.9667099690974</v>
+        <v>201.5783291221806</v>
       </c>
       <c r="D7" t="n">
-        <v>36.83026512481909</v>
+        <v>40.60312155223958</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.757950285407543</v>
+        <v>5.006913291658733</v>
       </c>
       <c r="C8" t="n">
-        <v>169.984706251814</v>
+        <v>129.7625028088221</v>
       </c>
       <c r="D8" t="n">
-        <v>32.54493639578176</v>
+        <v>33.12907627980861</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>1.996874830438012</v>
       </c>
       <c r="C9" t="n">
-        <v>70.44530651822986</v>
+        <v>57.46562012038278</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>32.39374724932775</v>
       </c>
     </row>
     <row r="10">
@@ -3072,10 +3072,10 @@
         <v>1.1388273369263</v>
       </c>
       <c r="C10" t="n">
-        <v>31.60245859970483</v>
+        <v>29.75186417719959</v>
       </c>
       <c r="D10" t="n">
-        <v>24.34243432679967</v>
+        <v>24.62714116103124</v>
       </c>
     </row>
     <row r="11">
@@ -3117,7 +3117,7 @@
         <v>14.82929907264807</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>15.34962535589888</v>
       </c>
     </row>
     <row r="14">
@@ -3131,7 +3131,7 @@
         <v>13.82791641431633</v>
       </c>
       <c r="D14" t="n">
-        <v>13.82791641431633</v>
+        <v>14.13520344574558</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.90016483380309</v>
+        <v>13.25850274585317</v>
       </c>
       <c r="D15" t="n">
-        <v>11.46681318560274</v>
+        <v>11.82515109765283</v>
       </c>
     </row>
     <row r="16">
@@ -3156,10 +3156,10 @@
         <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>23.55899965881071</v>
+        <v>23.97231544229862</v>
       </c>
       <c r="D16" t="n">
-        <v>7.852999886270235</v>
+        <v>8.266315669758143</v>
       </c>
     </row>
     <row r="17">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.870630287217673</v>
+        <v>1.884955592153876</v>
       </c>
       <c r="C2" t="n">
-        <v>1.98214861487431</v>
+        <v>3.980986940720816</v>
       </c>
       <c r="D2" t="n">
-        <v>9.309913479372502</v>
+        <v>11.59836737797182</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>14.53477476137403</v>
+        <v>11.29500733735955</v>
       </c>
       <c r="C3" t="n">
-        <v>18.07888397370501</v>
+        <v>22.60964962880404</v>
       </c>
       <c r="D3" t="n">
-        <v>64.88861451219293</v>
+        <v>106.499990956694</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.59897357724434</v>
+        <v>31.51115606320987</v>
       </c>
       <c r="C4" t="n">
-        <v>92.14683952060562</v>
+        <v>65.66419519854792</v>
       </c>
       <c r="D4" t="n">
-        <v>143.7337543879585</v>
+        <v>238.382087058985</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>59.81297888123694</v>
+        <v>50.56000676871075</v>
       </c>
       <c r="C5" t="n">
-        <v>235.6439927118407</v>
+        <v>184.0040634684585</v>
       </c>
       <c r="D5" t="n">
-        <v>134.6466976374501</v>
+        <v>212.4992905842222</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>52.81017250684443</v>
+        <v>45.72588107299945</v>
       </c>
       <c r="C6" t="n">
-        <v>333.9277371316932</v>
+        <v>278.1389420901639</v>
       </c>
       <c r="D6" t="n">
-        <v>72.41272891754049</v>
+        <v>101.7561860497734</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.00779722837174</v>
+        <v>14.73210604992764</v>
       </c>
       <c r="C7" t="n">
-        <v>307.7572885795859</v>
+        <v>252.5418341973368</v>
       </c>
       <c r="D7" t="n">
-        <v>40.90255460203486</v>
+        <v>46.17257627843174</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.589670517353839</v>
+        <v>4.005530633326986</v>
       </c>
       <c r="C8" t="n">
-        <v>212.4600206760522</v>
+        <v>164.3936530761284</v>
       </c>
       <c r="D8" t="n">
-        <v>33.79666471869644</v>
+        <v>34.38080460272329</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>1.553124868118454</v>
       </c>
       <c r="C9" t="n">
-        <v>77.32343093418301</v>
+        <v>63.23436963053704</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72812230584841</v>
+        <v>31.94999728700819</v>
       </c>
     </row>
     <row r="10">
@@ -3383,10 +3383,10 @@
         <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>31.74481201682062</v>
+        <v>30.60598467989432</v>
       </c>
       <c r="D10" t="n">
-        <v>25.19655482949439</v>
+        <v>25.33890824661018</v>
       </c>
     </row>
     <row r="11">
@@ -3414,7 +3414,7 @@
         <v>16.27246819789088</v>
       </c>
       <c r="D12" t="n">
-        <v>19.7439280801076</v>
+        <v>19.52696183746906</v>
       </c>
     </row>
     <row r="13">
@@ -3428,7 +3428,7 @@
         <v>11.44717823151781</v>
       </c>
       <c r="D13" t="n">
-        <v>15.60978849752428</v>
+        <v>15.86995163914969</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.06233313145306</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3453,10 +3453,10 @@
         <v>1.075013736150257</v>
       </c>
       <c r="C15" t="n">
-        <v>19.70858516275472</v>
+        <v>20.0669230748048</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>6.808420328951629</v>
       </c>
     </row>
     <row r="16">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.569634652641403</v>
+        <v>2.48382169174443</v>
       </c>
       <c r="C2" t="n">
-        <v>10.68534201302228</v>
+        <v>5.272966919509619</v>
       </c>
       <c r="D2" t="n">
-        <v>10.69712298547324</v>
+        <v>15.27010379185489</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.18839774822415</v>
+        <v>8.98790023237955</v>
       </c>
       <c r="C3" t="n">
-        <v>13.39594742444773</v>
+        <v>19.43369580556561</v>
       </c>
       <c r="D3" t="n">
-        <v>58.78214379177777</v>
+        <v>94.88100687693299</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.72361447795468</v>
+        <v>26.75066144531709</v>
       </c>
       <c r="C4" t="n">
-        <v>72.02002983584177</v>
+        <v>61.51631114810513</v>
       </c>
       <c r="D4" t="n">
-        <v>142.7127367755419</v>
+        <v>234.0172367659037</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>58.92940594741481</v>
+        <v>49.21010367537139</v>
       </c>
       <c r="C5" t="n">
-        <v>208.2777754559609</v>
+        <v>157.987749305918</v>
       </c>
       <c r="D5" t="n">
-        <v>146.9430876331414</v>
+        <v>239.0801096767046</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>61.86679507852126</v>
+        <v>53.81646390369741</v>
       </c>
       <c r="C6" t="n">
-        <v>350.3906643842079</v>
+        <v>284.4987037182747</v>
       </c>
       <c r="D6" t="n">
-        <v>90.00270253453061</v>
+        <v>131.2203981496287</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>31.68001666834032</v>
+        <v>27.30829414132927</v>
       </c>
       <c r="C7" t="n">
-        <v>374.2913122440964</v>
+        <v>309.3143404385213</v>
       </c>
       <c r="D7" t="n">
-        <v>48.32849423695774</v>
+        <v>58.03012505032471</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.428304040958867</v>
+        <v>7.510369937488099</v>
       </c>
       <c r="C8" t="n">
-        <v>286.4788888377404</v>
+        <v>226.7297235572796</v>
       </c>
       <c r="D8" t="n">
-        <v>35.88287859022092</v>
+        <v>37.21805546799658</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.32968730217768</v>
+        <v>2.107812321017901</v>
       </c>
       <c r="C9" t="n">
-        <v>139.559363149501</v>
+        <v>112.490615448008</v>
       </c>
       <c r="D9" t="n">
-        <v>32.61562223048752</v>
+        <v>32.9484347022272</v>
       </c>
     </row>
     <row r="10">
@@ -3694,10 +3694,10 @@
         <v>0.5694136684631501</v>
       </c>
       <c r="C10" t="n">
-        <v>51.38958357879929</v>
+        <v>45.12603322570465</v>
       </c>
       <c r="D10" t="n">
-        <v>26.47773558353648</v>
+        <v>26.62008900065227</v>
       </c>
     </row>
     <row r="11">
@@ -3708,7 +3708,7 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>26.65445017030089</v>
+        <v>26.83214650476957</v>
       </c>
       <c r="D11" t="n">
         <v>24.16670148773948</v>
@@ -3725,7 +3725,7 @@
         <v>18.87606310955342</v>
       </c>
       <c r="D12" t="n">
-        <v>20.17786056538469</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -3739,7 +3739,7 @@
         <v>13.00815708127024</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>16.1301147807751</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.36962016288231</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="D14" t="n">
-        <v>10.75504610002381</v>
+        <v>11.06233313145306</v>
       </c>
     </row>
     <row r="15">
@@ -3764,10 +3764,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>20.78359889890498</v>
+        <v>21.14193681095506</v>
       </c>
       <c r="D15" t="n">
-        <v>6.091744504851459</v>
+        <v>6.450082416901544</v>
       </c>
     </row>
     <row r="16">
@@ -3778,7 +3778,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
         <v>2.89321048441535</v>
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.320892630568465</v>
+        <v>4.66919208139783</v>
       </c>
       <c r="C2" t="n">
-        <v>12.00775617064274</v>
+        <v>8.185812358009905</v>
       </c>
       <c r="D2" t="n">
-        <v>5.285729639664827</v>
+        <v>7.954119899807657</v>
       </c>
     </row>
     <row r="3">
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.610467145592269</v>
+        <v>1.815251505152352</v>
       </c>
       <c r="C2" t="n">
-        <v>6.325400458462199</v>
+        <v>3.079742548222244</v>
       </c>
       <c r="D2" t="n">
-        <v>7.959028638328891</v>
+        <v>11.36176618124834</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.85031668506475</v>
+        <v>11.96750451476862</v>
       </c>
       <c r="C3" t="n">
-        <v>23.2085157283946</v>
+        <v>22.66855449105885</v>
       </c>
       <c r="D3" t="n">
-        <v>63.63688618927824</v>
+        <v>102.2735670899115</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>45.02687670757571</v>
+        <v>37.30543101367455</v>
       </c>
       <c r="C4" t="n">
-        <v>107.5003918673215</v>
+        <v>90.23243149732434</v>
       </c>
       <c r="D4" t="n">
-        <v>144.3718903957189</v>
+        <v>236.5187299163246</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.39200473809752</v>
+        <v>30.75324683553134</v>
       </c>
       <c r="C5" t="n">
-        <v>301.6419821298325</v>
+        <v>239.4973524510094</v>
       </c>
       <c r="D5" t="n">
-        <v>133.2231634662922</v>
+        <v>212.1065915025234</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>19.64280806657019</v>
+        <v>16.9459471230042</v>
       </c>
       <c r="C6" t="n">
-        <v>308.3276839957533</v>
+        <v>253.9074452539441</v>
       </c>
       <c r="D6" t="n">
-        <v>71.20517924131691</v>
+        <v>96.24170919501908</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.569454726192155</v>
+        <v>4.970588626601601</v>
       </c>
       <c r="C7" t="n">
-        <v>201.4585559022625</v>
+        <v>159.4181557110055</v>
       </c>
       <c r="D7" t="n">
-        <v>30.9014907388726</v>
+        <v>33.53650157707104</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.585522542358599</v>
+        <v>1.418625432636641</v>
       </c>
       <c r="C8" t="n">
-        <v>102.808619588726</v>
+        <v>82.86441497695203</v>
       </c>
       <c r="D8" t="n">
-        <v>24.03318379996192</v>
+        <v>24.28352946454485</v>
       </c>
     </row>
     <row r="9">
@@ -4302,10 +4302,10 @@
         <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>39.160934174701</v>
+        <v>34.39062207976576</v>
       </c>
       <c r="D9" t="n">
-        <v>20.1906232855399</v>
+        <v>20.30156077611979</v>
       </c>
     </row>
     <row r="10">
@@ -4333,7 +4333,7 @@
         <v>15.10418842983717</v>
       </c>
       <c r="D11" t="n">
-        <v>16.17036643664921</v>
+        <v>15.99267010218054</v>
       </c>
     </row>
     <row r="12">
@@ -4347,7 +4347,7 @@
         <v>10.63134588928871</v>
       </c>
       <c r="D12" t="n">
-        <v>12.80100831567416</v>
+        <v>13.0179745583127</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.365873098514571</v>
+        <v>9.626036240139976</v>
       </c>
       <c r="D13" t="n">
-        <v>8.845546815263763</v>
+        <v>9.105709956889166</v>
       </c>
     </row>
     <row r="14">
@@ -4372,10 +4372,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
-        <v>4.916592502868027</v>
+        <v>5.223879534297279</v>
       </c>
     </row>
     <row r="15">
@@ -4386,7 +4386,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.21695054710532</v>
+        <v>22.57528845915541</v>
       </c>
       <c r="D15" t="n">
         <v>2.150027472300515</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>7.176575718044184</v>
+        <v>6.10352547730242</v>
       </c>
       <c r="C2" t="n">
-        <v>9.483682823024189</v>
+        <v>5.431028299893355</v>
       </c>
       <c r="D2" t="n">
-        <v>15.67065685518759</v>
+        <v>24.16179274921825</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.54597489674824</v>
+        <v>9.925469289935252</v>
       </c>
       <c r="C3" t="n">
-        <v>30.25746424488669</v>
+        <v>20.62651926622549</v>
       </c>
       <c r="D3" t="n">
-        <v>7.574183538264141</v>
+        <v>9.817477042468104</v>
       </c>
     </row>
     <row r="4">
@@ -4543,7 +4543,7 @@
         <v>1.008254892261474</v>
       </c>
       <c r="C4" t="n">
-        <v>1.493238258159399</v>
+        <v>1.454950097693773</v>
       </c>
       <c r="D4" t="n">
         <v>19.62906359871073</v>
@@ -4554,10 +4554,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.736932672990861</v>
+        <v>4.68784528777852</v>
       </c>
       <c r="C5" t="n">
-        <v>9.35114688295087</v>
+        <v>9.424777960769381</v>
       </c>
       <c r="D5" t="n">
         <v>28.49522711576368</v>
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.050331174823848</v>
+        <v>8.130834486572086</v>
       </c>
       <c r="C6" t="n">
         <v>18.47551004622073</v>
       </c>
       <c r="D6" t="n">
-        <v>32.8453511932813</v>
+        <v>32.52333794628834</v>
       </c>
     </row>
     <row r="7">
@@ -4588,7 +4588,7 @@
         <v>20.9603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>32.21899615797182</v>
+        <v>32.69808903764427</v>
       </c>
     </row>
     <row r="8">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.397776363799</v>
+        <v>13.39842973255469</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14129978694773</v>
+        <v>70.14472036455103</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576208983976353</v>
+        <v>1.576285850888787</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.252751128347935</v>
+        <v>5.455571992499525</v>
       </c>
       <c r="C2" t="n">
-        <v>3.956443248114646</v>
+        <v>5.866924280578939</v>
       </c>
       <c r="D2" t="n">
-        <v>18.04157756094363</v>
+        <v>30.45970427196154</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.12721059539136</v>
+        <v>16.5915362017711</v>
       </c>
       <c r="C3" t="n">
-        <v>34.46425315758428</v>
+        <v>20.97013096271187</v>
       </c>
       <c r="D3" t="n">
-        <v>18.90355204527233</v>
+        <v>27.73928138349363</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>17.99543541884404</v>
+        <v>11.63960078155018</v>
       </c>
       <c r="C4" t="n">
-        <v>46.64774216728719</v>
+        <v>31.97061398879738</v>
       </c>
       <c r="D4" t="n">
-        <v>19.04197847157113</v>
+        <v>20.21614872585032</v>
       </c>
     </row>
     <row r="5">
@@ -4865,10 +4865,10 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.067961575771283</v>
+        <v>3.043417883165113</v>
       </c>
       <c r="C5" t="n">
-        <v>5.473243451175969</v>
+        <v>5.375068680751288</v>
       </c>
       <c r="D5" t="n">
         <v>29.40334374219198</v>
@@ -4882,10 +4882,10 @@
         <v>7.446556336712058</v>
       </c>
       <c r="C6" t="n">
-        <v>16.34217228489241</v>
+        <v>16.54343056426301</v>
       </c>
       <c r="D6" t="n">
-        <v>34.57617239586842</v>
+        <v>34.3346624606237</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.521970983489814</v>
       </c>
       <c r="C7" t="n">
         <v>24.49362347325367</v>
       </c>
       <c r="D7" t="n">
-        <v>34.97378021608837</v>
+        <v>35.27321326588365</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.513135254151592</v>
+        <v>9.596583809012571</v>
       </c>
       <c r="C8" t="n">
         <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>36.63391558396972</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -4952,7 +4952,7 @@
         <v>7.640942382152923</v>
       </c>
       <c r="C11" t="n">
-        <v>29.49759152179966</v>
+        <v>29.14219885286231</v>
       </c>
       <c r="D11" t="n">
         <v>47.97801030654161</v>
@@ -4966,7 +4966,7 @@
         <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>28.8565102709265</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
         <v>44.69504598354028</v>
@@ -5005,7 +5005,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>5.0167307687012</v>
       </c>
       <c r="C15" t="n">
         <v>26.51700549170635</v>
@@ -5025,7 +5025,7 @@
         <v>29.34542062764141</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>40.5049467818149</v>
       </c>
     </row>
     <row r="17">
@@ -5036,10 +5036,10 @@
         <v>5.66664774891259</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>31.63878326476196</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>36.83321036793183</v>
       </c>
     </row>
     <row r="18">
@@ -5050,7 +5050,7 @@
         <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>31.56809743005619</v>
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.43768895154831</v>
+        <v>15.44022153104499</v>
       </c>
       <c r="C21" t="n">
-        <v>86.12605415074323</v>
+        <v>86.14018327846154</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250039779273329</v>
+        <v>3.250572953904209</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.021058670145687</v>
+        <v>6.378414834491527</v>
       </c>
       <c r="C2" t="n">
-        <v>10.29755166984479</v>
+        <v>5.825690877000572</v>
       </c>
       <c r="D2" t="n">
-        <v>18.49612674800991</v>
+        <v>39.55854199492097</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.61317570899353</v>
+        <v>17.90216938694059</v>
       </c>
       <c r="C3" t="n">
-        <v>23.07107104980004</v>
+        <v>22.3003991019663</v>
       </c>
       <c r="D3" t="n">
-        <v>28.9468310597172</v>
+        <v>45.67090320156162</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>30.57947749187965</v>
+        <v>23.25367612278995</v>
       </c>
       <c r="C4" t="n">
-        <v>69.59511300635214</v>
+        <v>43.54640116957152</v>
       </c>
       <c r="D4" t="n">
-        <v>24.23640557474101</v>
+        <v>29.55845987946297</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>15.41343895667493</v>
+        <v>10.4801567428347</v>
       </c>
       <c r="C5" t="n">
-        <v>50.58455046131692</v>
+        <v>35.95650966803944</v>
       </c>
       <c r="D5" t="n">
-        <v>29.52606220522283</v>
+        <v>29.94330497952772</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.916993413495527</v>
+        <v>5.957245069369646</v>
       </c>
       <c r="C6" t="n">
         <v>12.23650338573225</v>
       </c>
       <c r="D6" t="n">
-        <v>36.54850353370026</v>
+        <v>36.34724525432967</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.581857593448868</v>
+        <v>9.462084373530759</v>
       </c>
       <c r="C7" t="n">
-        <v>24.37385025333556</v>
+        <v>24.25407703341745</v>
       </c>
       <c r="D7" t="n">
-        <v>37.4890178343687</v>
+        <v>37.66867766424586</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.34762080276138</v>
+        <v>10.43106935762236</v>
       </c>
       <c r="C8" t="n">
-        <v>29.54078842078653</v>
+        <v>29.87458264023044</v>
       </c>
       <c r="D8" t="n">
-        <v>37.88564390688441</v>
+        <v>38.05254101660637</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.09531164276995</v>
+        <v>9.984374152190059</v>
       </c>
       <c r="C9" t="n">
         <v>29.7312474754104</v>
       </c>
       <c r="D9" t="n">
-        <v>41.15780900513902</v>
+        <v>41.26874649571891</v>
       </c>
     </row>
     <row r="10">
@@ -5260,10 +5260,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.351727720027615</v>
+        <v>8.174031385558941</v>
       </c>
       <c r="C11" t="n">
-        <v>31.45225120095506</v>
+        <v>30.91916219754903</v>
       </c>
       <c r="D11" t="n">
         <v>49.75497365122833</v>
@@ -5277,7 +5277,7 @@
         <v>6.725953521794898</v>
       </c>
       <c r="C12" t="n">
-        <v>31.46010518258904</v>
+        <v>31.89403766786613</v>
       </c>
       <c r="D12" t="n">
         <v>46.2138096820101</v>
@@ -5291,7 +5291,7 @@
         <v>5.463425974133501</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>30.17892442854696</v>
       </c>
       <c r="D13" t="n">
         <v>45.00822350119503</v>
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>4.658392856651115</v>
       </c>
       <c r="C15" t="n">
-        <v>27.5920192278566</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>43.00054944601029</v>
       </c>
     </row>
     <row r="16">
@@ -5333,7 +5333,7 @@
         <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>29.75873641112932</v>
       </c>
       <c r="D16" t="n">
         <v>40.91826256530281</v>
@@ -5347,10 +5347,10 @@
         <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>32.11100391050468</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.72502612706146</v>
+        <v>16.73061019424582</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0226593750749</v>
+        <v>102.0567221848995</v>
       </c>
       <c r="D21" t="n">
-        <v>4.181256531765364</v>
+        <v>4.182652548561456</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.893431468593603</v>
+        <v>5.879687000734148</v>
       </c>
       <c r="C2" t="n">
-        <v>5.913066422678538</v>
+        <v>5.093307089632453</v>
       </c>
       <c r="D2" t="n">
-        <v>27.67939477353457</v>
+        <v>41.4150269036517</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.01921834792421</v>
+        <v>19.96874830438012</v>
       </c>
       <c r="C3" t="n">
-        <v>32.61856747360027</v>
+        <v>22.44766125760332</v>
       </c>
       <c r="D3" t="n">
-        <v>36.56519324467245</v>
+        <v>65.5758379051657</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>36.60348140513808</v>
+        <v>29.13729011434109</v>
       </c>
       <c r="C4" t="n">
-        <v>63.06060028688537</v>
+        <v>49.83842220608933</v>
       </c>
       <c r="D4" t="n">
-        <v>32.80019079888594</v>
+        <v>44.92477494633405</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.13965452037709</v>
+        <v>22.65382827549515</v>
       </c>
       <c r="C5" t="n">
-        <v>91.40071126537806</v>
+        <v>59.96024103687396</v>
       </c>
       <c r="D5" t="n">
-        <v>31.29320807286709</v>
+        <v>33.37942194439156</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>13.20254312671111</v>
+        <v>9.982410656781569</v>
       </c>
       <c r="C6" t="n">
-        <v>47.37619896383834</v>
+        <v>35.42145716922493</v>
       </c>
       <c r="D6" t="n">
-        <v>38.07806645691679</v>
+        <v>38.03781480104267</v>
       </c>
     </row>
     <row r="7">
@@ -5518,10 +5518,10 @@
         <v>8.683558444063037</v>
       </c>
       <c r="C7" t="n">
-        <v>21.31963314542373</v>
+        <v>21.02020009562846</v>
       </c>
       <c r="D7" t="n">
-        <v>39.88448223273092</v>
+        <v>39.64493579289469</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.76486357706628</v>
+        <v>10.6814150222053</v>
       </c>
       <c r="C8" t="n">
-        <v>31.29320807286708</v>
+        <v>31.71045084717197</v>
       </c>
       <c r="D8" t="n">
-        <v>39.30426933952106</v>
+        <v>40.05530633326986</v>
       </c>
     </row>
     <row r="9">
@@ -5546,10 +5546,10 @@
         <v>10.76093658624928</v>
       </c>
       <c r="C9" t="n">
-        <v>34.05780960802609</v>
+        <v>34.27968458918587</v>
       </c>
       <c r="D9" t="n">
-        <v>42.15624642035802</v>
+        <v>42.26718391093791</v>
       </c>
     </row>
     <row r="10">
@@ -5557,7 +5557,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.964739198105127</v>
+        <v>9.82238578098934</v>
       </c>
       <c r="C10" t="n">
         <v>33.16834618797849</v>
@@ -5571,10 +5571,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.884816723433632</v>
+        <v>8.707120388964958</v>
       </c>
       <c r="C11" t="n">
-        <v>33.93999988351647</v>
+        <v>33.58460721457913</v>
       </c>
       <c r="D11" t="n">
         <v>50.82115165804038</v>
@@ -5585,10 +5585,10 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.159886007071988</v>
+        <v>7.376852249710534</v>
       </c>
       <c r="C12" t="n">
-        <v>34.28066633689012</v>
+        <v>33.84673385161303</v>
       </c>
       <c r="D12" t="n">
         <v>47.08167465256428</v>
@@ -5602,7 +5602,7 @@
         <v>5.723589115758904</v>
       </c>
       <c r="C13" t="n">
-        <v>32.5203927031756</v>
+        <v>33.30088212805181</v>
       </c>
       <c r="D13" t="n">
         <v>45.78871292607123</v>
@@ -5630,10 +5630,10 @@
         <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>29.38370878810703</v>
+        <v>28.66703296400686</v>
       </c>
       <c r="D15" t="n">
-        <v>43.71722527011046</v>
+        <v>43.00054944601029</v>
       </c>
     </row>
     <row r="16">
@@ -5644,7 +5644,7 @@
         <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>30.17205219461722</v>
       </c>
       <c r="D16" t="n">
         <v>41.33157834879071</v>
@@ -5661,7 +5661,7 @@
         <v>32.58322455624739</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>37.30543101367455</v>
       </c>
     </row>
     <row r="18">
@@ -5672,7 +5672,7 @@
         <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>35.31346492175777</v>
+        <v>34.77841242294325</v>
       </c>
       <c r="D18" t="n">
         <v>32.1031499288707</v>
@@ -5686,10 +5686,10 @@
         <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>37.31230324760427</v>
       </c>
       <c r="D19" t="n">
-        <v>25.27607639353838</v>
+        <v>24.67426505083508</v>
       </c>
     </row>
     <row r="20">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.04007890562052</v>
+        <v>18.04964374960438</v>
       </c>
       <c r="C21" t="n">
-        <v>117.6900385747625</v>
+        <v>117.7524377950381</v>
       </c>
       <c r="D21" t="n">
-        <v>6.01335963520684</v>
+        <v>6.016547916534793</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.705336820005715</v>
+        <v>5.701008918561228</v>
       </c>
       <c r="C2" t="n">
-        <v>5.830599615521806</v>
+        <v>6.66999390265283</v>
       </c>
       <c r="D2" t="n">
-        <v>29.71455776443821</v>
+        <v>38.55814108429347</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>18.19669369821463</v>
+        <v>17.76472470834603</v>
       </c>
       <c r="C3" t="n">
-        <v>25.4861704022472</v>
+        <v>19.63986282345744</v>
       </c>
       <c r="D3" t="n">
-        <v>46.85881792370026</v>
+        <v>77.58261232810419</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>27.9631198600619</v>
+        <v>24.74691438094935</v>
       </c>
       <c r="C4" t="n">
-        <v>61.22276858453534</v>
+        <v>44.17177445717674</v>
       </c>
       <c r="D4" t="n">
-        <v>36.80768492762142</v>
+        <v>58.04485126588842</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>26.06540154775282</v>
+        <v>20.17491532227196</v>
       </c>
       <c r="C5" t="n">
-        <v>77.63169971331654</v>
+        <v>57.33406592801374</v>
       </c>
       <c r="D5" t="n">
-        <v>29.01064466049325</v>
+        <v>33.35487825178539</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>14.49059611468292</v>
+        <v>11.10945702125691</v>
       </c>
       <c r="C6" t="n">
-        <v>64.96617258082844</v>
+        <v>44.75984133202059</v>
       </c>
       <c r="D6" t="n">
-        <v>30.26924521733767</v>
+        <v>31.11452999069417</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>6.048547605864599</v>
+        <v>5.150248456478767</v>
       </c>
       <c r="C7" t="n">
-        <v>28.62579956042849</v>
+        <v>22.99645822427728</v>
       </c>
       <c r="D7" t="n">
-        <v>31.26081039862693</v>
+        <v>30.78171751895449</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.840016181936775</v>
+        <v>4.756567627075796</v>
       </c>
       <c r="C8" t="n">
-        <v>18.44213062427633</v>
+        <v>18.60902773399829</v>
       </c>
       <c r="D8" t="n">
-        <v>29.37389131106456</v>
+        <v>30.12492830481337</v>
       </c>
     </row>
     <row r="9">
@@ -5860,7 +5860,7 @@
         <v>21.85468564423824</v>
       </c>
       <c r="D9" t="n">
-        <v>30.17499743772996</v>
+        <v>30.39687241888974</v>
       </c>
     </row>
     <row r="10">
@@ -5868,10 +5868,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.412955930589413</v>
+        <v>4.270602513473626</v>
       </c>
       <c r="C10" t="n">
-        <v>21.06830573313655</v>
+        <v>21.49536598448391</v>
       </c>
       <c r="D10" t="n">
         <v>33.16834618797849</v>
@@ -5885,7 +5885,7 @@
         <v>3.731623023842126</v>
       </c>
       <c r="C11" t="n">
-        <v>20.43507846389736</v>
+        <v>20.07968579496001</v>
       </c>
       <c r="D11" t="n">
         <v>34.65078522139116</v>
@@ -5896,7 +5896,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.820561154301086</v>
+        <v>3.037527396939631</v>
       </c>
       <c r="C12" t="n">
         <v>19.7439280801076</v>
@@ -5927,7 +5927,7 @@
         <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>17.20807376003809</v>
+        <v>17.51536079146734</v>
       </c>
       <c r="D14" t="n">
         <v>29.49955501720816</v>
@@ -5944,7 +5944,7 @@
         <v>16.12520604225386</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>27.95035713990669</v>
       </c>
     </row>
     <row r="16">
@@ -5958,7 +5958,7 @@
         <v>15.70599977254047</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -5972,7 +5972,7 @@
         <v>16.52772260099505</v>
       </c>
       <c r="D17" t="n">
-        <v>23.13881164139307</v>
+        <v>23.61103228713579</v>
       </c>
     </row>
     <row r="18">
@@ -5983,7 +5983,7 @@
         <v>1.070104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>17.12167996206437</v>
       </c>
       <c r="D18" t="n">
         <v>20.33199495495144</v>
@@ -5997,7 +5997,7 @@
         <v>1.203622685406589</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>15.64709491028566</v>
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.04513808457749</v>
+        <v>7.051075727734198</v>
       </c>
       <c r="C21" t="n">
-        <v>66.04816954291397</v>
+        <v>66.1038349475081</v>
       </c>
       <c r="D21" t="n">
-        <v>4.403211302860931</v>
+        <v>4.406922329833874</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.368196446821559</v>
+        <v>4.775220833456485</v>
       </c>
       <c r="C2" t="n">
-        <v>5.693154936927254</v>
+        <v>11.31562403914874</v>
       </c>
       <c r="D2" t="n">
-        <v>25.64423178263093</v>
+        <v>43.23518714732528</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>21.38737373701677</v>
+        <v>19.11953654020664</v>
       </c>
       <c r="C3" t="n">
-        <v>23.75338570425158</v>
+        <v>23.70429831903924</v>
       </c>
       <c r="D3" t="n">
-        <v>60.49529353568845</v>
+        <v>91.22399667861362</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>32.86400439966198</v>
+        <v>31.00064725700153</v>
       </c>
       <c r="C4" t="n">
-        <v>62.9457358054885</v>
+        <v>47.34969177582366</v>
       </c>
       <c r="D4" t="n">
-        <v>52.82489872240812</v>
+        <v>85.24220791663781</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>35.41654843070369</v>
+        <v>29.77149913128453</v>
       </c>
       <c r="C5" t="n">
-        <v>99.10743074371554</v>
+        <v>71.47123286916781</v>
       </c>
       <c r="D5" t="n">
-        <v>35.85833489761475</v>
+        <v>47.02571503342222</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>26.04282135055514</v>
+        <v>20.40758952817845</v>
       </c>
       <c r="C6" t="n">
-        <v>98.89831848271095</v>
+        <v>72.09071567054754</v>
       </c>
       <c r="D6" t="n">
-        <v>33.12711278440013</v>
+        <v>35.17994723398021</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>12.39652826152447</v>
+        <v>9.761517423326035</v>
       </c>
       <c r="C7" t="n">
-        <v>65.63572451512475</v>
+        <v>47.31042186765379</v>
       </c>
       <c r="D7" t="n">
-        <v>33.47661496711198</v>
+        <v>32.99752208743954</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>6.00829594999048</v>
+        <v>5.424156065963627</v>
       </c>
       <c r="C8" t="n">
-        <v>29.95803119509142</v>
+        <v>25.78560345204247</v>
       </c>
       <c r="D8" t="n">
-        <v>31.2097595180061</v>
+        <v>32.12769362147687</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>5.103124566674919</v>
       </c>
       <c r="C9" t="n">
-        <v>23.18593553119691</v>
+        <v>23.2968730217768</v>
       </c>
       <c r="D9" t="n">
-        <v>31.39530983410874</v>
+        <v>31.72812230584841</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.840016181936776</v>
+        <v>4.697662764820988</v>
       </c>
       <c r="C10" t="n">
-        <v>24.48478774391545</v>
+        <v>24.62714116103124</v>
       </c>
       <c r="D10" t="n">
-        <v>33.31069960509428</v>
+        <v>33.45305302221006</v>
       </c>
     </row>
     <row r="11">
@@ -6196,7 +6196,7 @@
         <v>4.08701569277947</v>
       </c>
       <c r="C11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.27821981539612</v>
       </c>
       <c r="D11" t="n">
         <v>35.36157055926586</v>
@@ -6210,7 +6210,7 @@
         <v>3.254493639578176</v>
       </c>
       <c r="C12" t="n">
-        <v>22.1305567491316</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
         <v>33.1958351236974</v>
@@ -6221,10 +6221,10 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>20.81305133003238</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="D13" t="n">
         <v>30.95941385342317</v>
@@ -6238,7 +6238,7 @@
         <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>19.0517959486136</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
         <v>30.11412908006666</v>
@@ -6255,7 +6255,7 @@
         <v>17.5585576904542</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>28.30869505195678</v>
       </c>
     </row>
     <row r="16">
@@ -6269,7 +6269,7 @@
         <v>16.53263133951629</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -6283,7 +6283,7 @@
         <v>16.99994324673777</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -6297,7 +6297,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6308,7 +6308,7 @@
         <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
         <v>15.64709491028566</v>
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.261553477705645</v>
+        <v>7.269068920302517</v>
       </c>
       <c r="C21" t="n">
-        <v>75.33861733119608</v>
+        <v>75.41659004813862</v>
       </c>
       <c r="D21" t="n">
-        <v>5.446165108279234</v>
+        <v>5.451801690226888</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.773257338047992</v>
+        <v>3.788564390688441</v>
       </c>
       <c r="C2" t="n">
-        <v>13.18879865885165</v>
+        <v>6.947828502954677</v>
       </c>
       <c r="D2" t="n">
-        <v>25.58434517267188</v>
+        <v>40.13090090649687</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.78221624057323</v>
+        <v>17.63709750679395</v>
       </c>
       <c r="C3" t="n">
-        <v>22.78145547704723</v>
+        <v>36.03504948437918</v>
       </c>
       <c r="D3" t="n">
-        <v>66.5281331782851</v>
+        <v>103.7903672929728</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.85422798034851</v>
+        <v>34.58697162061513</v>
       </c>
       <c r="C4" t="n">
-        <v>60.38042905429158</v>
+        <v>53.71828913327272</v>
       </c>
       <c r="D4" t="n">
-        <v>69.76102836836986</v>
+        <v>109.5424270921549</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>42.7551125199486</v>
+        <v>38.48451000647497</v>
       </c>
       <c r="C5" t="n">
-        <v>108.826733015759</v>
+        <v>80.50331174823846</v>
       </c>
       <c r="D5" t="n">
-        <v>46.75573441475435</v>
+        <v>66.90610604442014</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>37.83655652167208</v>
+        <v>31.03402667894593</v>
       </c>
       <c r="C6" t="n">
-        <v>130.7776299350134</v>
+        <v>94.67189461592844</v>
       </c>
       <c r="D6" t="n">
-        <v>36.74976181307086</v>
+        <v>41.57996051796516</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>22.0382724649324</v>
+        <v>17.24734366820796</v>
       </c>
       <c r="C7" t="n">
-        <v>107.1371452167502</v>
+        <v>77.37350006709961</v>
       </c>
       <c r="D7" t="n">
-        <v>35.87207936547421</v>
+        <v>36.05173919535137</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.01382658331747</v>
+        <v>8.261406931236909</v>
       </c>
       <c r="C8" t="n">
-        <v>59.74916528046088</v>
+        <v>45.8132566186774</v>
       </c>
       <c r="D8" t="n">
-        <v>33.46287049925253</v>
+        <v>33.71321616383547</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.879687000734146</v>
+        <v>5.435937038414587</v>
       </c>
       <c r="C9" t="n">
-        <v>31.06249736236907</v>
+        <v>28.51093507903161</v>
       </c>
       <c r="D9" t="n">
-        <v>32.28280975874785</v>
+        <v>33.17030968338697</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.124723016168351</v>
+        <v>4.982369599052563</v>
       </c>
       <c r="C10" t="n">
-        <v>26.76244241776806</v>
+        <v>26.90479583488384</v>
       </c>
       <c r="D10" t="n">
-        <v>34.02246669067321</v>
+        <v>34.16482010778901</v>
       </c>
     </row>
     <row r="11">
@@ -6504,10 +6504,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>4.264712027248144</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
         <v>35.53926689373453</v>
@@ -6521,7 +6521,7 @@
         <v>3.471459882216721</v>
       </c>
       <c r="C12" t="n">
-        <v>24.73415166079414</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
         <v>34.28066633689012</v>
@@ -6535,7 +6535,7 @@
         <v>2.601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>23.15451960466103</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
         <v>31.47974013667398</v>
@@ -6563,10 +6563,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>18.99190933865455</v>
+        <v>19.35024725070463</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>28.66703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -6580,7 +6580,7 @@
         <v>17.77257868998001</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>26.03889435973815</v>
       </c>
     </row>
     <row r="17">
@@ -6608,7 +6608,7 @@
         <v>17.65673246087889</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>20.86704745376595</v>
       </c>
     </row>
     <row r="19">
@@ -6619,10 +6619,10 @@
         <v>0.6018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>18.05434028109884</v>
+        <v>18.65615162380213</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>16.24890625298896</v>
       </c>
     </row>
     <row r="20">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.464353916806528</v>
+        <v>7.472848637928375</v>
       </c>
       <c r="C21" t="n">
-        <v>83.97398156407343</v>
+        <v>84.06954717669421</v>
       </c>
       <c r="D21" t="n">
-        <v>6.531309677205711</v>
+        <v>6.538742558187328</v>
       </c>
     </row>
   </sheetData>

--- a/output/yearly_surface_area_iteration_17_growth_param_0.5.xlsx
+++ b/output/yearly_surface_area_iteration_17_growth_param_0.5.xlsx
@@ -735,10 +735,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>10.84497632556114</v>
+        <v>10.84497634775613</v>
       </c>
       <c r="C21" t="n">
-        <v>37.78907191872407</v>
+        <v>37.78907199606198</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -780,13 +780,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.741841411512095</v>
+        <v>0.8874999246391165</v>
       </c>
       <c r="C2" t="n">
-        <v>7.721445693901163</v>
+        <v>3.61970378555799</v>
       </c>
       <c r="D2" t="n">
-        <v>50.19872361354791</v>
+        <v>12.21981367476005</v>
       </c>
     </row>
     <row r="3">
@@ -794,13 +794,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.07964473723101</v>
+        <v>7.795076771719675</v>
       </c>
       <c r="C3" t="n">
-        <v>30.98395754602934</v>
+        <v>43.21162520242336</v>
       </c>
       <c r="D3" t="n">
-        <v>110.5938788834032</v>
+        <v>69.28684422721864</v>
       </c>
     </row>
     <row r="4">
@@ -808,13 +808,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.98712377332033</v>
+        <v>14.71541633895544</v>
       </c>
       <c r="C4" t="n">
-        <v>72.93894568701677</v>
+        <v>135.3996981266073</v>
       </c>
       <c r="D4" t="n">
-        <v>133.906459868448</v>
+        <v>81.96218883674922</v>
       </c>
     </row>
     <row r="5">
@@ -822,13 +822,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>45.33220024359647</v>
+        <v>15.04528356758237</v>
       </c>
       <c r="C5" t="n">
-        <v>89.21632262342891</v>
+        <v>160.8348176482337</v>
       </c>
       <c r="D5" t="n">
-        <v>87.67006998924018</v>
+        <v>48.49833658979244</v>
       </c>
     </row>
     <row r="6">
@@ -836,13 +836,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>41.09694064747573</v>
+        <v>10.82769543013807</v>
       </c>
       <c r="C6" t="n">
-        <v>111.5775900830585</v>
+        <v>100.266874782431</v>
       </c>
       <c r="D6" t="n">
-        <v>52.1258943569844</v>
+        <v>29.62521872335175</v>
       </c>
     </row>
     <row r="7">
@@ -850,13 +850,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>26.76931465169778</v>
+        <v>5.928774385946488</v>
       </c>
       <c r="C7" t="n">
-        <v>106.4185058972415</v>
+        <v>51.56237117474672</v>
       </c>
       <c r="D7" t="n">
-        <v>39.34550274309942</v>
+        <v>29.76364514965055</v>
       </c>
     </row>
     <row r="8">
@@ -864,13 +864,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>13.4352173326176</v>
+        <v>6.00829594999048</v>
       </c>
       <c r="C8" t="n">
-        <v>74.35266238113219</v>
+        <v>30.0414797499524</v>
       </c>
       <c r="D8" t="n">
-        <v>35.88287859022092</v>
+        <v>29.95803119509142</v>
       </c>
     </row>
     <row r="9">
@@ -878,13 +878,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6.878124415953151</v>
+        <v>5.879687000734146</v>
       </c>
       <c r="C9" t="n">
-        <v>42.71093387325747</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>34.16874709860598</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -892,13 +892,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.267076433284139</v>
+        <v>3.558835427894688</v>
       </c>
       <c r="C10" t="n">
-        <v>30.60598467989432</v>
+        <v>29.75186417719959</v>
       </c>
       <c r="D10" t="n">
-        <v>35.01894061048373</v>
+        <v>37.29659528433633</v>
       </c>
     </row>
     <row r="11">
@@ -906,13 +906,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.442408361716816</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>30.74146586308036</v>
       </c>
       <c r="D11" t="n">
-        <v>35.7169632282032</v>
+        <v>38.02701557629594</v>
       </c>
     </row>
     <row r="12">
@@ -920,13 +920,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.688426124855267</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>27.12078032981814</v>
+        <v>23.64932044760141</v>
       </c>
       <c r="D12" t="n">
-        <v>35.1485313074443</v>
+        <v>37.5351599764683</v>
       </c>
     </row>
     <row r="13">
@@ -934,13 +934,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.821141991377834</v>
       </c>
       <c r="C13" t="n">
-        <v>25.23582473766426</v>
+        <v>19.77239876353076</v>
       </c>
       <c r="D13" t="n">
-        <v>32.26022956155019</v>
+        <v>35.90251354430586</v>
       </c>
     </row>
     <row r="14">
@@ -948,13 +948,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.536435157146258</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>27.3485457972034</v>
       </c>
     </row>
     <row r="15">
@@ -968,7 +968,7 @@
         <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>25.44199175555609</v>
       </c>
     </row>
     <row r="16">
@@ -976,13 +976,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>1.653263133951629</v>
       </c>
       <c r="C16" t="n">
-        <v>19.01252604044373</v>
+        <v>22.31905230834699</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>22.31905230834699</v>
       </c>
     </row>
     <row r="17">
@@ -990,13 +990,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
+        <v>24.55547357862122</v>
+      </c>
+      <c r="D17" t="n">
         <v>17.9443845382232</v>
-      </c>
-      <c r="D17" t="n">
-        <v>24.0832529328785</v>
       </c>
     </row>
     <row r="18">
@@ -1004,13 +1004,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="C18" t="n">
-        <v>18.1917849596934</v>
+        <v>26.21757244191107</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>11.77115497391926</v>
       </c>
     </row>
     <row r="19">
@@ -1018,13 +1018,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>10.83260416865931</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>84.25358797846125</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>3.009056713516474</v>
       </c>
     </row>
     <row r="20">
@@ -1035,10 +1035,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1046,13 +1046,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.661798412501951</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>92.89930575158614</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>7.661798412501951</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1091,13 +1091,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.16791991515521</v>
+        <v>0.9945104244020189</v>
       </c>
       <c r="C2" t="n">
-        <v>12.0951317163207</v>
+        <v>8.273187903687871</v>
       </c>
       <c r="D2" t="n">
-        <v>50.32929605821273</v>
+        <v>15.76490463479528</v>
       </c>
     </row>
     <row r="3">
@@ -1105,13 +1105,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.29562923216531</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C3" t="n">
-        <v>30.29182541453534</v>
+        <v>26.62990647769473</v>
       </c>
       <c r="D3" t="n">
-        <v>121.3096550752571</v>
+        <v>63.82832699160638</v>
       </c>
     </row>
     <row r="4">
@@ -1119,13 +1119,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.01340997715674</v>
+        <v>14.86856898081794</v>
       </c>
       <c r="C4" t="n">
-        <v>74.22798042269284</v>
+        <v>121.7052994000686</v>
       </c>
       <c r="D4" t="n">
-        <v>152.1443869702409</v>
+        <v>96.43511349275569</v>
       </c>
     </row>
     <row r="5">
@@ -1133,13 +1133,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>47.66385104118265</v>
+        <v>18.72683745850791</v>
       </c>
       <c r="C5" t="n">
-        <v>110.3729856499477</v>
+        <v>207.1733092886832</v>
       </c>
       <c r="D5" t="n">
-        <v>111.0847527355266</v>
+        <v>64.81989217289566</v>
       </c>
     </row>
     <row r="6">
@@ -1147,13 +1147,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>50.39507315439728</v>
+        <v>15.13462260866883</v>
       </c>
       <c r="C6" t="n">
-        <v>124.4178683069026</v>
+        <v>178.6771004252153</v>
       </c>
       <c r="D6" t="n">
-        <v>64.12088780747193</v>
+        <v>36.87051678069322</v>
       </c>
     </row>
     <row r="7">
@@ -1161,13 +1161,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>36.4110588551057</v>
+        <v>8.982991493858314</v>
       </c>
       <c r="C7" t="n">
-        <v>132.0499749597172</v>
+        <v>96.95642152371074</v>
       </c>
       <c r="D7" t="n">
-        <v>44.55563780953724</v>
+        <v>31.56024344842221</v>
       </c>
     </row>
     <row r="8">
@@ -1175,13 +1175,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>20.19455027635689</v>
+        <v>6.425538724295373</v>
       </c>
       <c r="C8" t="n">
-        <v>103.9768993567797</v>
+        <v>48.31671326450677</v>
       </c>
       <c r="D8" t="n">
-        <v>37.71874679716245</v>
+        <v>31.2097595180061</v>
       </c>
     </row>
     <row r="9">
@@ -1189,13 +1189,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.873436661610169</v>
+        <v>6.101561981893925</v>
       </c>
       <c r="C9" t="n">
-        <v>65.23124446097505</v>
+        <v>34.94530953266521</v>
       </c>
       <c r="D9" t="n">
-        <v>35.61093447614454</v>
+        <v>35.83280945730432</v>
       </c>
     </row>
     <row r="10">
@@ -1203,13 +1203,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>5.836490101747287</v>
+        <v>4.128249096357838</v>
       </c>
       <c r="C10" t="n">
-        <v>39.43189654107314</v>
+        <v>33.73775985644164</v>
       </c>
       <c r="D10" t="n">
-        <v>35.3036474447153</v>
+        <v>37.72365553568369</v>
       </c>
     </row>
     <row r="11">
@@ -1217,13 +1217,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.620104696185489</v>
+        <v>2.843141351498762</v>
       </c>
       <c r="C11" t="n">
-        <v>32.16303653882975</v>
+        <v>33.22921454564179</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>38.73780091417063</v>
       </c>
     </row>
     <row r="12">
@@ -1231,13 +1231,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>2.169662426385451</v>
       </c>
       <c r="C12" t="n">
-        <v>30.15830772675777</v>
+        <v>28.20561154301086</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>38.40302494702248</v>
       </c>
     </row>
     <row r="13">
@@ -1245,13 +1245,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>1.560978849752429</v>
       </c>
       <c r="C13" t="n">
-        <v>27.3171298706675</v>
+        <v>22.37403017978481</v>
       </c>
       <c r="D13" t="n">
-        <v>33.04071898642641</v>
+        <v>36.16267668593127</v>
       </c>
     </row>
     <row r="14">
@@ -1259,13 +1259,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>1.229148125717007</v>
       </c>
       <c r="C14" t="n">
-        <v>25.19753657719863</v>
+        <v>21.51009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>28.88498095434966</v>
       </c>
     </row>
     <row r="15">
@@ -1276,10 +1276,10 @@
         <v>1.433351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>22.21695054710532</v>
+        <v>22.93362637120549</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>25.44199175555609</v>
       </c>
     </row>
     <row r="16">
@@ -1290,10 +1290,10 @@
         <v>1.239947350463722</v>
       </c>
       <c r="C16" t="n">
-        <v>20.25247339090745</v>
+        <v>24.79894700927443</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>21.90573652485908</v>
       </c>
     </row>
     <row r="17">
@@ -1301,13 +1301,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>1.416661937228147</v>
       </c>
       <c r="C17" t="n">
-        <v>18.41660518396592</v>
+        <v>26.44435616159209</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>16.99994324673777</v>
       </c>
     </row>
     <row r="18">
@@ -1315,13 +1315,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>8.560839981032187</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>50.82998738737861</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>9.63094497866121</v>
       </c>
     </row>
     <row r="19">
@@ -1332,10 +1332,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>45.13585070274711</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>1.805434028109884</v>
       </c>
     </row>
     <row r="20">
@@ -1346,10 +1346,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1357,13 +1357,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.834099524760994</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>100.8640313812978</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>8.813361965356119</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1402,13 +1402,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.959609475405639</v>
+        <v>0.5458517235612266</v>
       </c>
       <c r="C2" t="n">
-        <v>7.229590094073512</v>
+        <v>3.599087083768807</v>
       </c>
       <c r="D2" t="n">
-        <v>50.3076976087193</v>
+        <v>10.77958979262998</v>
       </c>
     </row>
     <row r="3">
@@ -1416,13 +1416,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>15.78159434576748</v>
+        <v>5.056000676871074</v>
       </c>
       <c r="C3" t="n">
-        <v>37.57148464152544</v>
+        <v>31.07231483941155</v>
       </c>
       <c r="D3" t="n">
-        <v>129.1832716633165</v>
+        <v>63.9903153628071</v>
       </c>
     </row>
     <row r="4">
@@ -1430,13 +1430,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.36701907713484</v>
+        <v>16.20865459711484</v>
       </c>
       <c r="C4" t="n">
-        <v>74.58533658703867</v>
+        <v>112.8734970526643</v>
       </c>
       <c r="D4" t="n">
-        <v>171.0204500797944</v>
+        <v>106.3900352138184</v>
       </c>
     </row>
     <row r="5">
@@ -1444,13 +1444,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.82936549257286</v>
+        <v>18.87409961414493</v>
       </c>
       <c r="C5" t="n">
-        <v>120.0677442293849</v>
+        <v>239.2764592175539</v>
       </c>
       <c r="D5" t="n">
-        <v>131.0142311317369</v>
+        <v>71.54486394698633</v>
       </c>
     </row>
     <row r="6">
@@ -1458,13 +1458,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>55.74854338565514</v>
+        <v>12.11574841810989</v>
       </c>
       <c r="C6" t="n">
-        <v>144.3826896204657</v>
+        <v>220.096054319684</v>
       </c>
       <c r="D6" t="n">
-        <v>79.13475544851842</v>
+        <v>37.47429161880501</v>
       </c>
     </row>
     <row r="7">
@@ -1472,13 +1472,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>45.6934833987593</v>
+        <v>4.251949307092936</v>
       </c>
       <c r="C7" t="n">
-        <v>152.7707420055504</v>
+        <v>88.93161578919732</v>
       </c>
       <c r="D7" t="n">
-        <v>50.12509253572939</v>
+        <v>32.93763547748049</v>
       </c>
     </row>
     <row r="8">
@@ -1486,13 +1486,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>27.87181732356695</v>
+        <v>4.172427743048944</v>
       </c>
       <c r="C8" t="n">
-        <v>132.6832022289564</v>
+        <v>41.80772598535042</v>
       </c>
       <c r="D8" t="n">
-        <v>40.05530633326986</v>
+        <v>35.63253292563798</v>
       </c>
     </row>
     <row r="9">
@@ -1500,13 +1500,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>14.08906130364597</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="C9" t="n">
-        <v>90.96874227550941</v>
+        <v>25.73749781453438</v>
       </c>
       <c r="D9" t="n">
-        <v>37.05312185368311</v>
+        <v>39.60468413702056</v>
       </c>
     </row>
     <row r="10">
@@ -1514,13 +1514,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.260024272905163</v>
+        <v>1.992947839621025</v>
       </c>
       <c r="C10" t="n">
-        <v>54.94841900669398</v>
+        <v>26.05067533218912</v>
       </c>
       <c r="D10" t="n">
-        <v>35.73070769606267</v>
+        <v>30.32127784566274</v>
       </c>
     </row>
     <row r="11">
@@ -1528,13 +1528,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.975497365122834</v>
+        <v>1.599267010218054</v>
       </c>
       <c r="C11" t="n">
-        <v>37.49392657288993</v>
+        <v>22.56743447752142</v>
       </c>
       <c r="D11" t="n">
-        <v>36.78314123501524</v>
+        <v>30.74146586308036</v>
       </c>
     </row>
     <row r="12">
@@ -1542,13 +1542,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.905392367493811</v>
+        <v>1.084831213192725</v>
       </c>
       <c r="C12" t="n">
-        <v>32.76190263842031</v>
+        <v>18.22516438163779</v>
       </c>
       <c r="D12" t="n">
-        <v>35.58246379272139</v>
+        <v>29.50740899884213</v>
       </c>
     </row>
     <row r="13">
@@ -1556,13 +1556,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.861794557879452</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>29.91876128692155</v>
+        <v>17.69109363052753</v>
       </c>
       <c r="D13" t="n">
-        <v>33.56104526967722</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1570,13 +1570,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>26.73397173434489</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>21.20280516861837</v>
       </c>
     </row>
     <row r="15">
@@ -1584,13 +1584,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
-        <v>24.00864010735575</v>
+        <v>20.78359889890498</v>
       </c>
       <c r="D15" t="n">
-        <v>29.38370878810703</v>
+        <v>18.27523351455437</v>
       </c>
     </row>
     <row r="16">
@@ -1598,13 +1598,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="C16" t="n">
-        <v>21.49242074137117</v>
+        <v>22.31905230834699</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>14.46605242207675</v>
       </c>
     </row>
     <row r="17">
@@ -1612,13 +1612,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>6.611089040398022</v>
       </c>
       <c r="C17" t="n">
-        <v>19.36104647545135</v>
+        <v>43.91652005407257</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>8.02775097762617</v>
       </c>
     </row>
     <row r="18">
@@ -1626,13 +1626,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>18.72683745850791</v>
+        <v>39.05883241345935</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>1.070104997629023</v>
       </c>
     </row>
     <row r="19">
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1657,10 +1657,10 @@
         <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1668,13 +1668,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.989951275870022</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>107.8643422242453</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>9.987439094837528</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1713,13 +1713,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.299875018151782</v>
+        <v>0.4123340357836604</v>
       </c>
       <c r="C2" t="n">
-        <v>5.031456984264903</v>
+        <v>7.254133786679681</v>
       </c>
       <c r="D2" t="n">
-        <v>41.48571273835746</v>
+        <v>12.85107744859075</v>
       </c>
     </row>
     <row r="3">
@@ -1727,13 +1727,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.43860454408685</v>
+        <v>3.436116964863836</v>
       </c>
       <c r="C3" t="n">
-        <v>51.94427103169874</v>
+        <v>21.94696992843745</v>
       </c>
       <c r="D3" t="n">
-        <v>138.0190010015378</v>
+        <v>58.74778262212914</v>
       </c>
     </row>
     <row r="4">
@@ -1741,13 +1741,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>22.48791291347744</v>
+        <v>13.26046624126167</v>
       </c>
       <c r="C4" t="n">
-        <v>100.0342005765245</v>
+        <v>95.58001124235672</v>
       </c>
       <c r="D4" t="n">
-        <v>158.7299505703286</v>
+        <v>112.9373106534403</v>
       </c>
     </row>
     <row r="5">
@@ -1755,13 +1755,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>31.39138284329177</v>
+        <v>21.59844949342983</v>
       </c>
       <c r="C5" t="n">
-        <v>86.27107951068848</v>
+        <v>226.1455836732528</v>
       </c>
       <c r="D5" t="n">
-        <v>82.49135084933826</v>
+        <v>89.80537124597699</v>
       </c>
     </row>
     <row r="6">
@@ -1769,13 +1769,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>28.37741739125406</v>
+        <v>17.67047692873834</v>
       </c>
       <c r="C6" t="n">
-        <v>100.588888029424</v>
+        <v>296.2119355776434</v>
       </c>
       <c r="D6" t="n">
-        <v>33.00635781677777</v>
+        <v>48.46299367243955</v>
       </c>
     </row>
     <row r="7">
@@ -1783,13 +1783,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>18.44507586738907</v>
+        <v>7.845145904636261</v>
       </c>
       <c r="C7" t="n">
-        <v>93.30333831620835</v>
+        <v>191.0981723793459</v>
       </c>
       <c r="D7" t="n">
-        <v>28.14670668075605</v>
+        <v>36.05173919535137</v>
       </c>
     </row>
     <row r="8">
@@ -1797,13 +1797,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.763480918734528</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C8" t="n">
-        <v>67.00918955336604</v>
+        <v>73.93541960682728</v>
       </c>
       <c r="D8" t="n">
-        <v>27.28767743954009</v>
+        <v>36.80081269369168</v>
       </c>
     </row>
     <row r="9">
@@ -1811,13 +1811,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.214062057254808</v>
+        <v>3.217187226816797</v>
       </c>
       <c r="C9" t="n">
-        <v>41.93437143919824</v>
+        <v>36.94218436310322</v>
       </c>
       <c r="D9" t="n">
-        <v>27.17968519207294</v>
+        <v>40.27030908049991</v>
       </c>
     </row>
     <row r="10">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>3.558835427894688</v>
+        <v>2.135301256736813</v>
       </c>
       <c r="C10" t="n">
-        <v>29.32480392585223</v>
+        <v>28.75539025738908</v>
       </c>
       <c r="D10" t="n">
-        <v>28.75539025738908</v>
+        <v>32.17187226816798</v>
       </c>
     </row>
     <row r="11">
@@ -1839,13 +1839,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.843141351498762</v>
+        <v>1.421570675749381</v>
       </c>
       <c r="C11" t="n">
-        <v>26.12136116689488</v>
+        <v>25.9436648324262</v>
       </c>
       <c r="D11" t="n">
-        <v>28.43141351498762</v>
+        <v>31.8076438698924</v>
       </c>
     </row>
     <row r="12">
@@ -1853,13 +1853,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>2.169662426385451</v>
+        <v>0.8678649705541803</v>
       </c>
       <c r="C12" t="n">
-        <v>24.30021917551705</v>
+        <v>20.82875929330033</v>
       </c>
       <c r="D12" t="n">
-        <v>27.33774657245668</v>
+        <v>30.15830772675777</v>
       </c>
     </row>
     <row r="13">
@@ -1867,13 +1867,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>1.300815708127024</v>
+        <v>0.7804894248762143</v>
       </c>
       <c r="C13" t="n">
-        <v>22.11386703815941</v>
+        <v>20.81305133003238</v>
       </c>
       <c r="D13" t="n">
-        <v>25.23582473766426</v>
+        <v>23.93500902953724</v>
       </c>
     </row>
     <row r="14">
@@ -1881,13 +1881,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.921861094287755</v>
+        <v>0.6145740628585034</v>
       </c>
       <c r="C14" t="n">
-        <v>19.97365704290136</v>
+        <v>20.89551813718911</v>
       </c>
       <c r="D14" t="n">
-        <v>24.58296251434014</v>
+        <v>21.20280516861837</v>
       </c>
     </row>
     <row r="15">
@@ -1898,10 +1898,10 @@
         <v>0.7166758241001715</v>
       </c>
       <c r="C15" t="n">
+        <v>23.29196428325557</v>
+      </c>
+      <c r="D15" t="n">
         <v>17.91689560250429</v>
-      </c>
-      <c r="D15" t="n">
-        <v>21.85861263505523</v>
       </c>
     </row>
     <row r="16">
@@ -1909,13 +1909,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.4133157834879072</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>37.61173629739955</v>
       </c>
       <c r="D16" t="n">
-        <v>20.25247339090745</v>
+        <v>12.81278928812512</v>
       </c>
     </row>
     <row r="17">
@@ -1926,10 +1926,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>16.05550195525234</v>
+        <v>46.27762328278614</v>
       </c>
       <c r="D17" t="n">
-        <v>17.9443845382232</v>
+        <v>5.194427103169874</v>
       </c>
     </row>
     <row r="18">
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>16.05157496443535</v>
+        <v>1.070104997629023</v>
       </c>
       <c r="D18" t="n">
-        <v>13.9113649691773</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1954,10 +1954,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>16.85071759569225</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>9.027170140549421</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1965,13 +1965,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>5.37997741927252</v>
+        <v>0</v>
       </c>
       <c r="C20" t="n">
-        <v>72.62969516017901</v>
+        <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>6.724971774090649</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2024,13 +2024,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.948589266480671</v>
+        <v>0.2228567288640259</v>
       </c>
       <c r="C2" t="n">
-        <v>2.735149104031614</v>
+        <v>5.002004553137499</v>
       </c>
       <c r="D2" t="n">
-        <v>28.43043176728338</v>
+        <v>10.03935202362788</v>
       </c>
     </row>
     <row r="3">
@@ -2038,13 +2038,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>20.92104357749953</v>
+        <v>2.586905200690345</v>
       </c>
       <c r="C3" t="n">
-        <v>36.49156216685395</v>
+        <v>25.5156228333746</v>
       </c>
       <c r="D3" t="n">
-        <v>139.1725545540278</v>
+        <v>56.16087742143878</v>
       </c>
     </row>
     <row r="4">
@@ -2052,13 +2052,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>28.76717122984004</v>
+        <v>10.97593933347934</v>
       </c>
       <c r="C4" t="n">
-        <v>117.5957035100914</v>
+        <v>79.7031873692773</v>
       </c>
       <c r="D4" t="n">
-        <v>185.7613918590602</v>
+        <v>117.4042627077633</v>
       </c>
     </row>
     <row r="5">
@@ -2066,13 +2066,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>34.36116964863837</v>
+        <v>22.38384765682728</v>
       </c>
       <c r="C5" t="n">
-        <v>130.3760951239765</v>
+        <v>213.8491936775615</v>
       </c>
       <c r="D5" t="n">
-        <v>107.2068493037517</v>
+        <v>102.5926350937917</v>
       </c>
     </row>
     <row r="6">
@@ -2080,13 +2080,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>33.40887437551896</v>
+        <v>21.17237098978672</v>
       </c>
       <c r="C6" t="n">
-        <v>119.1046497315188</v>
+        <v>332.9616973907143</v>
       </c>
       <c r="D6" t="n">
-        <v>42.38499363544755</v>
+        <v>58.76741757621409</v>
       </c>
     </row>
     <row r="7">
@@ -2094,13 +2094,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.0676838383308</v>
+        <v>8.024805734513427</v>
       </c>
       <c r="C7" t="n">
-        <v>115.8207036608132</v>
+        <v>270.148497525299</v>
       </c>
       <c r="D7" t="n">
-        <v>30.72183090899544</v>
+        <v>39.34550274309942</v>
       </c>
     </row>
     <row r="8">
@@ -2108,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.17795837637593</v>
+        <v>4.172427743048944</v>
       </c>
       <c r="C8" t="n">
-        <v>86.20235717139117</v>
+        <v>115.1590057081509</v>
       </c>
       <c r="D8" t="n">
-        <v>28.03871443328891</v>
+        <v>38.97047512007713</v>
       </c>
     </row>
     <row r="9">
@@ -2122,13 +2122,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.215624642035802</v>
+        <v>2.662499773917349</v>
       </c>
       <c r="C9" t="n">
-        <v>45.81718360949438</v>
+        <v>46.14999608123405</v>
       </c>
       <c r="D9" t="n">
-        <v>28.39999758845172</v>
+        <v>40.04843409934012</v>
       </c>
     </row>
     <row r="10">
@@ -2136,13 +2136,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.992947839621025</v>
+        <v>1.423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>31.46010518258904</v>
+        <v>31.17539834835747</v>
       </c>
       <c r="D10" t="n">
-        <v>29.60951076008381</v>
+        <v>33.31069960509428</v>
       </c>
     </row>
     <row r="11">
@@ -2150,13 +2150,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>28.96450251839364</v>
+        <v>26.65445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>29.67528785626833</v>
+        <v>32.69612554223576</v>
       </c>
     </row>
     <row r="12">
@@ -2164,13 +2164,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>20.17786056538469</v>
+        <v>22.34752299177014</v>
       </c>
       <c r="D12" t="n">
-        <v>28.20561154301086</v>
+        <v>28.8565102709265</v>
       </c>
     </row>
     <row r="13">
@@ -2178,13 +2178,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.5203262832508095</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>16.3902779224005</v>
+        <v>17.17076734727672</v>
       </c>
       <c r="D13" t="n">
-        <v>25.75615102091507</v>
+        <v>24.19517217116264</v>
       </c>
     </row>
     <row r="14">
@@ -2195,10 +2195,10 @@
         <v>0.3072870314292517</v>
       </c>
       <c r="C14" t="n">
-        <v>15.05706454003333</v>
+        <v>19.35908298004286</v>
       </c>
       <c r="D14" t="n">
-        <v>18.12993485432585</v>
+        <v>16.90078672860884</v>
       </c>
     </row>
     <row r="15">
@@ -2206,13 +2206,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>13.97517856995334</v>
+        <v>31.89207417245764</v>
       </c>
       <c r="D15" t="n">
-        <v>17.20021977840412</v>
+        <v>10.75013736150257</v>
       </c>
     </row>
     <row r="16">
@@ -2223,10 +2223,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>13.63942085510094</v>
+        <v>39.67831521483909</v>
       </c>
       <c r="D16" t="n">
-        <v>15.29268398905256</v>
+        <v>4.133157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -2237,10 +2237,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>13.69439872653876</v>
+        <v>0.4722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2251,10 +2251,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>14.44641746799181</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>7.490734983403163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2262,13 +2262,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>4.212679398923063</v>
+        <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>63.19019098384595</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2335,13 +2335,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.659955441432109</v>
+        <v>0.3504839304161113</v>
       </c>
       <c r="C2" t="n">
-        <v>5.14337622254904</v>
+        <v>8.626617077216721</v>
       </c>
       <c r="D2" t="n">
-        <v>29.11176467403067</v>
+        <v>13.91823720310703</v>
       </c>
     </row>
     <row r="3">
@@ -2349,13 +2349,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.16585860875548</v>
+        <v>1.713149743910684</v>
       </c>
       <c r="C3" t="n">
-        <v>23.33614292994668</v>
+        <v>22.38384765682728</v>
       </c>
       <c r="D3" t="n">
-        <v>130.2239242298182</v>
+        <v>51.7086515826795</v>
       </c>
     </row>
     <row r="4">
@@ -2363,13 +2363,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>33.97436105316512</v>
+        <v>8.155378179178253</v>
       </c>
       <c r="C4" t="n">
-        <v>104.4628644703819</v>
+        <v>72.00726711568656</v>
       </c>
       <c r="D4" t="n">
-        <v>208.8491526198325</v>
+        <v>118.2210767976967</v>
       </c>
     </row>
     <row r="5">
@@ -2377,13 +2377,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.38633523605029</v>
+        <v>20.32217747790898</v>
       </c>
       <c r="C5" t="n">
-        <v>170.8731879241574</v>
+        <v>185.2803354839793</v>
       </c>
       <c r="D5" t="n">
-        <v>142.3288734231814</v>
+        <v>117.196132194463</v>
       </c>
     </row>
     <row r="6">
@@ -2391,13 +2391,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>38.96360288614742</v>
+        <v>24.87552333020568</v>
       </c>
       <c r="C6" t="n">
-        <v>160.0405837554981</v>
+        <v>337.1881212574968</v>
       </c>
       <c r="D6" t="n">
-        <v>61.02151030516475</v>
+        <v>72.69449050865934</v>
       </c>
     </row>
     <row r="7">
@@ -2405,13 +2405,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>25.69135567243478</v>
+        <v>14.13323995033708</v>
       </c>
       <c r="C7" t="n">
-        <v>141.0329664535755</v>
+        <v>358.3015873850287</v>
       </c>
       <c r="D7" t="n">
-        <v>34.7941203862112</v>
+        <v>45.03473068920969</v>
       </c>
     </row>
     <row r="8">
@@ -2419,13 +2419,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.68279768053704</v>
+        <v>5.757950285407543</v>
       </c>
       <c r="C8" t="n">
-        <v>116.4107340310655</v>
+        <v>213.461403334384</v>
       </c>
       <c r="D8" t="n">
-        <v>29.87458264023044</v>
+        <v>40.38910055271378</v>
       </c>
     </row>
     <row r="9">
@@ -2433,13 +2433,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.435937038414587</v>
+        <v>3.106249736236907</v>
       </c>
       <c r="C9" t="n">
-        <v>71.55468142402876</v>
+        <v>83.20311793491715</v>
       </c>
       <c r="D9" t="n">
-        <v>29.06562253193106</v>
+        <v>40.82499653339935</v>
       </c>
     </row>
     <row r="10">
@@ -2447,13 +2447,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>2.420008090968388</v>
+        <v>1.70824100538945</v>
       </c>
       <c r="C10" t="n">
-        <v>40.57072387799944</v>
+        <v>40.14366362665208</v>
       </c>
       <c r="D10" t="n">
-        <v>30.17892442854695</v>
+        <v>35.01894061048373</v>
       </c>
     </row>
     <row r="11">
@@ -2461,13 +2461,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>1.599267010218054</v>
+        <v>0.5330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>32.51842920776709</v>
+        <v>30.56376952861169</v>
       </c>
       <c r="D11" t="n">
-        <v>29.852984190737</v>
+        <v>33.05151821117311</v>
       </c>
     </row>
     <row r="12">
@@ -2475,13 +2475,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>0.8678649705541803</v>
+        <v>0.4339324852770902</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>25.16808414607123</v>
       </c>
       <c r="D12" t="n">
-        <v>28.8565102709265</v>
+        <v>29.50740899884213</v>
       </c>
     </row>
     <row r="13">
@@ -2492,10 +2492,10 @@
         <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>18.47158305540374</v>
+        <v>19.51223562190536</v>
       </c>
       <c r="D13" t="n">
-        <v>26.01631416254048</v>
+        <v>24.45533531278805</v>
       </c>
     </row>
     <row r="14">
@@ -2503,13 +2503,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>0.921861094287755</v>
       </c>
       <c r="C14" t="n">
-        <v>15.97892563432109</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="D14" t="n">
-        <v>18.74450891718435</v>
+        <v>17.51536079146734</v>
       </c>
     </row>
     <row r="15">
@@ -2517,13 +2517,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0</v>
+        <v>2.5083653843506</v>
       </c>
       <c r="C15" t="n">
-        <v>15.76686813020377</v>
+        <v>32.96708790860789</v>
       </c>
       <c r="D15" t="n">
-        <v>16.84188186635403</v>
+        <v>10.39179944945249</v>
       </c>
     </row>
     <row r="16">
@@ -2534,10 +2534,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>14.46605242207675</v>
+        <v>38.85168364786328</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>3.719842051391165</v>
       </c>
     </row>
     <row r="17">
@@ -2548,10 +2548,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>14.63884001802419</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>10.86107485208246</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2559,13 +2559,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>3.21031499288707</v>
+        <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>6.955682484588652</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2576,10 +2576,10 @@
         <v>0</v>
       </c>
       <c r="C19" t="n">
-        <v>33.09962384868121</v>
+        <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -2646,13 +2646,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.223658550119025</v>
+        <v>0.2434734306532089</v>
       </c>
       <c r="C2" t="n">
-        <v>2.489712177969911</v>
+        <v>4.76147636559703</v>
       </c>
       <c r="D2" t="n">
-        <v>20.30254252382404</v>
+        <v>10.24453729381547</v>
       </c>
     </row>
     <row r="3">
@@ -2660,13 +2660,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.8222469122691</v>
+        <v>2.601631416254047</v>
       </c>
       <c r="C3" t="n">
-        <v>23.45886139297754</v>
+        <v>29.38861752662827</v>
       </c>
       <c r="D3" t="n">
-        <v>128.898564829085</v>
+        <v>56.710656135817</v>
       </c>
     </row>
     <row r="4">
@@ -2674,13 +2674,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.56068541677872</v>
+        <v>13.80926320793563</v>
       </c>
       <c r="C4" t="n">
-        <v>98.86003032224532</v>
+        <v>104.1310337463464</v>
       </c>
       <c r="D4" t="n">
-        <v>224.4324339293421</v>
+        <v>120.7225699481175</v>
       </c>
     </row>
     <row r="5">
@@ -2688,13 +2688,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>40.17802479630072</v>
+        <v>14.75075925630833</v>
       </c>
       <c r="C5" t="n">
-        <v>202.7309009269664</v>
+        <v>281.66341634841</v>
       </c>
       <c r="D5" t="n">
-        <v>150.8455347575224</v>
+        <v>107.2068493037517</v>
       </c>
     </row>
     <row r="6">
@@ -2702,13 +2702,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.43654323768712</v>
+        <v>8.774860980557992</v>
       </c>
       <c r="C6" t="n">
-        <v>188.1764912115074</v>
+        <v>308.6899488986204</v>
       </c>
       <c r="D6" t="n">
-        <v>58.92842419971056</v>
+        <v>61.102013616913</v>
       </c>
     </row>
     <row r="7">
@@ -2716,13 +2716,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>3.772856427420492</v>
       </c>
       <c r="C7" t="n">
-        <v>148.5187926984575</v>
+        <v>150.0758445573929</v>
       </c>
       <c r="D7" t="n">
-        <v>34.7941203862112</v>
+        <v>34.55457394637499</v>
       </c>
     </row>
     <row r="8">
@@ -2730,13 +2730,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>3.75518496874405</v>
+        <v>2.086213871524472</v>
       </c>
       <c r="C8" t="n">
-        <v>86.95339416514</v>
+        <v>61.33468782281948</v>
       </c>
       <c r="D8" t="n">
-        <v>31.37665662772806</v>
+        <v>30.0414797499524</v>
       </c>
     </row>
     <row r="9">
@@ -2744,13 +2744,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.664062358698343</v>
+        <v>1.220312396378785</v>
       </c>
       <c r="C9" t="n">
-        <v>30.95155987178918</v>
+        <v>30.61874740004951</v>
       </c>
       <c r="D9" t="n">
-        <v>31.50624732468863</v>
+        <v>26.73593522975338</v>
       </c>
     </row>
     <row r="10">
@@ -2758,13 +2758,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>0.2847068342315751</v>
       </c>
       <c r="C10" t="n">
-        <v>25.48126166372597</v>
+        <v>23.91537407545231</v>
       </c>
       <c r="D10" t="n">
-        <v>23.34596040698915</v>
+        <v>25.90832191507333</v>
       </c>
     </row>
     <row r="11">
@@ -2772,13 +2772,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.5330890034060179</v>
+        <v>0.1776963344686726</v>
       </c>
       <c r="C11" t="n">
-        <v>19.54659679155399</v>
+        <v>20.07968579496001</v>
       </c>
       <c r="D11" t="n">
-        <v>23.10052348092744</v>
+        <v>23.63361248433346</v>
       </c>
     </row>
     <row r="12">
@@ -2789,10 +2789,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>14.97067074205961</v>
+        <v>15.83853571261379</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>19.96089432274615</v>
       </c>
     </row>
     <row r="13">
@@ -2800,13 +2800,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>16.3902779224005</v>
       </c>
       <c r="D13" t="n">
-        <v>15.34962535589888</v>
+        <v>14.30897278939726</v>
       </c>
     </row>
     <row r="14">
@@ -2814,13 +2814,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0</v>
+        <v>1.84372218857551</v>
       </c>
       <c r="C14" t="n">
-        <v>13.21334235145782</v>
+        <v>27.65583282863265</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>8.604036880019047</v>
       </c>
     </row>
     <row r="15">
@@ -2831,10 +2831,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>12.18348900970292</v>
+        <v>32.96708790860789</v>
       </c>
       <c r="D15" t="n">
-        <v>12.541826921753</v>
+        <v>2.866703296400686</v>
       </c>
     </row>
     <row r="16">
@@ -2845,10 +2845,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>12.39947350463721</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>9.092947236733956</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2856,13 +2856,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>2.361103228713579</v>
+        <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>29.7499006817911</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>5.66664774891259</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -2873,10 +2873,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>28.35778243716912</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>2.675262494072558</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -2957,13 +2957,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.747911824186823</v>
+        <v>0.1629701189049705</v>
       </c>
       <c r="C2" t="n">
-        <v>7.549639845657972</v>
+        <v>3.612831551628263</v>
       </c>
       <c r="D2" t="n">
-        <v>15.78355784117597</v>
+        <v>7.463246047684253</v>
       </c>
     </row>
     <row r="3">
@@ -2971,13 +2971,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>12.4976482750619</v>
+        <v>1.752419652080556</v>
       </c>
       <c r="C3" t="n">
-        <v>16.71425466480195</v>
+        <v>23.72393327312417</v>
       </c>
       <c r="D3" t="n">
-        <v>116.9359690528376</v>
+        <v>51.97863220134738</v>
       </c>
     </row>
     <row r="4">
@@ -2985,13 +2985,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.90603962449534</v>
+        <v>9.036005869887644</v>
       </c>
       <c r="C4" t="n">
-        <v>79.71595008943251</v>
+        <v>85.93139480501907</v>
       </c>
       <c r="D4" t="n">
-        <v>234.6043218930433</v>
+        <v>116.3577196550362</v>
       </c>
     </row>
     <row r="5">
@@ -2999,13 +2999,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>46.90299657039137</v>
+        <v>13.67083678163684</v>
       </c>
       <c r="C5" t="n">
-        <v>194.9996377560228</v>
+        <v>215.3463589265379</v>
       </c>
       <c r="D5" t="n">
-        <v>186.679325962531</v>
+        <v>110.6920536538279</v>
       </c>
     </row>
     <row r="6">
@@ -3013,13 +3013,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>40.05039759474864</v>
+        <v>8.493099389439159</v>
       </c>
       <c r="C6" t="n">
-        <v>246.5413922289803</v>
+        <v>306.3151012020473</v>
       </c>
       <c r="D6" t="n">
-        <v>84.04545746516095</v>
+        <v>65.40894079544375</v>
       </c>
     </row>
     <row r="7">
@@ -3027,13 +3027,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>16.46881773874025</v>
+        <v>2.934443887993716</v>
       </c>
       <c r="C7" t="n">
-        <v>201.5783291221806</v>
+        <v>195.1105752466026</v>
       </c>
       <c r="D7" t="n">
-        <v>40.60312155223958</v>
+        <v>32.57831581772616</v>
       </c>
     </row>
     <row r="8">
@@ -3041,13 +3041,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.006913291658733</v>
+        <v>1.084831213192726</v>
       </c>
       <c r="C8" t="n">
-        <v>129.7625028088221</v>
+        <v>72.26644850960771</v>
       </c>
       <c r="D8" t="n">
-        <v>33.12907627980861</v>
+        <v>26.03594911662541</v>
       </c>
     </row>
     <row r="9">
@@ -3055,13 +3055,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.996874830438012</v>
+        <v>0.3328124717396686</v>
       </c>
       <c r="C9" t="n">
-        <v>57.46562012038278</v>
+        <v>28.84374755077128</v>
       </c>
       <c r="D9" t="n">
-        <v>32.39374724932775</v>
+        <v>21.07812321017901</v>
       </c>
     </row>
     <row r="10">
@@ -3069,13 +3069,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.1388273369263</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>29.75186417719959</v>
+        <v>16.79770321966293</v>
       </c>
       <c r="D10" t="n">
-        <v>24.62714116103124</v>
+        <v>19.64477156197868</v>
       </c>
     </row>
     <row r="11">
@@ -3083,13 +3083,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3553926689373453</v>
+        <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.92282714645877</v>
+        <v>12.79413608174443</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>17.23654444346124</v>
       </c>
     </row>
     <row r="12">
@@ -3100,10 +3100,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>17.14033316844506</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="D12" t="n">
-        <v>21.26269177857742</v>
+        <v>13.23494080095125</v>
       </c>
     </row>
     <row r="13">
@@ -3111,13 +3111,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.5203262832508095</v>
       </c>
       <c r="C13" t="n">
-        <v>14.82929907264807</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>15.34962535589888</v>
+        <v>8.325220532012953</v>
       </c>
     </row>
     <row r="14">
@@ -3128,10 +3128,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>13.82791641431633</v>
+        <v>15.67163860289184</v>
       </c>
       <c r="D14" t="n">
-        <v>14.13520344574558</v>
+        <v>2.765583282863265</v>
       </c>
     </row>
     <row r="15">
@@ -3142,10 +3142,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>13.25850274585317</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>11.82515109765283</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3153,13 +3153,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.653263133951629</v>
+        <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>23.97231544229862</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>8.266315669758143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3170,10 +3170,10 @@
         <v>0</v>
       </c>
       <c r="C17" t="n">
-        <v>33.0554452019901</v>
+        <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>4.249985811684442</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3184,10 +3184,10 @@
         <v>0</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3268,13 +3268,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.884955592153876</v>
+        <v>0.1992947839621025</v>
       </c>
       <c r="C2" t="n">
-        <v>3.980986940720816</v>
+        <v>6.7868218794582</v>
       </c>
       <c r="D2" t="n">
-        <v>11.59836737797182</v>
+        <v>12.92569027411351</v>
       </c>
     </row>
     <row r="3">
@@ -3282,13 +3282,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.29500733735955</v>
+        <v>1.119192382841364</v>
       </c>
       <c r="C3" t="n">
-        <v>22.60964962880404</v>
+        <v>18.33904711533042</v>
       </c>
       <c r="D3" t="n">
-        <v>106.499990956694</v>
+        <v>46.08814597586652</v>
       </c>
     </row>
     <row r="4">
@@ -3296,13 +3296,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.51115606320987</v>
+        <v>6.126105674500097</v>
       </c>
       <c r="C4" t="n">
-        <v>65.66419519854792</v>
+        <v>71.3308429474605</v>
       </c>
       <c r="D4" t="n">
-        <v>238.382087058985</v>
+        <v>116.2428551736393</v>
       </c>
     </row>
     <row r="5">
@@ -3310,13 +3310,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>50.56000676871075</v>
+        <v>13.94081740030471</v>
       </c>
       <c r="C5" t="n">
-        <v>184.0040634684585</v>
+        <v>185.378510254404</v>
       </c>
       <c r="D5" t="n">
-        <v>212.4992905842222</v>
+        <v>126.8418033886879</v>
       </c>
     </row>
     <row r="6">
@@ -3324,13 +3324,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>45.72588107299945</v>
+        <v>13.20254312671111</v>
       </c>
       <c r="C6" t="n">
-        <v>278.1389420901639</v>
+        <v>328.9767834591765</v>
       </c>
       <c r="D6" t="n">
-        <v>101.7561860497734</v>
+        <v>83.44168262704918</v>
       </c>
     </row>
     <row r="7">
@@ -3338,13 +3338,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>14.73210604992764</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>252.5418341973368</v>
+        <v>317.578692612871</v>
       </c>
       <c r="D7" t="n">
-        <v>46.17257627843174</v>
+        <v>42.33983324105218</v>
       </c>
     </row>
     <row r="8">
@@ -3352,13 +3352,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.005530633326986</v>
+        <v>1.919316761802514</v>
       </c>
       <c r="C8" t="n">
-        <v>164.3936530761284</v>
+        <v>162.8915790886308</v>
       </c>
       <c r="D8" t="n">
-        <v>34.38080460272329</v>
+        <v>28.53940576245478</v>
       </c>
     </row>
     <row r="9">
@@ -3366,13 +3366,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>1.553124868118454</v>
+        <v>0.5546874528994477</v>
       </c>
       <c r="C9" t="n">
-        <v>63.23436963053704</v>
+        <v>57.35468262980289</v>
       </c>
       <c r="D9" t="n">
-        <v>31.94999728700819</v>
+        <v>22.63124807829746</v>
       </c>
     </row>
     <row r="10">
@@ -3380,13 +3380,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.4270602513473625</v>
+        <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>30.60598467989432</v>
+        <v>24.91184799526281</v>
       </c>
       <c r="D10" t="n">
-        <v>25.33890824661018</v>
+        <v>20.4988920646734</v>
       </c>
     </row>
     <row r="11">
@@ -3397,10 +3397,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>22.38973814305275</v>
+        <v>15.63727743324319</v>
       </c>
       <c r="D11" t="n">
-        <v>23.98900515327081</v>
+        <v>17.76963344686726</v>
       </c>
     </row>
     <row r="12">
@@ -3411,10 +3411,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>16.27246819789088</v>
+        <v>12.80100831567416</v>
       </c>
       <c r="D12" t="n">
-        <v>19.52696183746906</v>
+        <v>13.88583952886689</v>
       </c>
     </row>
     <row r="13">
@@ -3422,13 +3422,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>0.2601631416254048</v>
       </c>
       <c r="C13" t="n">
-        <v>11.44717823151781</v>
+        <v>14.04880964777186</v>
       </c>
       <c r="D13" t="n">
-        <v>15.86995163914969</v>
+        <v>8.845546815263763</v>
       </c>
     </row>
     <row r="14">
@@ -3439,10 +3439,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.06233313145306</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>3.072870314292517</v>
       </c>
     </row>
     <row r="15">
@@ -3450,13 +3450,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.075013736150257</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>20.0669230748048</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="D15" t="n">
-        <v>6.808420328951629</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3467,10 +3467,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>28.10547327717769</v>
+        <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>3.306526267903257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3484,7 +3484,7 @@
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4722206457427158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3579,13 +3579,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.48382169174443</v>
+        <v>0.3809181092477624</v>
       </c>
       <c r="C2" t="n">
-        <v>5.272966919509619</v>
+        <v>19.65851602983813</v>
       </c>
       <c r="D2" t="n">
-        <v>15.27010379185489</v>
+        <v>11.79766216193392</v>
       </c>
     </row>
     <row r="3">
@@ -3593,13 +3593,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>8.98790023237955</v>
+        <v>0.8835729338221294</v>
       </c>
       <c r="C3" t="n">
-        <v>19.43369580556561</v>
+        <v>22.37403017978481</v>
       </c>
       <c r="D3" t="n">
-        <v>94.88100687693299</v>
+        <v>45.5089148303609</v>
       </c>
     </row>
     <row r="4">
@@ -3607,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>26.75066144531709</v>
+        <v>4.160646770597982</v>
       </c>
       <c r="C4" t="n">
-        <v>61.51631114810513</v>
+        <v>58.49154647132072</v>
       </c>
       <c r="D4" t="n">
-        <v>234.0172367659037</v>
+        <v>113.281904097631</v>
       </c>
     </row>
     <row r="5">
@@ -3621,13 +3621,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>49.21010367537139</v>
+        <v>11.97732199181109</v>
       </c>
       <c r="C5" t="n">
-        <v>157.987749305918</v>
+        <v>157.5214191464007</v>
       </c>
       <c r="D5" t="n">
-        <v>239.0801096767046</v>
+        <v>136.6101930459437</v>
       </c>
     </row>
     <row r="6">
@@ -3635,13 +3635,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>53.81646390369741</v>
+        <v>15.6981457909065</v>
       </c>
       <c r="C6" t="n">
-        <v>284.4987037182747</v>
+        <v>314.4861873444935</v>
       </c>
       <c r="D6" t="n">
-        <v>131.2203981496287</v>
+        <v>101.4341728027805</v>
       </c>
     </row>
     <row r="7">
@@ -3649,13 +3649,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>27.30829414132927</v>
+        <v>10.36038352291659</v>
       </c>
       <c r="C7" t="n">
-        <v>309.3143404385213</v>
+        <v>393.215480991158</v>
       </c>
       <c r="D7" t="n">
-        <v>58.03012505032471</v>
+        <v>53.89794896314989</v>
       </c>
     </row>
     <row r="8">
@@ -3663,13 +3663,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>7.510369937488099</v>
+        <v>3.922082078466008</v>
       </c>
       <c r="C8" t="n">
-        <v>226.7297235572796</v>
+        <v>280.637489997472</v>
       </c>
       <c r="D8" t="n">
-        <v>37.21805546799658</v>
+        <v>32.12769362147687</v>
       </c>
     </row>
     <row r="9">
@@ -3677,13 +3677,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>2.107812321017901</v>
+        <v>1.109374905798895</v>
       </c>
       <c r="C9" t="n">
-        <v>112.490615448008</v>
+        <v>121.2546772038193</v>
       </c>
       <c r="D9" t="n">
-        <v>32.9484347022272</v>
+        <v>24.4062479275757</v>
       </c>
     </row>
     <row r="10">
@@ -3691,13 +3691,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0.5694136684631501</v>
+        <v>0.1423534171157875</v>
       </c>
       <c r="C10" t="n">
-        <v>45.12603322570465</v>
+        <v>43.41779222031519</v>
       </c>
       <c r="D10" t="n">
-        <v>26.62008900065227</v>
+        <v>21.35301256736813</v>
       </c>
     </row>
     <row r="11">
@@ -3708,10 +3708,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>26.83214650476957</v>
+        <v>20.96816746730337</v>
       </c>
       <c r="D11" t="n">
-        <v>24.16670148773948</v>
+        <v>18.30272245027328</v>
       </c>
     </row>
     <row r="12">
@@ -3722,10 +3722,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>18.87606310955342</v>
+        <v>14.97067074205961</v>
       </c>
       <c r="D12" t="n">
-        <v>19.96089432274615</v>
+        <v>14.53673825678252</v>
       </c>
     </row>
     <row r="13">
@@ -3736,10 +3736,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>13.00815708127024</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="D13" t="n">
-        <v>16.1301147807751</v>
+        <v>9.365873098514571</v>
       </c>
     </row>
     <row r="14">
@@ -3750,10 +3750,10 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>11.67690719431156</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>11.06233313145306</v>
+        <v>3.68744437715102</v>
       </c>
     </row>
     <row r="15">
@@ -3761,13 +3761,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.7166758241001715</v>
+        <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>21.14193681095506</v>
+        <v>7.525096153051802</v>
       </c>
       <c r="D15" t="n">
-        <v>6.450082416901544</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -3778,10 +3778,10 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>26.86552592671396</v>
+        <v>0.8266315669758143</v>
       </c>
       <c r="D16" t="n">
-        <v>2.89321048441535</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3890,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.66919208139783</v>
+        <v>4.424736903040374</v>
       </c>
       <c r="C2" t="n">
-        <v>8.185812358009905</v>
+        <v>15.07179075559703</v>
       </c>
       <c r="D2" t="n">
-        <v>7.954119899807657</v>
+        <v>12.80689880189964</v>
       </c>
     </row>
     <row r="3">
@@ -3904,13 +3904,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.06872233929727672</v>
+        <v>0.07363107781851078</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>4.138066573400306</v>
+        <v>4.196971435655114</v>
       </c>
     </row>
     <row r="4">
@@ -3918,13 +3918,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>2.233476027161494</v>
+        <v>2.616357631817749</v>
       </c>
       <c r="C4" t="n">
-        <v>3.994731408580271</v>
+        <v>4.390375733391735</v>
       </c>
       <c r="D4" t="n">
-        <v>23.03670988015141</v>
+        <v>24.32574461582747</v>
       </c>
     </row>
     <row r="5">
@@ -3932,13 +3932,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.111379458936396</v>
+        <v>7.706719478337463</v>
       </c>
       <c r="C5" t="n">
-        <v>12.64000169217769</v>
+        <v>14.38260386721577</v>
       </c>
       <c r="D5" t="n">
-        <v>25.47635292520474</v>
+        <v>27.95526587842793</v>
       </c>
     </row>
     <row r="6">
@@ -3946,13 +3946,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.3258013690897</v>
+        <v>10.2641722479004</v>
       </c>
       <c r="C6" t="n">
-        <v>15.8994040702771</v>
+        <v>19.64280806657019</v>
       </c>
       <c r="D6" t="n">
-        <v>31.27553661419064</v>
+        <v>36.14598697495907</v>
       </c>
     </row>
     <row r="7">
@@ -3960,13 +3960,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>7.72537268471815</v>
+        <v>12.0970952117292</v>
       </c>
       <c r="C7" t="n">
-        <v>17.54677671800324</v>
+        <v>23.2360046641135</v>
       </c>
       <c r="D7" t="n">
-        <v>29.70375853969149</v>
+        <v>35.69241953559704</v>
       </c>
     </row>
     <row r="8">
@@ -3974,13 +3974,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>14.26970288122739</v>
       </c>
       <c r="C8" t="n">
-        <v>18.52557917913731</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>35.04839304161113</v>
+        <v>44.31118263117978</v>
       </c>
     </row>
     <row r="9">
@@ -3988,13 +3988,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.320311793491715</v>
+        <v>15.08749871886498</v>
       </c>
       <c r="C9" t="n">
-        <v>20.74531073843935</v>
+        <v>30.7296848906294</v>
       </c>
       <c r="D9" t="n">
-        <v>38.71718421238145</v>
+        <v>49.36718330805084</v>
       </c>
     </row>
     <row r="10">
@@ -4002,13 +4002,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7.544731107136738</v>
+        <v>14.94710879715769</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>37.72365553568369</v>
       </c>
       <c r="D10" t="n">
-        <v>51.53193699591508</v>
+        <v>69.04140730115694</v>
       </c>
     </row>
     <row r="11">
@@ -4016,13 +4016,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.04167537193487</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>24.34439782220815</v>
+        <v>38.20471191076462</v>
       </c>
       <c r="D11" t="n">
-        <v>43.5356019448248</v>
+        <v>58.10670137125595</v>
       </c>
     </row>
     <row r="12">
@@ -4030,13 +4030,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.207189823325082</v>
+        <v>11.28224461720434</v>
       </c>
       <c r="C12" t="n">
-        <v>22.56448923440869</v>
+        <v>36.66729500591412</v>
       </c>
       <c r="D12" t="n">
-        <v>42.52538355715483</v>
+        <v>59.44875048296136</v>
       </c>
     </row>
     <row r="13">
@@ -4044,13 +4044,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.682936549257286</v>
+        <v>10.926851948267</v>
       </c>
       <c r="C13" t="n">
-        <v>21.853703896534</v>
+        <v>36.94316611080748</v>
       </c>
       <c r="D13" t="n">
-        <v>43.70740779306801</v>
+        <v>60.87817514034472</v>
       </c>
     </row>
     <row r="14">
@@ -4058,13 +4058,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.916592502868027</v>
+        <v>11.67690719431156</v>
       </c>
       <c r="C14" t="n">
-        <v>23.04652735719387</v>
+        <v>39.33274002294421</v>
       </c>
       <c r="D14" t="n">
-        <v>44.55661955724149</v>
+        <v>63.60841550585509</v>
       </c>
     </row>
     <row r="15">
@@ -4072,13 +4072,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.733406592801372</v>
+        <v>13.61684065790326</v>
       </c>
       <c r="C15" t="n">
-        <v>25.80032966760617</v>
+        <v>45.50891483036089</v>
       </c>
       <c r="D15" t="n">
-        <v>41.92553570986004</v>
+        <v>61.27578296056467</v>
       </c>
     </row>
     <row r="16">
@@ -4086,13 +4086,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>6.199736752318607</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>51.25115715250048</v>
       </c>
       <c r="D16" t="n">
-        <v>40.09163099832699</v>
+        <v>57.864209688307</v>
       </c>
     </row>
     <row r="17">
@@ -4100,13 +4100,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.611089040398022</v>
+        <v>16.99994324673777</v>
       </c>
       <c r="C17" t="n">
-        <v>31.16656261901925</v>
+        <v>56.19425684338318</v>
       </c>
       <c r="D17" t="n">
-        <v>35.8887690764464</v>
+        <v>53.8331536146696</v>
       </c>
     </row>
     <row r="18">
@@ -4114,13 +4114,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.955682484588652</v>
+        <v>18.1917849596934</v>
       </c>
       <c r="C18" t="n">
-        <v>33.70830742531424</v>
+        <v>62.06608986248335</v>
       </c>
       <c r="D18" t="n">
-        <v>30.49799243242716</v>
+        <v>45.47946239923349</v>
       </c>
     </row>
     <row r="19">
@@ -4128,13 +4128,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>20.46158565191202</v>
       </c>
       <c r="C19" t="n">
-        <v>36.10868056219768</v>
+        <v>66.80105904006572</v>
       </c>
       <c r="D19" t="n">
-        <v>22.8688310227252</v>
+        <v>34.9050578767911</v>
       </c>
     </row>
     <row r="20">
@@ -4142,13 +4142,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>7.397468951499714</v>
+        <v>20.84741249968101</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>73.30219233758808</v>
       </c>
       <c r="D20" t="n">
-        <v>13.4499435481813</v>
+        <v>20.17491532227195</v>
       </c>
     </row>
     <row r="21">
@@ -4156,13 +4156,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>11.44977350273866</v>
+        <v>27.41820207255788</v>
       </c>
       <c r="C21" t="n">
-        <v>54.95891281314559</v>
+        <v>99.77179087514119</v>
       </c>
       <c r="D21" t="n">
-        <v>0.763318233515911</v>
+        <v>0.761616724237719</v>
       </c>
     </row>
   </sheetData>
@@ -4201,13 +4201,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>1.815251505152352</v>
+        <v>0.4388412237983242</v>
       </c>
       <c r="C2" t="n">
-        <v>3.079742548222244</v>
+        <v>16.62786086682823</v>
       </c>
       <c r="D2" t="n">
-        <v>11.36176618124834</v>
+        <v>12.07058802371453</v>
       </c>
     </row>
     <row r="3">
@@ -4215,13 +4215,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>11.96750451476862</v>
+        <v>1.035743827980385</v>
       </c>
       <c r="C3" t="n">
-        <v>22.66855449105885</v>
+        <v>47.19752088166541</v>
       </c>
       <c r="D3" t="n">
-        <v>102.2735670899115</v>
+        <v>44.21300786075511</v>
       </c>
     </row>
     <row r="4">
@@ -4229,13 +4229,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>37.30543101367455</v>
+        <v>2.986476516318797</v>
       </c>
       <c r="C4" t="n">
-        <v>90.23243149732434</v>
+        <v>57.1259354147134</v>
       </c>
       <c r="D4" t="n">
-        <v>236.5187299163246</v>
+        <v>109.4658507712236</v>
       </c>
     </row>
     <row r="5">
@@ -4243,13 +4243,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>30.75324683553134</v>
+        <v>9.645671194224914</v>
       </c>
       <c r="C5" t="n">
-        <v>239.4973524510094</v>
+        <v>134.1312800927205</v>
       </c>
       <c r="D5" t="n">
-        <v>212.1065915025234</v>
+        <v>144.145106676038</v>
       </c>
     </row>
     <row r="6">
@@ -4257,13 +4257,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>16.9459471230042</v>
+        <v>16.06041069377357</v>
       </c>
       <c r="C6" t="n">
-        <v>253.9074452539441</v>
+        <v>289.0471408320502</v>
       </c>
       <c r="D6" t="n">
-        <v>96.24170919501908</v>
+        <v>115.5625040145963</v>
       </c>
     </row>
     <row r="7">
@@ -4271,13 +4271,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>4.970588626601601</v>
+        <v>13.59426046070558</v>
       </c>
       <c r="C7" t="n">
-        <v>159.4181557110055</v>
+        <v>418.4277437839203</v>
       </c>
       <c r="D7" t="n">
-        <v>33.53650157707104</v>
+        <v>66.65379688442869</v>
       </c>
     </row>
     <row r="8">
@@ -4285,13 +4285,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>1.418625432636641</v>
+        <v>6.759332943739289</v>
       </c>
       <c r="C8" t="n">
-        <v>82.86441497695203</v>
+        <v>382.6116240375882</v>
       </c>
       <c r="D8" t="n">
-        <v>24.28352946454485</v>
+        <v>36.88426124855267</v>
       </c>
     </row>
     <row r="9">
@@ -4299,13 +4299,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3328124717396686</v>
+        <v>2.107812321017901</v>
       </c>
       <c r="C9" t="n">
-        <v>34.39062207976576</v>
+        <v>211.2249820641097</v>
       </c>
       <c r="D9" t="n">
-        <v>20.30156077611979</v>
+        <v>26.40312275801371</v>
       </c>
     </row>
     <row r="10">
@@ -4313,13 +4313,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>0</v>
+        <v>0.4270602513473625</v>
       </c>
       <c r="C10" t="n">
-        <v>20.92595231602077</v>
+        <v>82.84968876138834</v>
       </c>
       <c r="D10" t="n">
-        <v>18.93300447639974</v>
+        <v>22.20713307006285</v>
       </c>
     </row>
     <row r="11">
@@ -4330,10 +4330,10 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>15.10418842983717</v>
+        <v>31.8076438698924</v>
       </c>
       <c r="D11" t="n">
-        <v>15.99267010218054</v>
+        <v>18.8358114536793</v>
       </c>
     </row>
     <row r="12">
@@ -4344,10 +4344,10 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>10.63134588928871</v>
+        <v>18.22516438163779</v>
       </c>
       <c r="D12" t="n">
-        <v>13.0179745583127</v>
+        <v>15.18763698469816</v>
       </c>
     </row>
     <row r="13">
@@ -4358,10 +4358,10 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>9.626036240139976</v>
+        <v>15.34962535589888</v>
       </c>
       <c r="D13" t="n">
-        <v>9.105709956889166</v>
+        <v>9.886199381765381</v>
       </c>
     </row>
     <row r="14">
@@ -4369,13 +4369,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.3072870314292517</v>
+        <v>0</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>16.28621266575034</v>
       </c>
       <c r="D14" t="n">
-        <v>5.223879534297279</v>
+        <v>4.302018440009523</v>
       </c>
     </row>
     <row r="15">
@@ -4386,10 +4386,10 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>22.57528845915541</v>
+        <v>10.39179944945249</v>
       </c>
       <c r="D15" t="n">
-        <v>2.150027472300515</v>
+        <v>0.3583379120500857</v>
       </c>
     </row>
     <row r="16">
@@ -4400,7 +4400,7 @@
         <v>0</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>2.479894700927443</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -4512,13 +4512,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.10352547730242</v>
+        <v>4.608323723734528</v>
       </c>
       <c r="C2" t="n">
-        <v>5.431028299893355</v>
+        <v>11.06920536538279</v>
       </c>
       <c r="D2" t="n">
-        <v>24.16179274921825</v>
+        <v>18.95754816900591</v>
       </c>
     </row>
     <row r="3">
@@ -4526,13 +4526,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>9.925469289935252</v>
+        <v>7.137305809874312</v>
       </c>
       <c r="C3" t="n">
-        <v>20.62651926622549</v>
+        <v>29.75677291572082</v>
       </c>
       <c r="D3" t="n">
-        <v>9.817477042468104</v>
+        <v>11.74661128131309</v>
       </c>
     </row>
     <row r="4">
@@ -4540,13 +4540,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.008254892261474</v>
+        <v>0.9189158511750145</v>
       </c>
       <c r="C4" t="n">
-        <v>1.454950097693773</v>
+        <v>1.710204500797944</v>
       </c>
       <c r="D4" t="n">
-        <v>19.62906359871073</v>
+        <v>18.45489334443154</v>
       </c>
     </row>
     <row r="5">
@@ -4554,13 +4554,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.68784528777852</v>
+        <v>3.632466505713199</v>
       </c>
       <c r="C5" t="n">
-        <v>9.424777960769381</v>
+        <v>8.29576810088555</v>
       </c>
       <c r="D5" t="n">
-        <v>28.49522711576368</v>
+        <v>24.20008090968388</v>
       </c>
     </row>
     <row r="6">
@@ -4568,13 +4568,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.130834486572086</v>
+        <v>5.75598678999905</v>
       </c>
       <c r="C6" t="n">
-        <v>18.47551004622073</v>
+        <v>14.32958949118645</v>
       </c>
       <c r="D6" t="n">
-        <v>32.52333794628834</v>
+        <v>28.6591789823729</v>
       </c>
     </row>
     <row r="7">
@@ -4582,13 +4582,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.108434215823654</v>
       </c>
       <c r="C7" t="n">
-        <v>20.9603134856694</v>
+        <v>16.58859095865835</v>
       </c>
       <c r="D7" t="n">
-        <v>32.69808903764427</v>
+        <v>27.90716024091983</v>
       </c>
     </row>
     <row r="8">
@@ -4596,13 +4596,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.762098260402782</v>
+        <v>6.508987279156353</v>
       </c>
       <c r="C8" t="n">
-        <v>21.69662426385451</v>
+        <v>17.19040230136165</v>
       </c>
       <c r="D8" t="n">
-        <v>35.79943003535994</v>
+        <v>32.04424506661589</v>
       </c>
     </row>
     <row r="9">
@@ -4610,13 +4610,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>8.874999246391162</v>
+        <v>6.656249434793372</v>
       </c>
       <c r="C9" t="n">
-        <v>22.74218556887735</v>
+        <v>18.74843590800133</v>
       </c>
       <c r="D9" t="n">
-        <v>39.2718716652809</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -4624,13 +4624,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.256498192715677</v>
+        <v>6.405903770210439</v>
       </c>
       <c r="C10" t="n">
-        <v>25.62361508084176</v>
+        <v>21.78007281871549</v>
       </c>
       <c r="D10" t="n">
-        <v>50.67781649322036</v>
+        <v>46.12250714551515</v>
       </c>
     </row>
     <row r="11">
@@ -4638,13 +4638,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>6.75246070980956</v>
+        <v>5.330890034060179</v>
       </c>
       <c r="C11" t="n">
-        <v>27.36523550817559</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="D11" t="n">
-        <v>46.37874329632356</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4652,13 +4652,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>5.641122308602172</v>
+        <v>4.339324852770901</v>
       </c>
       <c r="C12" t="n">
-        <v>25.81898287398687</v>
+        <v>21.69662426385451</v>
       </c>
       <c r="D12" t="n">
-        <v>43.17628228507047</v>
+        <v>39.4878561602152</v>
       </c>
     </row>
     <row r="13">
@@ -4666,13 +4666,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>4.943099690882691</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>23.93500902953724</v>
+        <v>20.55288818840698</v>
       </c>
       <c r="D13" t="n">
-        <v>44.22773407631881</v>
+        <v>40.06512381031234</v>
       </c>
     </row>
     <row r="14">
@@ -4680,13 +4680,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.994731408580272</v>
       </c>
       <c r="C14" t="n">
-        <v>23.96838845148163</v>
+        <v>21.20280516861837</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>40.86917518009047</v>
       </c>
     </row>
     <row r="15">
@@ -4694,13 +4694,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.375068680751286</v>
+        <v>4.30005494460103</v>
       </c>
       <c r="C15" t="n">
-        <v>26.15866757965626</v>
+        <v>23.29196428325557</v>
       </c>
       <c r="D15" t="n">
-        <v>42.28387362191012</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -4708,13 +4708,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.7864209688307</v>
+        <v>4.959789401854886</v>
       </c>
       <c r="C16" t="n">
-        <v>28.9321048441535</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -4722,13 +4722,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>6.138868394655306</v>
+        <v>5.194427103169874</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.36098972218912</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -4736,13 +4736,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>5.885577486959628</v>
       </c>
       <c r="C18" t="n">
-        <v>34.24335992412875</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>31.03304493124168</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -4750,13 +4750,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.221736112439537</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>23.47064236542849</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -4767,10 +4767,10 @@
         <v>6.724971774090649</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.12244072559037</v>
+        <v>12.77744637077223</v>
       </c>
     </row>
     <row r="21">
@@ -4778,13 +4778,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>13.39842973255469</v>
+        <v>11.67707032909678</v>
       </c>
       <c r="C21" t="n">
-        <v>70.14472036455103</v>
+        <v>59.94229435603012</v>
       </c>
       <c r="D21" t="n">
-        <v>1.576285850888787</v>
+        <v>0.7784713552731184</v>
       </c>
     </row>
   </sheetData>
@@ -4823,13 +4823,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.455571992499525</v>
+        <v>2.088177366932966</v>
       </c>
       <c r="C2" t="n">
-        <v>5.866924280578939</v>
+        <v>7.279659226990098</v>
       </c>
       <c r="D2" t="n">
-        <v>30.45970427196154</v>
+        <v>24.74200564242812</v>
       </c>
     </row>
     <row r="3">
@@ -4837,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>16.5915362017711</v>
+        <v>12.74799393964483</v>
       </c>
       <c r="C3" t="n">
-        <v>20.97013096271187</v>
+        <v>38.61704594654829</v>
       </c>
       <c r="D3" t="n">
-        <v>27.73928138349363</v>
+        <v>25.47635292520473</v>
       </c>
     </row>
     <row r="4">
@@ -4851,13 +4851,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>11.63960078155018</v>
+        <v>8.908378668335558</v>
       </c>
       <c r="C4" t="n">
-        <v>31.97061398879738</v>
+        <v>48.15374314560181</v>
       </c>
       <c r="D4" t="n">
-        <v>20.21614872585032</v>
+        <v>20.44587768864407</v>
       </c>
     </row>
     <row r="5">
@@ -4865,13 +4865,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.043417883165113</v>
+        <v>2.454369260617026</v>
       </c>
       <c r="C5" t="n">
-        <v>5.375068680751288</v>
+        <v>5.129631754689585</v>
       </c>
       <c r="D5" t="n">
-        <v>29.40334374219198</v>
+        <v>25.72178985126644</v>
       </c>
     </row>
     <row r="6">
@@ -4879,13 +4879,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>7.446556336712058</v>
+        <v>5.514476854754335</v>
       </c>
       <c r="C6" t="n">
-        <v>16.54343056426301</v>
+        <v>13.72581465307466</v>
       </c>
       <c r="D6" t="n">
-        <v>34.3346624606237</v>
+        <v>30.06798693796707</v>
       </c>
     </row>
     <row r="7">
@@ -4893,13 +4893,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.521970983489814</v>
+        <v>6.827073535332318</v>
       </c>
       <c r="C7" t="n">
-        <v>24.49362347325367</v>
+        <v>19.22360179685679</v>
       </c>
       <c r="D7" t="n">
-        <v>35.27321326588365</v>
+        <v>30.48228446915921</v>
       </c>
     </row>
     <row r="8">
@@ -4907,13 +4907,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>9.596583809012571</v>
+        <v>6.842781498600267</v>
       </c>
       <c r="C8" t="n">
-        <v>25.61870634232051</v>
+        <v>20.36144738607885</v>
       </c>
       <c r="D8" t="n">
-        <v>36.80081269369168</v>
+        <v>32.96217917008666</v>
       </c>
     </row>
     <row r="9">
@@ -4921,13 +4921,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.429686699290611</v>
+        <v>7.09999939711293</v>
       </c>
       <c r="C9" t="n">
-        <v>25.73749781453438</v>
+        <v>20.85624822901923</v>
       </c>
       <c r="D9" t="n">
-        <v>40.27030908049991</v>
+        <v>35.38905949498476</v>
       </c>
     </row>
     <row r="10">
@@ -4935,13 +4935,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>8.825911861178826</v>
+        <v>6.8329640215578</v>
       </c>
       <c r="C10" t="n">
-        <v>27.3318560862312</v>
+        <v>22.91890015564179</v>
       </c>
       <c r="D10" t="n">
-        <v>50.1084028247572</v>
+        <v>45.26838664282043</v>
       </c>
     </row>
     <row r="11">
@@ -4949,13 +4949,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7.640942382152923</v>
+        <v>5.863979037466197</v>
       </c>
       <c r="C11" t="n">
-        <v>29.14219885286231</v>
+        <v>24.87748682561417</v>
       </c>
       <c r="D11" t="n">
-        <v>47.97801030654161</v>
+        <v>43.35790561035613</v>
       </c>
     </row>
     <row r="12">
@@ -4963,13 +4963,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.075054793879263</v>
+        <v>4.773257338047991</v>
       </c>
       <c r="C12" t="n">
-        <v>29.29044275620359</v>
+        <v>24.5171854181556</v>
       </c>
       <c r="D12" t="n">
-        <v>44.69504598354028</v>
+        <v>40.57268737340794</v>
       </c>
     </row>
     <row r="13">
@@ -4977,13 +4977,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.203262832508096</v>
+        <v>3.902447124381071</v>
       </c>
       <c r="C13" t="n">
-        <v>26.79680358741669</v>
+        <v>22.89435646303562</v>
       </c>
       <c r="D13" t="n">
-        <v>44.74806035956962</v>
+        <v>40.32528695193774</v>
       </c>
     </row>
     <row r="14">
@@ -4991,13 +4991,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>25.50482360862789</v>
+        <v>22.43195329433537</v>
       </c>
       <c r="D14" t="n">
-        <v>44.86390658867074</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5005,13 +5005,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>5.0167307687012</v>
+        <v>3.941717032550943</v>
       </c>
       <c r="C15" t="n">
-        <v>26.51700549170635</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5019,13 +5019,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>5.373105185342793</v>
+        <v>4.546473618366978</v>
       </c>
       <c r="C16" t="n">
-        <v>29.34542062764141</v>
+        <v>26.03889435973815</v>
       </c>
       <c r="D16" t="n">
-        <v>40.5049467818149</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -5033,13 +5033,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="C17" t="n">
-        <v>31.63878326476196</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>36.83321036793183</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -5047,13 +5047,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -5061,13 +5061,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.619924769736241</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.09962384868121</v>
       </c>
       <c r="D19" t="n">
-        <v>24.07245370813179</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -5078,10 +5078,10 @@
         <v>6.052474596681584</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>14.79493790299943</v>
+        <v>13.4499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -5089,13 +5089,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>15.44022153104499</v>
+        <v>13.62503236339233</v>
       </c>
       <c r="C21" t="n">
-        <v>86.14018327846154</v>
+        <v>73.7354692607114</v>
       </c>
       <c r="D21" t="n">
-        <v>3.250572953904209</v>
+        <v>1.602944983928509</v>
       </c>
     </row>
   </sheetData>
@@ -5134,13 +5134,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>6.378414834491527</v>
+        <v>1.752419652080557</v>
       </c>
       <c r="C2" t="n">
-        <v>5.825690877000572</v>
+        <v>10.74817386609408</v>
       </c>
       <c r="D2" t="n">
-        <v>39.55854199492097</v>
+        <v>20.94755076551419</v>
       </c>
     </row>
     <row r="3">
@@ -5148,13 +5148,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.90216938694059</v>
+        <v>9.58185759344887</v>
       </c>
       <c r="C3" t="n">
-        <v>22.3003991019663</v>
+        <v>32.51057522613313</v>
       </c>
       <c r="D3" t="n">
-        <v>45.67090320156162</v>
+        <v>40.10439371848221</v>
       </c>
     </row>
     <row r="4">
@@ -5162,13 +5162,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>23.25367612278995</v>
+        <v>18.26345254210341</v>
       </c>
       <c r="C4" t="n">
-        <v>43.54640116957152</v>
+        <v>77.73772846537518</v>
       </c>
       <c r="D4" t="n">
-        <v>29.55845987946297</v>
+        <v>29.04795107325463</v>
       </c>
     </row>
     <row r="5">
@@ -5176,13 +5176,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>10.4801567428347</v>
+        <v>8.320311793491719</v>
       </c>
       <c r="C5" t="n">
-        <v>35.95650966803944</v>
+        <v>54.51154127830416</v>
       </c>
       <c r="D5" t="n">
-        <v>29.94330497952772</v>
+        <v>27.53802310412304</v>
       </c>
     </row>
     <row r="6">
@@ -5190,13 +5190,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>4.508185457901354</v>
       </c>
       <c r="C6" t="n">
-        <v>12.23650338573225</v>
+        <v>10.58618549489336</v>
       </c>
       <c r="D6" t="n">
-        <v>36.34724525432967</v>
+        <v>31.55729820530948</v>
       </c>
     </row>
     <row r="7">
@@ -5204,13 +5204,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.462084373530759</v>
+        <v>7.006733365209485</v>
       </c>
       <c r="C7" t="n">
-        <v>24.25407703341745</v>
+        <v>19.82246789644735</v>
       </c>
       <c r="D7" t="n">
-        <v>37.66867766424586</v>
+        <v>32.81786225756237</v>
       </c>
     </row>
     <row r="8">
@@ -5218,13 +5218,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.43106935762236</v>
+        <v>7.42692138262712</v>
       </c>
       <c r="C8" t="n">
-        <v>29.87458264023044</v>
+        <v>23.699389580518</v>
       </c>
       <c r="D8" t="n">
-        <v>38.05254101660637</v>
+        <v>34.29735604786232</v>
       </c>
     </row>
     <row r="9">
@@ -5232,13 +5232,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>9.984374152190059</v>
+        <v>7.432811868852599</v>
       </c>
       <c r="C9" t="n">
-        <v>29.7312474754104</v>
+        <v>23.96249796525614</v>
       </c>
       <c r="D9" t="n">
-        <v>41.26874649571891</v>
+        <v>36.0546844384641</v>
       </c>
     </row>
     <row r="10">
@@ -5246,13 +5246,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.395325529641976</v>
+        <v>7.260024272905163</v>
       </c>
       <c r="C10" t="n">
-        <v>29.89421759431538</v>
+        <v>24.76949457814703</v>
       </c>
       <c r="D10" t="n">
-        <v>49.25428232206248</v>
+        <v>44.69897297435728</v>
       </c>
     </row>
     <row r="11">
@@ -5260,13 +5260,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.174031385558941</v>
+        <v>6.397068040872215</v>
       </c>
       <c r="C11" t="n">
-        <v>30.91916219754903</v>
+        <v>26.47675383583222</v>
       </c>
       <c r="D11" t="n">
-        <v>49.75497365122833</v>
+        <v>44.95717262057418</v>
       </c>
     </row>
     <row r="12">
@@ -5274,13 +5274,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>6.725953521794898</v>
+        <v>5.207189823325082</v>
       </c>
       <c r="C12" t="n">
-        <v>31.89403766786613</v>
+        <v>27.12078032981814</v>
       </c>
       <c r="D12" t="n">
-        <v>46.2138096820101</v>
+        <v>41.44055234396211</v>
       </c>
     </row>
     <row r="13">
@@ -5288,13 +5288,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.463425974133501</v>
+        <v>4.162610266006476</v>
       </c>
       <c r="C13" t="n">
-        <v>30.17892442854696</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>45.00822350119503</v>
+        <v>41.10577637681396</v>
       </c>
     </row>
     <row r="14">
@@ -5302,13 +5302,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>27.9631198600619</v>
+        <v>24.27567548291088</v>
       </c>
       <c r="D14" t="n">
-        <v>45.47848065152925</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5316,13 +5316,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.658392856651115</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="C15" t="n">
-        <v>27.23368131580652</v>
+        <v>24.72531593145592</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5330,13 +5330,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.959789401854886</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="C16" t="n">
-        <v>29.75873641112932</v>
+        <v>26.45221014322606</v>
       </c>
       <c r="D16" t="n">
-        <v>40.91826256530281</v>
+        <v>37.61173629739955</v>
       </c>
     </row>
     <row r="17">
@@ -5344,13 +5344,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="C17" t="n">
-        <v>32.11100391050468</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5358,13 +5358,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>5.350524988145117</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>31.56809743005619</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -5372,13 +5372,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>6.018113427032947</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="C19" t="n">
-        <v>36.71049190490098</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -5389,10 +5389,10 @@
         <v>5.37997741927252</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>15.46743508040849</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -5400,13 +5400,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>16.73061019424582</v>
+        <v>14.82885832525245</v>
       </c>
       <c r="C21" t="n">
-        <v>102.0567221848995</v>
+        <v>87.32549902648667</v>
       </c>
       <c r="D21" t="n">
-        <v>4.182652548561456</v>
+        <v>2.471476387542075</v>
       </c>
     </row>
   </sheetData>
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.879687000734148</v>
+        <v>1.877101610519901</v>
       </c>
       <c r="C2" t="n">
-        <v>5.093307089632453</v>
+        <v>10.09923863358694</v>
       </c>
       <c r="D2" t="n">
-        <v>41.4150269036517</v>
+        <v>28.02496996542945</v>
       </c>
     </row>
     <row r="3">
@@ -5459,13 +5459,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.96874830438012</v>
+        <v>7.677267047210058</v>
       </c>
       <c r="C3" t="n">
-        <v>22.44766125760332</v>
+        <v>38.0427235395639</v>
       </c>
       <c r="D3" t="n">
-        <v>65.5758379051657</v>
+        <v>47.55585879371549</v>
       </c>
     </row>
     <row r="4">
@@ -5473,13 +5473,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>29.13729011434109</v>
+        <v>18.42936790412112</v>
       </c>
       <c r="C4" t="n">
-        <v>49.83842220608933</v>
+        <v>79.89462817160542</v>
       </c>
       <c r="D4" t="n">
-        <v>44.92477494633405</v>
+        <v>42.60195987808609</v>
       </c>
     </row>
     <row r="5">
@@ -5487,13 +5487,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>22.65382827549515</v>
+        <v>18.28505099159685</v>
       </c>
       <c r="C5" t="n">
-        <v>59.96024103687396</v>
+        <v>104.4334120392545</v>
       </c>
       <c r="D5" t="n">
-        <v>33.37942194439156</v>
+        <v>31.857713002809</v>
       </c>
     </row>
     <row r="6">
@@ -5501,13 +5501,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9.982410656781569</v>
+        <v>7.969827863075609</v>
       </c>
       <c r="C6" t="n">
-        <v>35.42145716922493</v>
+        <v>51.20010627187966</v>
       </c>
       <c r="D6" t="n">
-        <v>38.03781480104267</v>
+        <v>33.12711278440013</v>
       </c>
     </row>
     <row r="7">
@@ -5515,13 +5515,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>8.683558444063037</v>
+        <v>6.467753875577986</v>
       </c>
       <c r="C7" t="n">
-        <v>21.02020009562846</v>
+        <v>17.66654993792135</v>
       </c>
       <c r="D7" t="n">
-        <v>39.64493579289469</v>
+        <v>34.97378021608837</v>
       </c>
     </row>
     <row r="8">
@@ -5529,13 +5529,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>10.6814150222053</v>
+        <v>7.844164156932015</v>
       </c>
       <c r="C8" t="n">
-        <v>31.71045084717197</v>
+        <v>25.61870634232051</v>
       </c>
       <c r="D8" t="n">
-        <v>40.05530633326986</v>
+        <v>35.79943003535994</v>
       </c>
     </row>
     <row r="9">
@@ -5543,13 +5543,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>10.76093658624928</v>
+        <v>7.765624340592267</v>
       </c>
       <c r="C9" t="n">
-        <v>34.27968458918587</v>
+        <v>27.5124976638126</v>
       </c>
       <c r="D9" t="n">
-        <v>42.26718391093791</v>
+        <v>36.72030938194344</v>
       </c>
     </row>
     <row r="10">
@@ -5557,13 +5557,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>9.82238578098934</v>
+        <v>7.544731107136738</v>
       </c>
       <c r="C10" t="n">
-        <v>33.16834618797849</v>
+        <v>27.47420950334699</v>
       </c>
       <c r="D10" t="n">
-        <v>48.68486865359933</v>
+        <v>44.4142661401257</v>
       </c>
     </row>
     <row r="11">
@@ -5571,13 +5571,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>8.707120388964958</v>
+        <v>6.930157044278233</v>
       </c>
       <c r="C11" t="n">
-        <v>33.58460721457913</v>
+        <v>28.25371718051895</v>
       </c>
       <c r="D11" t="n">
-        <v>50.82115165804038</v>
+        <v>45.4902616239802</v>
       </c>
     </row>
     <row r="12">
@@ -5585,13 +5585,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>7.376852249710534</v>
+        <v>5.641122308602172</v>
       </c>
       <c r="C12" t="n">
-        <v>33.84673385161303</v>
+        <v>29.29044275620359</v>
       </c>
       <c r="D12" t="n">
-        <v>47.08167465256428</v>
+        <v>42.95931604243193</v>
       </c>
     </row>
     <row r="13">
@@ -5599,13 +5599,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>5.723589115758904</v>
+        <v>4.422773407631881</v>
       </c>
       <c r="C13" t="n">
-        <v>33.30088212805181</v>
+        <v>28.09761929554372</v>
       </c>
       <c r="D13" t="n">
-        <v>45.78871292607123</v>
+        <v>41.62610266006477</v>
       </c>
     </row>
     <row r="14">
@@ -5613,13 +5613,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>4.609305471438775</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>30.72870314292517</v>
+        <v>26.42668470291564</v>
       </c>
       <c r="D14" t="n">
-        <v>45.7857676829585</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5627,13 +5627,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>4.30005494460103</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>28.66703296400686</v>
+        <v>25.44199175555609</v>
       </c>
       <c r="D15" t="n">
-        <v>43.00054944601029</v>
+        <v>40.49218406165969</v>
       </c>
     </row>
     <row r="16">
@@ -5641,13 +5641,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="C16" t="n">
-        <v>30.17205219461722</v>
+        <v>26.86552592671396</v>
       </c>
       <c r="D16" t="n">
-        <v>41.33157834879071</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -5655,13 +5655,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="C17" t="n">
-        <v>32.58322455624739</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>37.30543101367455</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5669,13 +5669,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.815472489330605</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="C18" t="n">
-        <v>34.77841242294325</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>32.1031499288707</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -5683,13 +5683,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="C19" t="n">
-        <v>37.31230324760427</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>24.67426505083508</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -5700,10 +5700,10 @@
         <v>4.707480241863455</v>
       </c>
       <c r="C20" t="n">
-        <v>39.00483628972577</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -5711,13 +5711,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>18.04964374960438</v>
+        <v>16.06034426079604</v>
       </c>
       <c r="C21" t="n">
-        <v>117.7524377950381</v>
+        <v>100.5884719491962</v>
       </c>
       <c r="D21" t="n">
-        <v>6.016547916534793</v>
+        <v>3.381125107536008</v>
       </c>
     </row>
   </sheetData>
@@ -5756,13 +5756,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>5.701008918561228</v>
+        <v>1.814269757448106</v>
       </c>
       <c r="C2" t="n">
-        <v>6.66999390265283</v>
+        <v>7.465209543092746</v>
       </c>
       <c r="D2" t="n">
-        <v>38.55814108429347</v>
+        <v>29.31596819651401</v>
       </c>
     </row>
     <row r="3">
@@ -5770,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.76472470834603</v>
+        <v>6.975317438673589</v>
       </c>
       <c r="C3" t="n">
-        <v>19.63986282345744</v>
+        <v>38.61213720802706</v>
       </c>
       <c r="D3" t="n">
-        <v>77.58261232810419</v>
+        <v>57.61386402372407</v>
       </c>
     </row>
     <row r="4">
@@ -5784,13 +5784,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>24.74691438094935</v>
+        <v>16.43838355990859</v>
       </c>
       <c r="C4" t="n">
-        <v>44.17177445717674</v>
+        <v>87.32253130193681</v>
       </c>
       <c r="D4" t="n">
-        <v>58.04485126588842</v>
+        <v>54.89245938755191</v>
       </c>
     </row>
     <row r="5">
@@ -5798,13 +5798,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>20.17491532227196</v>
+        <v>23.07107104980005</v>
       </c>
       <c r="C5" t="n">
-        <v>57.33406592801374</v>
+        <v>127.283589855599</v>
       </c>
       <c r="D5" t="n">
-        <v>33.35487825178539</v>
+        <v>39.5398887885403</v>
       </c>
     </row>
     <row r="6">
@@ -5812,13 +5812,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>11.10945702125691</v>
+        <v>15.97990738202533</v>
       </c>
       <c r="C6" t="n">
-        <v>44.75984133202059</v>
+        <v>109.4040006658561</v>
       </c>
       <c r="D6" t="n">
-        <v>31.11452999069417</v>
+        <v>35.46170882509904</v>
       </c>
     </row>
     <row r="7">
@@ -5826,13 +5826,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>5.150248456478767</v>
+        <v>8.084692344472483</v>
       </c>
       <c r="C7" t="n">
-        <v>22.99645822427728</v>
+        <v>45.75337000871835</v>
       </c>
       <c r="D7" t="n">
-        <v>30.78171751895449</v>
+        <v>36.9500383447372</v>
       </c>
     </row>
     <row r="8">
@@ -5840,13 +5840,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>4.756567627075796</v>
+        <v>7.677267047210056</v>
       </c>
       <c r="C8" t="n">
-        <v>18.60902773399829</v>
+        <v>24.86766934857171</v>
       </c>
       <c r="D8" t="n">
-        <v>30.12492830481337</v>
+        <v>37.38495257771854</v>
       </c>
     </row>
     <row r="9">
@@ -5854,13 +5854,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>4.881249585515139</v>
+        <v>8.209374302911826</v>
       </c>
       <c r="C9" t="n">
-        <v>21.85468564423824</v>
+        <v>30.39687241888974</v>
       </c>
       <c r="D9" t="n">
-        <v>30.39687241888974</v>
+        <v>37.49687181600267</v>
       </c>
     </row>
     <row r="10">
@@ -5868,13 +5868,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.270602513473626</v>
+        <v>7.829437941368314</v>
       </c>
       <c r="C10" t="n">
-        <v>21.49536598448391</v>
+        <v>30.7483380970101</v>
       </c>
       <c r="D10" t="n">
-        <v>33.16834618797849</v>
+        <v>44.27191272300992</v>
       </c>
     </row>
     <row r="11">
@@ -5882,13 +5882,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>3.731623023842126</v>
+        <v>7.285549713215578</v>
       </c>
       <c r="C11" t="n">
-        <v>20.07968579496001</v>
+        <v>30.56376952861169</v>
       </c>
       <c r="D11" t="n">
-        <v>34.65078522139116</v>
+        <v>45.84565429291754</v>
       </c>
     </row>
     <row r="12">
@@ -5896,13 +5896,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.037527396939631</v>
+        <v>6.075054793879263</v>
       </c>
       <c r="C12" t="n">
-        <v>19.7439280801076</v>
+        <v>31.02617269731195</v>
       </c>
       <c r="D12" t="n">
-        <v>31.89403766786613</v>
+        <v>44.04414725562465</v>
       </c>
     </row>
     <row r="13">
@@ -5910,13 +5910,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.341468274628643</v>
+        <v>4.682936549257286</v>
       </c>
       <c r="C13" t="n">
-        <v>18.99190933865455</v>
+        <v>30.69925071179776</v>
       </c>
       <c r="D13" t="n">
-        <v>30.43908757017236</v>
+        <v>42.40659208494097</v>
       </c>
     </row>
     <row r="14">
@@ -5924,13 +5924,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.536435157146258</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>17.51536079146734</v>
+        <v>28.5776939229204</v>
       </c>
       <c r="D14" t="n">
-        <v>29.49955501720816</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -5938,13 +5938,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>16.12520604225386</v>
+        <v>27.23368131580652</v>
       </c>
       <c r="D15" t="n">
-        <v>27.95035713990669</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -5952,13 +5952,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="C16" t="n">
-        <v>15.70599977254047</v>
+        <v>27.27884171020187</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -5966,13 +5966,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>1.416661937228147</v>
+        <v>3.305544520199011</v>
       </c>
       <c r="C17" t="n">
-        <v>16.52772260099505</v>
+        <v>28.80545939030567</v>
       </c>
       <c r="D17" t="n">
-        <v>23.61103228713579</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5980,13 +5980,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="C18" t="n">
-        <v>17.12167996206437</v>
+        <v>31.56809743005619</v>
       </c>
       <c r="D18" t="n">
-        <v>20.33199495495144</v>
+        <v>31.03304493124168</v>
       </c>
     </row>
     <row r="19">
@@ -5994,13 +5994,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -6008,13 +6008,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>36.31484758008951</v>
       </c>
       <c r="D20" t="n">
-        <v>10.08745766113597</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -6022,13 +6022,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.051075727734198</v>
+        <v>17.31105916808768</v>
       </c>
       <c r="C21" t="n">
-        <v>66.1038349475081</v>
+        <v>113.3874375509743</v>
       </c>
       <c r="D21" t="n">
-        <v>4.406922329833874</v>
+        <v>4.327764792021919</v>
       </c>
     </row>
   </sheetData>
@@ -6067,13 +6067,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>4.775220833456485</v>
+        <v>1.790707812546182</v>
       </c>
       <c r="C2" t="n">
-        <v>11.31562403914874</v>
+        <v>12.39947350463721</v>
       </c>
       <c r="D2" t="n">
-        <v>43.23518714732528</v>
+        <v>22.52718282164731</v>
       </c>
     </row>
     <row r="3">
@@ -6081,13 +6081,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>19.11953654020664</v>
+        <v>6.49426106359265</v>
       </c>
       <c r="C3" t="n">
-        <v>23.70429831903924</v>
+        <v>33.76230354904781</v>
       </c>
       <c r="D3" t="n">
-        <v>91.22399667861362</v>
+        <v>65.84090978531235</v>
       </c>
     </row>
     <row r="4">
@@ -6095,13 +6095,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>31.00064725700153</v>
+        <v>14.74094177926586</v>
       </c>
       <c r="C4" t="n">
-        <v>47.34969177582366</v>
+        <v>90.93438110586081</v>
       </c>
       <c r="D4" t="n">
-        <v>85.24220791663781</v>
+        <v>68.17845106912399</v>
       </c>
     </row>
     <row r="5">
@@ -6109,13 +6109,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>29.77149913128453</v>
+        <v>24.02827506144069</v>
       </c>
       <c r="C5" t="n">
-        <v>71.47123286916781</v>
+        <v>143.7524075943392</v>
       </c>
       <c r="D5" t="n">
-        <v>47.02571503342222</v>
+        <v>49.1119289049467</v>
       </c>
     </row>
     <row r="6">
@@ -6123,13 +6123,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>20.40758952817845</v>
+        <v>22.78243722475149</v>
       </c>
       <c r="C6" t="n">
-        <v>72.09071567054754</v>
+        <v>152.0707558924225</v>
       </c>
       <c r="D6" t="n">
-        <v>35.17994723398021</v>
+        <v>39.48687441251096</v>
       </c>
     </row>
     <row r="7">
@@ -6137,13 +6137,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.761517423326035</v>
+        <v>13.11516758103314</v>
       </c>
       <c r="C7" t="n">
-        <v>47.31042186765379</v>
+        <v>98.45358677268713</v>
       </c>
       <c r="D7" t="n">
-        <v>32.99752208743954</v>
+        <v>38.50709020367265</v>
       </c>
     </row>
     <row r="8">
@@ -6151,13 +6151,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>5.424156065963627</v>
+        <v>8.344855486097888</v>
       </c>
       <c r="C8" t="n">
-        <v>25.78560345204247</v>
+        <v>41.55738032076748</v>
       </c>
       <c r="D8" t="n">
-        <v>32.12769362147687</v>
+        <v>39.05392367493811</v>
       </c>
     </row>
     <row r="9">
@@ -6165,13 +6165,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.103124566674919</v>
+        <v>8.320311793491715</v>
       </c>
       <c r="C9" t="n">
-        <v>23.2968730217768</v>
+        <v>31.17343485294896</v>
       </c>
       <c r="D9" t="n">
-        <v>31.72812230584841</v>
+        <v>38.38437174064178</v>
       </c>
     </row>
     <row r="10">
@@ -6179,13 +6179,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.697662764820988</v>
+        <v>8.114144775599888</v>
       </c>
       <c r="C10" t="n">
-        <v>24.62714116103124</v>
+        <v>34.02246669067321</v>
       </c>
       <c r="D10" t="n">
-        <v>33.45305302221006</v>
+        <v>44.27191272300992</v>
       </c>
     </row>
     <row r="11">
@@ -6193,13 +6193,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.08701569277947</v>
+        <v>7.463246047684251</v>
       </c>
       <c r="C11" t="n">
-        <v>23.27821981539612</v>
+        <v>33.40691088011046</v>
       </c>
       <c r="D11" t="n">
-        <v>35.36157055926586</v>
+        <v>46.02335062738621</v>
       </c>
     </row>
     <row r="12">
@@ -6207,13 +6207,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.254493639578176</v>
+        <v>6.508987279156352</v>
       </c>
       <c r="C12" t="n">
-        <v>21.69662426385451</v>
+        <v>32.97886888105885</v>
       </c>
       <c r="D12" t="n">
-        <v>33.1958351236974</v>
+        <v>44.91201222617883</v>
       </c>
     </row>
     <row r="13">
@@ -6221,13 +6221,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>4.943099690882691</v>
       </c>
       <c r="C13" t="n">
-        <v>21.07321447165778</v>
+        <v>32.780555844801</v>
       </c>
       <c r="D13" t="n">
-        <v>30.95941385342317</v>
+        <v>43.1870815098172</v>
       </c>
     </row>
     <row r="14">
@@ -6235,13 +6235,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>3.68744437715102</v>
       </c>
       <c r="C14" t="n">
-        <v>19.35908298004286</v>
+        <v>31.03599017435442</v>
       </c>
       <c r="D14" t="n">
-        <v>30.11412908006666</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -6249,13 +6249,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="C15" t="n">
-        <v>17.5585576904542</v>
+        <v>28.66703296400686</v>
       </c>
       <c r="D15" t="n">
-        <v>28.30869505195678</v>
+        <v>41.20885988575986</v>
       </c>
     </row>
     <row r="16">
@@ -6263,13 +6263,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.89321048441535</v>
       </c>
       <c r="C16" t="n">
-        <v>16.53263133951629</v>
+        <v>28.51878906066559</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -6277,13 +6277,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="C17" t="n">
-        <v>16.99994324673777</v>
+        <v>29.27768003604838</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -6291,13 +6291,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>31.03304493124168</v>
       </c>
       <c r="D18" t="n">
-        <v>20.86704745376595</v>
+        <v>31.03304493124168</v>
       </c>
     </row>
     <row r="19">
@@ -6305,13 +6305,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>33.7014351913845</v>
       </c>
       <c r="D19" t="n">
-        <v>15.64709491028566</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -6319,13 +6319,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>35.64235040268044</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>16.13993225781756</v>
       </c>
     </row>
     <row r="21">
@@ -6333,13 +6333,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.269068920302517</v>
+        <v>17.69005485229327</v>
       </c>
       <c r="C21" t="n">
-        <v>75.41659004813862</v>
+        <v>126.4838921938969</v>
       </c>
       <c r="D21" t="n">
-        <v>5.451801690226888</v>
+        <v>5.307016455687981</v>
       </c>
     </row>
   </sheetData>
@@ -6378,13 +6378,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>3.788564390688441</v>
+        <v>1.664062358698343</v>
       </c>
       <c r="C2" t="n">
-        <v>6.947828502954677</v>
+        <v>7.935466693426968</v>
       </c>
       <c r="D2" t="n">
-        <v>40.13090090649687</v>
+        <v>18.03961406553514</v>
       </c>
     </row>
     <row r="3">
@@ -6392,13 +6392,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>17.63709750679395</v>
+        <v>9.198975988792613</v>
       </c>
       <c r="C3" t="n">
-        <v>36.03504948437918</v>
+        <v>54.75206946584461</v>
       </c>
       <c r="D3" t="n">
-        <v>103.7903672929728</v>
+        <v>70.66129101316419</v>
       </c>
     </row>
     <row r="4">
@@ -6406,13 +6406,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>34.58697162061513</v>
+        <v>11.53749902030852</v>
       </c>
       <c r="C4" t="n">
-        <v>53.71828913327272</v>
+        <v>126.746573861376</v>
       </c>
       <c r="D4" t="n">
-        <v>109.5424270921549</v>
+        <v>62.97126124579891</v>
       </c>
     </row>
     <row r="5">
@@ -6420,13 +6420,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>38.48451000647497</v>
+        <v>12.81180754042088</v>
       </c>
       <c r="C5" t="n">
-        <v>80.50331174823846</v>
+        <v>90.86075002804232</v>
       </c>
       <c r="D5" t="n">
-        <v>66.90610604442014</v>
+        <v>37.7236555356837</v>
       </c>
     </row>
     <row r="6">
@@ -6434,13 +6434,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>31.03402667894593</v>
+        <v>8.130834486572086</v>
       </c>
       <c r="C6" t="n">
-        <v>94.67189461592844</v>
+        <v>64.84541761320608</v>
       </c>
       <c r="D6" t="n">
-        <v>41.57996051796516</v>
+        <v>25.35854320069512</v>
       </c>
     </row>
     <row r="7">
@@ -6448,13 +6448,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>17.24734366820796</v>
+        <v>5.509568116233099</v>
       </c>
       <c r="C7" t="n">
-        <v>77.37350006709961</v>
+        <v>29.22466566001905</v>
       </c>
       <c r="D7" t="n">
-        <v>36.05173919535137</v>
+        <v>27.42806736124739</v>
       </c>
     </row>
     <row r="8">
@@ -6462,13 +6462,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>8.261406931236909</v>
+        <v>5.757950285407543</v>
       </c>
       <c r="C8" t="n">
-        <v>45.8132566186774</v>
+        <v>22.94835258676919</v>
       </c>
       <c r="D8" t="n">
-        <v>33.71321616383547</v>
+        <v>28.28906009787184</v>
       </c>
     </row>
     <row r="9">
@@ -6476,13 +6476,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>5.435937038414587</v>
+        <v>5.768749510154256</v>
       </c>
       <c r="C9" t="n">
-        <v>28.51093507903161</v>
+        <v>25.95937279569415</v>
       </c>
       <c r="D9" t="n">
-        <v>33.17030968338697</v>
+        <v>33.72499713628642</v>
       </c>
     </row>
     <row r="10">
@@ -6490,13 +6490,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>4.982369599052563</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="C10" t="n">
-        <v>26.90479583488384</v>
+        <v>26.1930287493049</v>
       </c>
       <c r="D10" t="n">
-        <v>34.16482010778901</v>
+        <v>36.01541453029424</v>
       </c>
     </row>
     <row r="11">
@@ -6504,13 +6504,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>4.264712027248144</v>
+        <v>4.797801030654161</v>
       </c>
       <c r="C11" t="n">
         <v>26.29905750136355</v>
       </c>
       <c r="D11" t="n">
-        <v>35.53926689373453</v>
+        <v>35.89465956267188</v>
       </c>
     </row>
     <row r="12">
@@ -6518,13 +6518,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="C12" t="n">
-        <v>24.5171854181556</v>
+        <v>26.68684784454105</v>
       </c>
       <c r="D12" t="n">
-        <v>34.28066633689012</v>
+        <v>35.1485313074443</v>
       </c>
     </row>
     <row r="13">
@@ -6532,13 +6532,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.861794557879452</v>
       </c>
       <c r="C13" t="n">
-        <v>22.89435646303562</v>
+        <v>25.49598787928967</v>
       </c>
       <c r="D13" t="n">
-        <v>31.47974013667398</v>
+        <v>34.34153469455343</v>
       </c>
     </row>
     <row r="14">
@@ -6546,13 +6546,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>1.84372218857551</v>
+        <v>2.458296251434013</v>
       </c>
       <c r="C14" t="n">
-        <v>21.20280516861837</v>
+        <v>23.96838845148163</v>
       </c>
       <c r="D14" t="n">
-        <v>30.42141611149592</v>
+        <v>34.41614752007619</v>
       </c>
     </row>
     <row r="15">
@@ -6560,13 +6560,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>1.433351648200343</v>
+        <v>2.150027472300515</v>
       </c>
       <c r="C15" t="n">
-        <v>19.35024725070463</v>
+        <v>24.00864010735575</v>
       </c>
       <c r="D15" t="n">
-        <v>28.66703296400686</v>
+        <v>32.6087499965578</v>
       </c>
     </row>
     <row r="16">
@@ -6574,13 +6574,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="C16" t="n">
-        <v>17.77257868998001</v>
+        <v>24.79894700927443</v>
       </c>
       <c r="D16" t="n">
-        <v>26.03889435973815</v>
+        <v>30.17205219461722</v>
       </c>
     </row>
     <row r="17">
@@ -6588,13 +6588,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.9444412914854317</v>
+        <v>2.361103228713579</v>
       </c>
       <c r="C17" t="n">
-        <v>17.47216389248049</v>
+        <v>26.44435616159209</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>26.44435616159209</v>
       </c>
     </row>
     <row r="18">
@@ -6602,10 +6602,10 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.140209995258047</v>
       </c>
       <c r="C18" t="n">
-        <v>17.65673246087889</v>
+        <v>28.89283493598363</v>
       </c>
       <c r="D18" t="n">
         <v>20.86704745376595</v>
@@ -6616,13 +6616,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="C19" t="n">
-        <v>18.65615162380213</v>
+        <v>30.69237847786803</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>13.84166088217578</v>
       </c>
     </row>
     <row r="20">
@@ -6630,13 +6630,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>13.4499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>19.50241814486288</v>
+        <v>96.16709636949629</v>
       </c>
       <c r="D20" t="n">
-        <v>10.75995483854504</v>
+        <v>4.03498306445439</v>
       </c>
     </row>
     <row r="21">
@@ -6644,13 +6644,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.472848637928375</v>
+        <v>0</v>
       </c>
       <c r="C21" t="n">
-        <v>84.06954717669421</v>
+        <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>6.538742558187328</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
